--- a/115年法規清單檢核表_已完成檢核.xlsx
+++ b/115年法規清單檢核表_已完成檢核.xlsx
@@ -2571,7 +2571,7 @@
       </c>
       <c r="G4" s="14" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>V</t>
         </is>
       </c>
       <c r="H4" s="14" t="inlineStr">
@@ -2584,10 +2584,14 @@
           <t>董事會</t>
         </is>
       </c>
-      <c r="J4" s="52" t="n"/>
+      <c r="J4" s="52" t="inlineStr">
+        <is>
+          <t>110.10.29</t>
+        </is>
+      </c>
       <c r="K4" s="52" t="inlineStr">
         <is>
-          <t>無特別說明</t>
+          <t>逾2年未更新(5年未修，預計115提案)</t>
         </is>
       </c>
     </row>
@@ -2800,7 +2804,11 @@
           <t>會計室</t>
         </is>
       </c>
-      <c r="J4" s="38" t="n"/>
+      <c r="J4" s="38" t="inlineStr">
+        <is>
+          <t>115.2.25</t>
+        </is>
+      </c>
       <c r="K4" s="38" t="inlineStr">
         <is>
           <t>無特別說明</t>
@@ -2838,7 +2846,7 @@
       </c>
       <c r="G5" s="97" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>V</t>
         </is>
       </c>
       <c r="H5" s="97" t="inlineStr">
@@ -2851,10 +2859,14 @@
           <t>會計室</t>
         </is>
       </c>
-      <c r="J5" s="38" t="n"/>
+      <c r="J5" s="38" t="inlineStr">
+        <is>
+          <t>112.4.12</t>
+        </is>
+      </c>
       <c r="K5" s="38" t="inlineStr">
         <is>
-          <t>無特別說明</t>
+          <t>逾2年未更新(3年未修，預計115提案)</t>
         </is>
       </c>
     </row>
@@ -2889,7 +2901,7 @@
       </c>
       <c r="G6" s="97" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>V</t>
         </is>
       </c>
       <c r="H6" s="97" t="inlineStr">
@@ -2902,10 +2914,14 @@
           <t>會計室</t>
         </is>
       </c>
-      <c r="J6" s="38" t="n"/>
+      <c r="J6" s="38" t="inlineStr">
+        <is>
+          <t>111.10.5</t>
+        </is>
+      </c>
       <c r="K6" s="38" t="inlineStr">
         <is>
-          <t>無特別說明</t>
+          <t>逾2年未更新(4年未修，預計115提案)</t>
         </is>
       </c>
     </row>
@@ -2940,7 +2956,7 @@
       </c>
       <c r="G7" s="97" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>V</t>
         </is>
       </c>
       <c r="H7" s="97" t="inlineStr">
@@ -2953,10 +2969,14 @@
           <t>會計室</t>
         </is>
       </c>
-      <c r="J7" s="38" t="n"/>
+      <c r="J7" s="38" t="inlineStr">
+        <is>
+          <t>111.10.5</t>
+        </is>
+      </c>
       <c r="K7" s="38" t="inlineStr">
         <is>
-          <t>無特別說明</t>
+          <t>逾2年未更新(4年未修，預計115提案)</t>
         </is>
       </c>
     </row>
@@ -3147,7 +3167,7 @@
       </c>
       <c r="G4" s="97" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>V</t>
         </is>
       </c>
       <c r="H4" s="97" t="inlineStr">
@@ -3160,10 +3180,14 @@
           <t>稽核室</t>
         </is>
       </c>
-      <c r="J4" s="38" t="n"/>
+      <c r="J4" s="38" t="inlineStr">
+        <is>
+          <t>105.9.7</t>
+        </is>
+      </c>
       <c r="K4" s="38" t="inlineStr">
         <is>
-          <t>無特別說明</t>
+          <t>逾2年未更新(10年未修，預計115提案)</t>
         </is>
       </c>
     </row>
@@ -3211,7 +3235,11 @@
           <t>稽核室</t>
         </is>
       </c>
-      <c r="J5" s="38" t="n"/>
+      <c r="J5" s="38" t="inlineStr">
+        <is>
+          <t>114.3.26</t>
+        </is>
+      </c>
       <c r="K5" s="38" t="inlineStr">
         <is>
           <t>無特別說明</t>
@@ -3262,7 +3290,11 @@
           <t>稽核室</t>
         </is>
       </c>
-      <c r="J6" s="38" t="n"/>
+      <c r="J6" s="38" t="inlineStr">
+        <is>
+          <t>114.11.5</t>
+        </is>
+      </c>
       <c r="K6" s="38" t="inlineStr">
         <is>
           <t>無特別說明</t>
@@ -3313,7 +3345,11 @@
           <t>稽核室</t>
         </is>
       </c>
-      <c r="J7" s="38" t="n"/>
+      <c r="J7" s="38" t="inlineStr">
+        <is>
+          <t>114.11.5</t>
+        </is>
+      </c>
       <c r="K7" s="38" t="inlineStr">
         <is>
           <t>無特別說明</t>
@@ -3503,7 +3539,7 @@
       </c>
       <c r="F4" s="97" t="inlineStr">
         <is>
-          <t>V</t>
+          <t>X</t>
         </is>
       </c>
       <c r="G4" s="97" t="inlineStr">
@@ -3521,10 +3557,14 @@
           <t>公共事務暨校友服務室</t>
         </is>
       </c>
-      <c r="J4" s="38" t="n"/>
+      <c r="J4" s="38" t="inlineStr">
+        <is>
+          <t>114.9.3</t>
+        </is>
+      </c>
       <c r="K4" s="38" t="inlineStr">
         <is>
-          <t>無特別說明</t>
+          <t>格式瑕疵(含各式顏色標記)</t>
         </is>
       </c>
     </row>
@@ -3554,7 +3594,7 @@
       </c>
       <c r="F5" s="97" t="inlineStr">
         <is>
-          <t>V</t>
+          <t>X</t>
         </is>
       </c>
       <c r="G5" s="97" t="inlineStr">
@@ -3572,10 +3612,14 @@
           <t>公共事務暨校友服務室</t>
         </is>
       </c>
-      <c r="J5" s="38" t="n"/>
+      <c r="J5" s="38" t="inlineStr">
+        <is>
+          <t>113.5.22</t>
+        </is>
+      </c>
       <c r="K5" s="38" t="inlineStr">
         <is>
-          <t>無特別說明</t>
+          <t>格式瑕疵(含各式顏色標記)</t>
         </is>
       </c>
     </row>
@@ -3610,7 +3654,7 @@
       </c>
       <c r="G6" s="97" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>V</t>
         </is>
       </c>
       <c r="H6" s="97" t="inlineStr">
@@ -3623,10 +3667,14 @@
           <t>公共事務暨校友服務室</t>
         </is>
       </c>
-      <c r="J6" s="38" t="n"/>
+      <c r="J6" s="38" t="inlineStr">
+        <is>
+          <t>108.3.13</t>
+        </is>
+      </c>
       <c r="K6" s="38" t="inlineStr">
         <is>
-          <t>無特別說明</t>
+          <t>逾2年未更新(7年未修，預計115提案)</t>
         </is>
       </c>
     </row>
@@ -3835,12 +3883,12 @@
       </c>
       <c r="J4" s="75" t="inlineStr">
         <is>
-          <t>105.10.05</t>
+          <t>105.10.5</t>
         </is>
       </c>
       <c r="K4" s="75" t="inlineStr">
         <is>
-          <t>預計廢止；逾2年未更新(預計115提案)</t>
+          <t>預計廢止；逾2年未更新(10年未修，預計115提案)</t>
         </is>
       </c>
     </row>
@@ -3870,7 +3918,7 @@
       </c>
       <c r="F5" s="103" t="inlineStr">
         <is>
-          <t>V</t>
+          <t>X</t>
         </is>
       </c>
       <c r="G5" s="103" t="inlineStr">
@@ -3890,12 +3938,12 @@
       </c>
       <c r="J5" s="75" t="inlineStr">
         <is>
-          <t>114.09.03</t>
+          <t>114.9.3</t>
         </is>
       </c>
       <c r="K5" s="75" t="inlineStr">
         <is>
-          <t>無特別說明</t>
+          <t>格式瑕疵(含各式顏色標記)</t>
         </is>
       </c>
     </row>
@@ -3945,12 +3993,12 @@
       </c>
       <c r="J6" s="75" t="inlineStr">
         <is>
-          <t>112.03.08</t>
+          <t>112.3.8</t>
         </is>
       </c>
       <c r="K6" s="75" t="inlineStr">
         <is>
-          <t>逾2年未更新(預計115提案)</t>
+          <t>逾2年未更新(3年未修，預計115提案)</t>
         </is>
       </c>
     </row>
@@ -4159,7 +4207,11 @@
           <t>體育暨健康促進中心</t>
         </is>
       </c>
-      <c r="J4" s="38" t="n"/>
+      <c r="J4" s="38" t="inlineStr">
+        <is>
+          <t>114.6.18</t>
+        </is>
+      </c>
       <c r="K4" s="38" t="inlineStr">
         <is>
           <t>無特別說明</t>
@@ -4197,7 +4249,7 @@
       </c>
       <c r="G5" s="97" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>V</t>
         </is>
       </c>
       <c r="H5" s="97" t="inlineStr">
@@ -4210,10 +4262,14 @@
           <t>體育暨健康促進中心</t>
         </is>
       </c>
-      <c r="J5" s="38" t="n"/>
+      <c r="J5" s="38" t="inlineStr">
+        <is>
+          <t>111.9.6</t>
+        </is>
+      </c>
       <c r="K5" s="38" t="inlineStr">
         <is>
-          <t>無特別說明</t>
+          <t>逾2年未更新(4年未修，預計115提案)</t>
         </is>
       </c>
     </row>
@@ -4261,7 +4317,11 @@
           <t>體育暨健康促進中心</t>
         </is>
       </c>
-      <c r="J6" s="38" t="n"/>
+      <c r="J6" s="38" t="inlineStr">
+        <is>
+          <t>113.12.11</t>
+        </is>
+      </c>
       <c r="K6" s="38" t="inlineStr">
         <is>
           <t>無特別說明</t>
@@ -4299,7 +4359,7 @@
       </c>
       <c r="G7" s="97" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>V</t>
         </is>
       </c>
       <c r="H7" s="97" t="inlineStr">
@@ -4312,10 +4372,14 @@
           <t>體育暨健康促進中心</t>
         </is>
       </c>
-      <c r="J7" s="38" t="n"/>
+      <c r="J7" s="38" t="inlineStr">
+        <is>
+          <t>111.9.6</t>
+        </is>
+      </c>
       <c r="K7" s="38" t="inlineStr">
         <is>
-          <t>無特別說明</t>
+          <t>逾2年未更新(4年未修，預計115提案)</t>
         </is>
       </c>
     </row>
@@ -4350,7 +4414,7 @@
       </c>
       <c r="G8" s="97" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>V</t>
         </is>
       </c>
       <c r="H8" s="97" t="inlineStr">
@@ -4363,10 +4427,14 @@
           <t>體育暨健康促進中心</t>
         </is>
       </c>
-      <c r="J8" s="38" t="n"/>
+      <c r="J8" s="38" t="inlineStr">
+        <is>
+          <t>111.9.6</t>
+        </is>
+      </c>
       <c r="K8" s="38" t="inlineStr">
         <is>
-          <t>無特別說明</t>
+          <t>逾2年未更新(4年未修，預計115提案)</t>
         </is>
       </c>
     </row>
@@ -4401,7 +4469,7 @@
       </c>
       <c r="G9" s="97" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>V</t>
         </is>
       </c>
       <c r="H9" s="97" t="inlineStr">
@@ -4414,10 +4482,14 @@
           <t>體育暨健康促進中心</t>
         </is>
       </c>
-      <c r="J9" s="38" t="n"/>
+      <c r="J9" s="38" t="inlineStr">
+        <is>
+          <t>110.2.3</t>
+        </is>
+      </c>
       <c r="K9" s="38" t="inlineStr">
         <is>
-          <t>無特別說明</t>
+          <t>逾2年未更新(5年未修，預計115提案)</t>
         </is>
       </c>
     </row>
@@ -4452,7 +4524,7 @@
       </c>
       <c r="G10" s="97" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>V</t>
         </is>
       </c>
       <c r="H10" s="97" t="inlineStr">
@@ -4465,10 +4537,14 @@
           <t>體育暨健康促進中心</t>
         </is>
       </c>
-      <c r="J10" s="38" t="n"/>
+      <c r="J10" s="38" t="inlineStr">
+        <is>
+          <t>111.9.6</t>
+        </is>
+      </c>
       <c r="K10" s="38" t="inlineStr">
         <is>
-          <t>無特別說明</t>
+          <t>逾2年未更新(4年未修，預計115提案)</t>
         </is>
       </c>
     </row>
@@ -4503,7 +4579,7 @@
       </c>
       <c r="G11" s="97" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>V</t>
         </is>
       </c>
       <c r="H11" s="97" t="inlineStr">
@@ -4516,10 +4592,14 @@
           <t>體育暨健康促進中心</t>
         </is>
       </c>
-      <c r="J11" s="38" t="n"/>
+      <c r="J11" s="38" t="inlineStr">
+        <is>
+          <t>108.9.25</t>
+        </is>
+      </c>
       <c r="K11" s="38" t="inlineStr">
         <is>
-          <t>無特別說明</t>
+          <t>逾2年未更新(7年未修，預計115提案)</t>
         </is>
       </c>
     </row>
@@ -4567,7 +4647,11 @@
           <t>體育暨健康促進中心</t>
         </is>
       </c>
-      <c r="J12" s="38" t="n"/>
+      <c r="J12" s="38" t="inlineStr">
+        <is>
+          <t>113.2.2</t>
+        </is>
+      </c>
       <c r="K12" s="38" t="inlineStr">
         <is>
           <t>無特別說明</t>
@@ -4618,7 +4702,11 @@
           <t>體育暨健康促進中心</t>
         </is>
       </c>
-      <c r="J13" s="38" t="n"/>
+      <c r="J13" s="38" t="inlineStr">
+        <is>
+          <t>113.4.26</t>
+        </is>
+      </c>
       <c r="K13" s="38" t="inlineStr">
         <is>
           <t>無特別說明</t>
@@ -4807,7 +4895,7 @@
       </c>
       <c r="G4" s="97" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>V</t>
         </is>
       </c>
       <c r="H4" s="97" t="inlineStr">
@@ -4820,10 +4908,14 @@
           <t>環境安全衛生中心</t>
         </is>
       </c>
-      <c r="J4" s="38" t="n"/>
+      <c r="J4" s="38" t="inlineStr">
+        <is>
+          <t>110.5.12</t>
+        </is>
+      </c>
       <c r="K4" s="38" t="inlineStr">
         <is>
-          <t>無特別說明</t>
+          <t>逾2年未更新(5年未修，預計115提案)</t>
         </is>
       </c>
     </row>
@@ -4858,7 +4950,7 @@
       </c>
       <c r="G5" s="97" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>V</t>
         </is>
       </c>
       <c r="H5" s="97" t="inlineStr">
@@ -4871,10 +4963,14 @@
           <t>環境安全衛生中心</t>
         </is>
       </c>
-      <c r="J5" s="38" t="n"/>
+      <c r="J5" s="38" t="inlineStr">
+        <is>
+          <t>112.11.29</t>
+        </is>
+      </c>
       <c r="K5" s="38" t="inlineStr">
         <is>
-          <t>無特別說明</t>
+          <t>逾2年未更新(3年未修，預計115提案)</t>
         </is>
       </c>
     </row>
@@ -5065,7 +5161,7 @@
       </c>
       <c r="G4" s="97" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>V</t>
         </is>
       </c>
       <c r="H4" s="97" t="inlineStr">
@@ -5078,10 +5174,14 @@
           <t>推廣教育中心</t>
         </is>
       </c>
-      <c r="J4" s="38" t="n"/>
+      <c r="J4" s="38" t="inlineStr">
+        <is>
+          <t>106.5.10</t>
+        </is>
+      </c>
       <c r="K4" s="38" t="inlineStr">
         <is>
-          <t>無特別說明</t>
+          <t>逾2年未更新(9年未修，預計115提案)</t>
         </is>
       </c>
     </row>
@@ -5116,7 +5216,7 @@
       </c>
       <c r="G5" s="97" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>V</t>
         </is>
       </c>
       <c r="H5" s="97" t="inlineStr">
@@ -5129,10 +5229,14 @@
           <t>推廣教育中心</t>
         </is>
       </c>
-      <c r="J5" s="38" t="n"/>
+      <c r="J5" s="38" t="inlineStr">
+        <is>
+          <t>104.12.2</t>
+        </is>
+      </c>
       <c r="K5" s="38" t="inlineStr">
         <is>
-          <t>無特別說明</t>
+          <t>逾2年未更新(11年未修，預計115提案)</t>
         </is>
       </c>
     </row>
@@ -5180,7 +5284,11 @@
           <t>推廣教育中心</t>
         </is>
       </c>
-      <c r="J6" s="38" t="n"/>
+      <c r="J6" s="38" t="inlineStr">
+        <is>
+          <t>113.11.13</t>
+        </is>
+      </c>
       <c r="K6" s="38" t="inlineStr">
         <is>
           <t>無特別說明</t>
@@ -5231,7 +5339,11 @@
           <t>推廣教育中心</t>
         </is>
       </c>
-      <c r="J7" s="38" t="n"/>
+      <c r="J7" s="38" t="inlineStr">
+        <is>
+          <t>113.11.13</t>
+        </is>
+      </c>
       <c r="K7" s="38" t="inlineStr">
         <is>
           <t>無特別說明</t>
@@ -5421,7 +5533,7 @@
       </c>
       <c r="G4" s="97" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>V</t>
         </is>
       </c>
       <c r="H4" s="97" t="inlineStr">
@@ -5434,10 +5546,14 @@
           <t>共同教育中心</t>
         </is>
       </c>
-      <c r="J4" s="38" t="n"/>
+      <c r="J4" s="38" t="inlineStr">
+        <is>
+          <t>108.3.27</t>
+        </is>
+      </c>
       <c r="K4" s="53" t="inlineStr">
         <is>
-          <t>無特別說明</t>
+          <t>逾2年未更新(7年未修，預計115提案)</t>
         </is>
       </c>
     </row>
@@ -5472,7 +5588,7 @@
       </c>
       <c r="G5" s="97" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>V</t>
         </is>
       </c>
       <c r="H5" s="97" t="inlineStr">
@@ -5485,10 +5601,14 @@
           <t>共同教育中心</t>
         </is>
       </c>
-      <c r="J5" s="38" t="n"/>
+      <c r="J5" s="38" t="inlineStr">
+        <is>
+          <t>109.1.9</t>
+        </is>
+      </c>
       <c r="K5" s="53" t="inlineStr">
         <is>
-          <t>無特別說明</t>
+          <t>逾2年未更新(6年未修，預計115提案)</t>
         </is>
       </c>
     </row>
@@ -5536,7 +5656,11 @@
           <t>共同教育中心</t>
         </is>
       </c>
-      <c r="J6" s="38" t="n"/>
+      <c r="J6" s="38" t="inlineStr">
+        <is>
+          <t>114.6.18</t>
+        </is>
+      </c>
       <c r="K6" s="53" t="inlineStr">
         <is>
           <t>無特別說明</t>
@@ -5574,7 +5698,7 @@
       </c>
       <c r="G7" s="97" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>V</t>
         </is>
       </c>
       <c r="H7" s="97" t="inlineStr">
@@ -5587,10 +5711,14 @@
           <t>共同教育中心</t>
         </is>
       </c>
-      <c r="J7" s="38" t="n"/>
+      <c r="J7" s="38" t="inlineStr">
+        <is>
+          <t>109.1.9</t>
+        </is>
+      </c>
       <c r="K7" s="53" t="inlineStr">
         <is>
-          <t>無特別說明</t>
+          <t>逾2年未更新(6年未修，預計115提案)</t>
         </is>
       </c>
     </row>
@@ -5625,7 +5753,7 @@
       </c>
       <c r="G8" s="97" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>V</t>
         </is>
       </c>
       <c r="H8" s="97" t="inlineStr">
@@ -5638,10 +5766,14 @@
           <t>共同教育中心</t>
         </is>
       </c>
-      <c r="J8" s="38" t="n"/>
+      <c r="J8" s="38" t="inlineStr">
+        <is>
+          <t>112.10.12</t>
+        </is>
+      </c>
       <c r="K8" s="53" t="inlineStr">
         <is>
-          <t>無特別說明</t>
+          <t>逾2年未更新(3年未修，預計115提案)</t>
         </is>
       </c>
     </row>
@@ -5689,7 +5821,11 @@
           <t>共同教育中心</t>
         </is>
       </c>
-      <c r="J9" s="38" t="n"/>
+      <c r="J9" s="38" t="inlineStr">
+        <is>
+          <t>113.6.13</t>
+        </is>
+      </c>
       <c r="K9" s="53" t="inlineStr">
         <is>
           <t>無特別說明</t>
@@ -5740,7 +5876,11 @@
           <t>共同教育中心</t>
         </is>
       </c>
-      <c r="J10" s="38" t="n"/>
+      <c r="J10" s="38" t="inlineStr">
+        <is>
+          <t>114.3.19</t>
+        </is>
+      </c>
       <c r="K10" s="53" t="inlineStr">
         <is>
           <t>無特別說明</t>
@@ -5773,7 +5913,7 @@
       </c>
       <c r="F11" s="97" t="inlineStr">
         <is>
-          <t>V</t>
+          <t>X</t>
         </is>
       </c>
       <c r="G11" s="97" t="inlineStr">
@@ -5791,10 +5931,14 @@
           <t>共同教育中心</t>
         </is>
       </c>
-      <c r="J11" s="38" t="n"/>
+      <c r="J11" s="38" t="inlineStr">
+        <is>
+          <t>114.6.18</t>
+        </is>
+      </c>
       <c r="K11" s="53" t="inlineStr">
         <is>
-          <t>無特別說明</t>
+          <t>格式瑕疵(含各式顏色標記)</t>
         </is>
       </c>
     </row>
@@ -6000,7 +6144,7 @@
       </c>
       <c r="G4" s="97" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>V</t>
         </is>
       </c>
       <c r="H4" s="97" t="inlineStr">
@@ -6013,10 +6157,14 @@
           <t>研究暨產學發展處</t>
         </is>
       </c>
-      <c r="J4" s="38" t="n"/>
+      <c r="J4" s="38" t="inlineStr">
+        <is>
+          <t>105.9.30</t>
+        </is>
+      </c>
       <c r="K4" s="38" t="inlineStr">
         <is>
-          <t>無特別說明</t>
+          <t>逾2年未更新(10年未修，預計115提案)</t>
         </is>
       </c>
     </row>
@@ -6064,7 +6212,11 @@
           <t>研究暨產學發展處</t>
         </is>
       </c>
-      <c r="J5" s="38" t="n"/>
+      <c r="J5" s="38" t="inlineStr">
+        <is>
+          <t>114.1.2</t>
+        </is>
+      </c>
       <c r="K5" s="38" t="inlineStr">
         <is>
           <t>無特別說明</t>
@@ -6097,12 +6249,12 @@
       </c>
       <c r="F6" s="35" t="inlineStr">
         <is>
-          <t>V</t>
+          <t>X</t>
         </is>
       </c>
       <c r="G6" s="97" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>V</t>
         </is>
       </c>
       <c r="H6" s="97" t="inlineStr">
@@ -6115,10 +6267,14 @@
           <t>研究暨產學發展處</t>
         </is>
       </c>
-      <c r="J6" s="38" t="n"/>
+      <c r="J6" s="38" t="inlineStr">
+        <is>
+          <t>105.9.30</t>
+        </is>
+      </c>
       <c r="K6" s="38" t="inlineStr">
         <is>
-          <t>無特別說明</t>
+          <t>格式瑕疵(含各式顏色標記)；逾2年未更新(10年未修，預計115提案)</t>
         </is>
       </c>
     </row>
@@ -6166,7 +6322,11 @@
           <t>研究暨產學發展處</t>
         </is>
       </c>
-      <c r="J7" s="38" t="n"/>
+      <c r="J7" s="38" t="inlineStr">
+        <is>
+          <t>114.3.19</t>
+        </is>
+      </c>
       <c r="K7" s="38" t="inlineStr">
         <is>
           <t>無特別說明</t>
@@ -6204,12 +6364,12 @@
       </c>
       <c r="G8" s="97" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>V</t>
         </is>
       </c>
       <c r="H8" s="97" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>V</t>
         </is>
       </c>
       <c r="I8" s="38" t="inlineStr">
@@ -6217,10 +6377,14 @@
           <t>研究暨產學發展處</t>
         </is>
       </c>
-      <c r="J8" s="38" t="n"/>
+      <c r="J8" s="38" t="inlineStr">
+        <is>
+          <t>103.10.1</t>
+        </is>
+      </c>
       <c r="K8" s="38" t="inlineStr">
         <is>
-          <t>無特別說明</t>
+          <t>逾2年未更新(12年未修，預計115提案)；配合組織規程修訂(科技部→國家科學及技術委員會(國科會))</t>
         </is>
       </c>
     </row>
@@ -6427,7 +6591,7 @@
       </c>
       <c r="G4" s="97" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>V</t>
         </is>
       </c>
       <c r="H4" s="97" t="inlineStr">
@@ -6440,10 +6604,14 @@
           <t>護理學院</t>
         </is>
       </c>
-      <c r="J4" s="38" t="n"/>
+      <c r="J4" s="38" t="inlineStr">
+        <is>
+          <t>108.2.20</t>
+        </is>
+      </c>
       <c r="K4" s="38" t="inlineStr">
         <is>
-          <t>無特別說明</t>
+          <t>逾2年未更新(7年未修，預計115提案)</t>
         </is>
       </c>
     </row>
@@ -6647,7 +6815,7 @@
       </c>
       <c r="G4" s="97" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>V</t>
         </is>
       </c>
       <c r="H4" s="97" t="inlineStr">
@@ -6660,10 +6828,14 @@
           <t>教務處</t>
         </is>
       </c>
-      <c r="J4" s="38" t="n"/>
+      <c r="J4" s="38" t="inlineStr">
+        <is>
+          <t>111.12.28</t>
+        </is>
+      </c>
       <c r="K4" s="38" t="inlineStr">
         <is>
-          <t>無特別說明</t>
+          <t>逾2年未更新(4年未修，預計115提案)</t>
         </is>
       </c>
     </row>
@@ -6698,7 +6870,7 @@
       </c>
       <c r="G5" s="97" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>V</t>
         </is>
       </c>
       <c r="H5" s="97" t="inlineStr">
@@ -6714,7 +6886,7 @@
       <c r="J5" s="38" t="n"/>
       <c r="K5" s="38" t="inlineStr">
         <is>
-          <t>無特別說明</t>
+          <t>逾2年未更新(多年未修，預計115提案)</t>
         </is>
       </c>
     </row>
@@ -6762,7 +6934,11 @@
           <t>教務處</t>
         </is>
       </c>
-      <c r="J6" s="38" t="n"/>
+      <c r="J6" s="38" t="inlineStr">
+        <is>
+          <t>113.2.15</t>
+        </is>
+      </c>
       <c r="K6" s="38" t="inlineStr">
         <is>
           <t>無特別說明</t>
@@ -6800,7 +6976,7 @@
       </c>
       <c r="G7" s="97" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>V</t>
         </is>
       </c>
       <c r="H7" s="97" t="inlineStr">
@@ -6813,10 +6989,14 @@
           <t>教務處</t>
         </is>
       </c>
-      <c r="J7" s="38" t="n"/>
+      <c r="J7" s="38" t="inlineStr">
+        <is>
+          <t>111.12.22</t>
+        </is>
+      </c>
       <c r="K7" s="38" t="inlineStr">
         <is>
-          <t>無特別說明</t>
+          <t>逾2年未更新(4年未修，預計115提案)</t>
         </is>
       </c>
     </row>
@@ -6851,7 +7031,7 @@
       </c>
       <c r="G8" s="97" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>V</t>
         </is>
       </c>
       <c r="H8" s="97" t="inlineStr">
@@ -6864,10 +7044,14 @@
           <t>教務處</t>
         </is>
       </c>
-      <c r="J8" s="38" t="n"/>
+      <c r="J8" s="38" t="inlineStr">
+        <is>
+          <t>112.11.29</t>
+        </is>
+      </c>
       <c r="K8" s="38" t="inlineStr">
         <is>
-          <t>無特別說明</t>
+          <t>逾2年未更新(3年未修，預計115提案)</t>
         </is>
       </c>
     </row>
@@ -6902,7 +7086,7 @@
       </c>
       <c r="G9" s="97" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>V</t>
         </is>
       </c>
       <c r="H9" s="97" t="inlineStr">
@@ -6915,10 +7099,14 @@
           <t>教務處</t>
         </is>
       </c>
-      <c r="J9" s="38" t="n"/>
+      <c r="J9" s="38" t="inlineStr">
+        <is>
+          <t>109.3.5</t>
+        </is>
+      </c>
       <c r="K9" s="38" t="inlineStr">
         <is>
-          <t>無特別說明</t>
+          <t>逾2年未更新(6年未修，預計115提案)</t>
         </is>
       </c>
     </row>
@@ -6966,7 +7154,11 @@
           <t>教務處</t>
         </is>
       </c>
-      <c r="J10" s="38" t="n"/>
+      <c r="J10" s="38" t="inlineStr">
+        <is>
+          <t>114.3.20</t>
+        </is>
+      </c>
       <c r="K10" s="38" t="inlineStr">
         <is>
           <t>無特別說明</t>
@@ -7004,7 +7196,7 @@
       </c>
       <c r="G11" s="97" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>V</t>
         </is>
       </c>
       <c r="H11" s="97" t="inlineStr">
@@ -7017,10 +7209,14 @@
           <t>教務處</t>
         </is>
       </c>
-      <c r="J11" s="38" t="n"/>
+      <c r="J11" s="38" t="inlineStr">
+        <is>
+          <t>104.9.30</t>
+        </is>
+      </c>
       <c r="K11" s="38" t="inlineStr">
         <is>
-          <t>無特別說明</t>
+          <t>逾2年未更新(11年未修，預計115提案)</t>
         </is>
       </c>
     </row>
@@ -7068,7 +7264,11 @@
           <t>教務處</t>
         </is>
       </c>
-      <c r="J12" s="38" t="n"/>
+      <c r="J12" s="38" t="inlineStr">
+        <is>
+          <t>115.1.15</t>
+        </is>
+      </c>
       <c r="K12" s="38" t="inlineStr">
         <is>
           <t>無特別說明</t>
@@ -7119,7 +7319,11 @@
           <t>教務處</t>
         </is>
       </c>
-      <c r="J13" s="38" t="n"/>
+      <c r="J13" s="38" t="inlineStr">
+        <is>
+          <t>115.4.2</t>
+        </is>
+      </c>
       <c r="K13" s="38" t="inlineStr">
         <is>
           <t>無特別說明</t>
@@ -7157,7 +7361,7 @@
       </c>
       <c r="G14" s="97" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>V</t>
         </is>
       </c>
       <c r="H14" s="97" t="inlineStr">
@@ -7170,10 +7374,14 @@
           <t>教務處</t>
         </is>
       </c>
-      <c r="J14" s="38" t="n"/>
+      <c r="J14" s="38" t="inlineStr">
+        <is>
+          <t>109.3.5</t>
+        </is>
+      </c>
       <c r="K14" s="38" t="inlineStr">
         <is>
-          <t>無特別說明</t>
+          <t>逾2年未更新(6年未修，預計115提案)</t>
         </is>
       </c>
     </row>
@@ -7221,7 +7429,11 @@
           <t>教務處</t>
         </is>
       </c>
-      <c r="J15" s="38" t="n"/>
+      <c r="J15" s="38" t="inlineStr">
+        <is>
+          <t>115.6.3</t>
+        </is>
+      </c>
       <c r="K15" s="38" t="inlineStr">
         <is>
           <t>無特別說明</t>
@@ -7259,7 +7471,7 @@
       </c>
       <c r="G16" s="97" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>V</t>
         </is>
       </c>
       <c r="H16" s="97" t="inlineStr">
@@ -7272,10 +7484,14 @@
           <t>教務處</t>
         </is>
       </c>
-      <c r="J16" s="38" t="n"/>
+      <c r="J16" s="38" t="inlineStr">
+        <is>
+          <t>100.7.8</t>
+        </is>
+      </c>
       <c r="K16" s="38" t="inlineStr">
         <is>
-          <t>無特別說明</t>
+          <t>逾2年未更新(15年未修，預計115提案)</t>
         </is>
       </c>
     </row>
@@ -7323,7 +7539,11 @@
           <t>教務處</t>
         </is>
       </c>
-      <c r="J17" s="38" t="n"/>
+      <c r="J17" s="38" t="inlineStr">
+        <is>
+          <t>113.3.14</t>
+        </is>
+      </c>
       <c r="K17" s="38" t="inlineStr">
         <is>
           <t>無特別說明</t>
@@ -7374,7 +7594,11 @@
           <t>教務處</t>
         </is>
       </c>
-      <c r="J18" s="38" t="n"/>
+      <c r="J18" s="38" t="inlineStr">
+        <is>
+          <t>114.4.30</t>
+        </is>
+      </c>
       <c r="K18" s="38" t="inlineStr">
         <is>
           <t>無特別說明</t>
@@ -7425,7 +7649,11 @@
           <t>教務處</t>
         </is>
       </c>
-      <c r="J19" s="38" t="n"/>
+      <c r="J19" s="38" t="inlineStr">
+        <is>
+          <t>114.10.22</t>
+        </is>
+      </c>
       <c r="K19" s="38" t="inlineStr">
         <is>
           <t>無特別說明</t>
@@ -7476,7 +7704,11 @@
           <t>教務處</t>
         </is>
       </c>
-      <c r="J20" s="38" t="n"/>
+      <c r="J20" s="38" t="inlineStr">
+        <is>
+          <t>114.6.12</t>
+        </is>
+      </c>
       <c r="K20" s="38" t="inlineStr">
         <is>
           <t>無特別說明</t>
@@ -7514,7 +7746,7 @@
       </c>
       <c r="G21" s="97" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>V</t>
         </is>
       </c>
       <c r="H21" s="97" t="inlineStr">
@@ -7527,10 +7759,14 @@
           <t>教務處</t>
         </is>
       </c>
-      <c r="J21" s="38" t="n"/>
+      <c r="J21" s="38" t="inlineStr">
+        <is>
+          <t>110.10.7</t>
+        </is>
+      </c>
       <c r="K21" s="38" t="inlineStr">
         <is>
-          <t>無特別說明</t>
+          <t>逾2年未更新(5年未修，預計115提案)</t>
         </is>
       </c>
     </row>
@@ -7578,7 +7814,11 @@
           <t>教務處</t>
         </is>
       </c>
-      <c r="J22" s="38" t="n"/>
+      <c r="J22" s="38" t="inlineStr">
+        <is>
+          <t>113.10.17</t>
+        </is>
+      </c>
       <c r="K22" s="38" t="inlineStr">
         <is>
           <t>無特別說明</t>
@@ -7629,7 +7869,11 @@
           <t>教務處</t>
         </is>
       </c>
-      <c r="J23" s="38" t="n"/>
+      <c r="J23" s="38" t="inlineStr">
+        <is>
+          <t>115.1.15</t>
+        </is>
+      </c>
       <c r="K23" s="38" t="inlineStr">
         <is>
           <t>無特別說明</t>
@@ -7680,7 +7924,11 @@
           <t>教務處</t>
         </is>
       </c>
-      <c r="J24" s="38" t="n"/>
+      <c r="J24" s="38" t="inlineStr">
+        <is>
+          <t>114.11.19</t>
+        </is>
+      </c>
       <c r="K24" s="38" t="inlineStr">
         <is>
           <t>無特別說明</t>
@@ -7718,7 +7966,7 @@
       </c>
       <c r="G25" s="97" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>V</t>
         </is>
       </c>
       <c r="H25" s="97" t="inlineStr">
@@ -7731,10 +7979,14 @@
           <t>教務處</t>
         </is>
       </c>
-      <c r="J25" s="38" t="n"/>
+      <c r="J25" s="38" t="inlineStr">
+        <is>
+          <t>104.9.30</t>
+        </is>
+      </c>
       <c r="K25" s="38" t="inlineStr">
         <is>
-          <t>無特別說明</t>
+          <t>逾2年未更新(11年未修，預計115提案)</t>
         </is>
       </c>
     </row>
@@ -7782,7 +8034,11 @@
           <t>教務處</t>
         </is>
       </c>
-      <c r="J26" s="38" t="n"/>
+      <c r="J26" s="38" t="inlineStr">
+        <is>
+          <t>114.1.9</t>
+        </is>
+      </c>
       <c r="K26" s="38" t="inlineStr">
         <is>
           <t>無特別說明</t>
@@ -7833,7 +8089,11 @@
           <t>教務處</t>
         </is>
       </c>
-      <c r="J27" s="38" t="n"/>
+      <c r="J27" s="38" t="inlineStr">
+        <is>
+          <t>113.10.17</t>
+        </is>
+      </c>
       <c r="K27" s="38" t="inlineStr">
         <is>
           <t>無特別說明</t>
@@ -7884,7 +8144,11 @@
           <t>教務處</t>
         </is>
       </c>
-      <c r="J28" s="38" t="n"/>
+      <c r="J28" s="38" t="inlineStr">
+        <is>
+          <t>114.10.16</t>
+        </is>
+      </c>
       <c r="K28" s="38" t="inlineStr">
         <is>
           <t>無特別說明</t>
@@ -7917,12 +8181,12 @@
       </c>
       <c r="F29" s="97" t="inlineStr">
         <is>
-          <t>V</t>
+          <t>X</t>
         </is>
       </c>
       <c r="G29" s="97" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>V</t>
         </is>
       </c>
       <c r="H29" s="97" t="inlineStr">
@@ -7935,10 +8199,14 @@
           <t>教務處</t>
         </is>
       </c>
-      <c r="J29" s="38" t="n"/>
+      <c r="J29" s="38" t="inlineStr">
+        <is>
+          <t>110.10.20</t>
+        </is>
+      </c>
       <c r="K29" s="38" t="inlineStr">
         <is>
-          <t>無特別說明</t>
+          <t>格式瑕疵(含各式顏色標記)；逾2年未更新(5年未修，預計115提案)</t>
         </is>
       </c>
     </row>
@@ -7986,7 +8254,11 @@
           <t>教務處</t>
         </is>
       </c>
-      <c r="J30" s="38" t="n"/>
+      <c r="J30" s="38" t="inlineStr">
+        <is>
+          <t>113.6.13</t>
+        </is>
+      </c>
       <c r="K30" s="38" t="inlineStr">
         <is>
           <t>無特別說明</t>
@@ -8037,7 +8309,11 @@
           <t>教務處</t>
         </is>
       </c>
-      <c r="J31" s="38" t="n"/>
+      <c r="J31" s="38" t="inlineStr">
+        <is>
+          <t>114.1.9</t>
+        </is>
+      </c>
       <c r="K31" s="38" t="inlineStr">
         <is>
           <t>無特別說明</t>
@@ -8070,7 +8346,7 @@
       </c>
       <c r="F32" s="97" t="inlineStr">
         <is>
-          <t>V</t>
+          <t>X</t>
         </is>
       </c>
       <c r="G32" s="97" t="inlineStr">
@@ -8088,10 +8364,14 @@
           <t>教務處</t>
         </is>
       </c>
-      <c r="J32" s="38" t="n"/>
+      <c r="J32" s="38" t="inlineStr">
+        <is>
+          <t>114.12.3</t>
+        </is>
+      </c>
       <c r="K32" s="38" t="inlineStr">
         <is>
-          <t>無特別說明</t>
+          <t>格式瑕疵(含各式顏色標記)</t>
         </is>
       </c>
     </row>
@@ -8121,12 +8401,12 @@
       </c>
       <c r="F33" s="97" t="inlineStr">
         <is>
-          <t>V</t>
+          <t>X</t>
         </is>
       </c>
       <c r="G33" s="97" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>V</t>
         </is>
       </c>
       <c r="H33" s="97" t="inlineStr">
@@ -8139,10 +8419,14 @@
           <t>教務處</t>
         </is>
       </c>
-      <c r="J33" s="38" t="n"/>
+      <c r="J33" s="38" t="inlineStr">
+        <is>
+          <t>112.5.10</t>
+        </is>
+      </c>
       <c r="K33" s="38" t="inlineStr">
         <is>
-          <t>無特別說明</t>
+          <t>格式瑕疵(含各式顏色標記)；逾2年未更新(3年未修，預計115提案)</t>
         </is>
       </c>
     </row>
@@ -8172,7 +8456,7 @@
       </c>
       <c r="F34" s="97" t="inlineStr">
         <is>
-          <t>V</t>
+          <t>X</t>
         </is>
       </c>
       <c r="G34" s="97" t="inlineStr">
@@ -8190,10 +8474,14 @@
           <t>教務處</t>
         </is>
       </c>
-      <c r="J34" s="38" t="n"/>
+      <c r="J34" s="38" t="inlineStr">
+        <is>
+          <t>115.3.5</t>
+        </is>
+      </c>
       <c r="K34" s="38" t="inlineStr">
         <is>
-          <t>無特別說明</t>
+          <t>格式瑕疵(含各式顏色標記)</t>
         </is>
       </c>
     </row>
@@ -8228,7 +8516,7 @@
       </c>
       <c r="G35" s="97" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>V</t>
         </is>
       </c>
       <c r="H35" s="97" t="inlineStr">
@@ -8241,10 +8529,14 @@
           <t>教務處</t>
         </is>
       </c>
-      <c r="J35" s="38" t="n"/>
+      <c r="J35" s="38" t="inlineStr">
+        <is>
+          <t>105.7.26</t>
+        </is>
+      </c>
       <c r="K35" s="38" t="inlineStr">
         <is>
-          <t>無特別說明</t>
+          <t>逾2年未更新(10年未修，預計115提案)</t>
         </is>
       </c>
     </row>
@@ -8279,7 +8571,7 @@
       </c>
       <c r="G36" s="97" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>V</t>
         </is>
       </c>
       <c r="H36" s="97" t="inlineStr">
@@ -8292,10 +8584,14 @@
           <t>教務處</t>
         </is>
       </c>
-      <c r="J36" s="38" t="n"/>
+      <c r="J36" s="38" t="inlineStr">
+        <is>
+          <t>112.11.29</t>
+        </is>
+      </c>
       <c r="K36" s="38" t="inlineStr">
         <is>
-          <t>無特別說明</t>
+          <t>逾2年未更新(3年未修，預計115提案)</t>
         </is>
       </c>
     </row>
@@ -8330,7 +8626,7 @@
       </c>
       <c r="G37" s="97" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>V</t>
         </is>
       </c>
       <c r="H37" s="97" t="inlineStr">
@@ -8343,10 +8639,14 @@
           <t>教務處</t>
         </is>
       </c>
-      <c r="J37" s="38" t="n"/>
+      <c r="J37" s="38" t="inlineStr">
+        <is>
+          <t>103.1.22</t>
+        </is>
+      </c>
       <c r="K37" s="38" t="inlineStr">
         <is>
-          <t>無特別說明</t>
+          <t>逾2年未更新(12年未修，預計115提案)</t>
         </is>
       </c>
     </row>
@@ -8394,7 +8694,11 @@
           <t>教務處</t>
         </is>
       </c>
-      <c r="J38" s="38" t="n"/>
+      <c r="J38" s="38" t="inlineStr">
+        <is>
+          <t>115.1.15</t>
+        </is>
+      </c>
       <c r="K38" s="38" t="inlineStr">
         <is>
           <t>無特別說明</t>
@@ -8432,7 +8736,7 @@
       </c>
       <c r="G39" s="97" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>V</t>
         </is>
       </c>
       <c r="H39" s="97" t="inlineStr">
@@ -8445,10 +8749,14 @@
           <t>教務處</t>
         </is>
       </c>
-      <c r="J39" s="38" t="n"/>
+      <c r="J39" s="38" t="inlineStr">
+        <is>
+          <t>105.4.29</t>
+        </is>
+      </c>
       <c r="K39" s="38" t="inlineStr">
         <is>
-          <t>無特別說明</t>
+          <t>逾2年未更新(10年未修，預計115提案)</t>
         </is>
       </c>
     </row>
@@ -8478,7 +8786,7 @@
       </c>
       <c r="F40" s="97" t="inlineStr">
         <is>
-          <t>V</t>
+          <t>X</t>
         </is>
       </c>
       <c r="G40" s="97" t="inlineStr">
@@ -8496,10 +8804,14 @@
           <t>教務處</t>
         </is>
       </c>
-      <c r="J40" s="38" t="n"/>
+      <c r="J40" s="38" t="inlineStr">
+        <is>
+          <t>114.9.3</t>
+        </is>
+      </c>
       <c r="K40" s="38" t="inlineStr">
         <is>
-          <t>無特別說明</t>
+          <t>格式瑕疵(含各式顏色標記)</t>
         </is>
       </c>
     </row>
@@ -8529,12 +8841,12 @@
       </c>
       <c r="F41" s="97" t="inlineStr">
         <is>
-          <t>V</t>
+          <t>X</t>
         </is>
       </c>
       <c r="G41" s="97" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>V</t>
         </is>
       </c>
       <c r="H41" s="97" t="inlineStr">
@@ -8547,10 +8859,14 @@
           <t>教務處</t>
         </is>
       </c>
-      <c r="J41" s="38" t="n"/>
+      <c r="J41" s="38" t="inlineStr">
+        <is>
+          <t>111.6.16</t>
+        </is>
+      </c>
       <c r="K41" s="38" t="inlineStr">
         <is>
-          <t>無特別說明</t>
+          <t>格式瑕疵(含各式顏色標記)；逾2年未更新(4年未修，預計115提案)</t>
         </is>
       </c>
     </row>
@@ -8580,12 +8896,12 @@
       </c>
       <c r="F42" s="97" t="inlineStr">
         <is>
-          <t>V</t>
+          <t>X</t>
         </is>
       </c>
       <c r="G42" s="97" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>V</t>
         </is>
       </c>
       <c r="H42" s="97" t="inlineStr">
@@ -8598,10 +8914,14 @@
           <t>教務處</t>
         </is>
       </c>
-      <c r="J42" s="38" t="n"/>
+      <c r="J42" s="38" t="inlineStr">
+        <is>
+          <t>110.6.16</t>
+        </is>
+      </c>
       <c r="K42" s="38" t="inlineStr">
         <is>
-          <t>無特別說明</t>
+          <t>格式瑕疵(含各式顏色標記)；逾2年未更新(5年未修，預計115提案)</t>
         </is>
       </c>
     </row>
@@ -8631,12 +8951,12 @@
       </c>
       <c r="F43" s="97" t="inlineStr">
         <is>
-          <t>V</t>
+          <t>X</t>
         </is>
       </c>
       <c r="G43" s="97" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>V</t>
         </is>
       </c>
       <c r="H43" s="97" t="inlineStr">
@@ -8649,10 +8969,14 @@
           <t>教務處</t>
         </is>
       </c>
-      <c r="J43" s="38" t="n"/>
+      <c r="J43" s="38" t="inlineStr">
+        <is>
+          <t>108.6.12</t>
+        </is>
+      </c>
       <c r="K43" s="38" t="inlineStr">
         <is>
-          <t>無特別說明</t>
+          <t>格式瑕疵(含各式顏色標記)；逾2年未更新(7年未修，預計115提案)</t>
         </is>
       </c>
     </row>
@@ -8700,7 +9024,11 @@
           <t>教務處</t>
         </is>
       </c>
-      <c r="J44" s="38" t="n"/>
+      <c r="J44" s="38" t="inlineStr">
+        <is>
+          <t>115.4.2</t>
+        </is>
+      </c>
       <c r="K44" s="38" t="inlineStr">
         <is>
           <t>無特別說明</t>
@@ -8738,7 +9066,7 @@
       </c>
       <c r="G45" s="97" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>V</t>
         </is>
       </c>
       <c r="H45" s="97" t="inlineStr">
@@ -8751,10 +9079,14 @@
           <t>教務處</t>
         </is>
       </c>
-      <c r="J45" s="38" t="n"/>
+      <c r="J45" s="38" t="inlineStr">
+        <is>
+          <t>112.11.29</t>
+        </is>
+      </c>
       <c r="K45" s="38" t="inlineStr">
         <is>
-          <t>無特別說明</t>
+          <t>逾2年未更新(3年未修，預計115提案)</t>
         </is>
       </c>
     </row>
@@ -8784,12 +9116,12 @@
       </c>
       <c r="F46" s="97" t="inlineStr">
         <is>
-          <t>V</t>
+          <t>X</t>
         </is>
       </c>
       <c r="G46" s="97" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>V</t>
         </is>
       </c>
       <c r="H46" s="97" t="inlineStr">
@@ -8802,10 +9134,14 @@
           <t>教務處</t>
         </is>
       </c>
-      <c r="J46" s="38" t="n"/>
+      <c r="J46" s="38" t="inlineStr">
+        <is>
+          <t>110.6.24</t>
+        </is>
+      </c>
       <c r="K46" s="38" t="inlineStr">
         <is>
-          <t>無特別說明</t>
+          <t>格式瑕疵(含各式顏色標記)；逾2年未更新(5年未修，預計115提案)</t>
         </is>
       </c>
     </row>
@@ -8853,7 +9189,11 @@
           <t>教務處</t>
         </is>
       </c>
-      <c r="J47" s="38" t="n"/>
+      <c r="J47" s="38" t="inlineStr">
+        <is>
+          <t>114.6.12</t>
+        </is>
+      </c>
       <c r="K47" s="38" t="inlineStr">
         <is>
           <t>無特別說明</t>
@@ -8891,7 +9231,7 @@
       </c>
       <c r="G48" s="97" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>V</t>
         </is>
       </c>
       <c r="H48" s="97" t="inlineStr">
@@ -8904,10 +9244,14 @@
           <t>教務處</t>
         </is>
       </c>
-      <c r="J48" s="38" t="n"/>
+      <c r="J48" s="38" t="inlineStr">
+        <is>
+          <t>111.10.6</t>
+        </is>
+      </c>
       <c r="K48" s="38" t="inlineStr">
         <is>
-          <t>無特別說明</t>
+          <t>逾2年未更新(4年未修，預計115提案)</t>
         </is>
       </c>
     </row>
@@ -8942,7 +9286,7 @@
       </c>
       <c r="G49" s="97" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>V</t>
         </is>
       </c>
       <c r="H49" s="97" t="inlineStr">
@@ -8955,10 +9299,14 @@
           <t>教務處</t>
         </is>
       </c>
-      <c r="J49" s="38" t="n"/>
+      <c r="J49" s="38" t="inlineStr">
+        <is>
+          <t>111.12.28</t>
+        </is>
+      </c>
       <c r="K49" s="38" t="inlineStr">
         <is>
-          <t>無特別說明</t>
+          <t>逾2年未更新(4年未修，預計115提案)</t>
         </is>
       </c>
     </row>
@@ -8993,7 +9341,7 @@
       </c>
       <c r="G50" s="97" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>V</t>
         </is>
       </c>
       <c r="H50" s="97" t="inlineStr">
@@ -9006,10 +9354,14 @@
           <t>教務處</t>
         </is>
       </c>
-      <c r="J50" s="38" t="n"/>
+      <c r="J50" s="38" t="inlineStr">
+        <is>
+          <t>112.5.10</t>
+        </is>
+      </c>
       <c r="K50" s="38" t="inlineStr">
         <is>
-          <t>無特別說明</t>
+          <t>逾2年未更新(3年未修，預計115提案)</t>
         </is>
       </c>
     </row>
@@ -9057,7 +9409,11 @@
           <t>教務處</t>
         </is>
       </c>
-      <c r="J51" s="38" t="n"/>
+      <c r="J51" s="38" t="inlineStr">
+        <is>
+          <t>113.2.15</t>
+        </is>
+      </c>
       <c r="K51" s="38" t="inlineStr">
         <is>
           <t>無特別說明</t>
@@ -9090,7 +9446,7 @@
       </c>
       <c r="F52" s="97" t="inlineStr">
         <is>
-          <t>V</t>
+          <t>X</t>
         </is>
       </c>
       <c r="G52" s="97" t="inlineStr">
@@ -9108,10 +9464,14 @@
           <t>教務處</t>
         </is>
       </c>
-      <c r="J52" s="38" t="n"/>
+      <c r="J52" s="38" t="inlineStr">
+        <is>
+          <t>114.9.3</t>
+        </is>
+      </c>
       <c r="K52" s="38" t="inlineStr">
         <is>
-          <t>無特別說明</t>
+          <t>格式瑕疵(含各式顏色標記)</t>
         </is>
       </c>
     </row>
@@ -9146,7 +9506,7 @@
       </c>
       <c r="G53" s="97" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>V</t>
         </is>
       </c>
       <c r="H53" s="97" t="inlineStr">
@@ -9159,10 +9519,14 @@
           <t>教務處</t>
         </is>
       </c>
-      <c r="J53" s="38" t="n"/>
+      <c r="J53" s="38" t="inlineStr">
+        <is>
+          <t>110.10.13</t>
+        </is>
+      </c>
       <c r="K53" s="38" t="inlineStr">
         <is>
-          <t>無特別說明</t>
+          <t>逾2年未更新(5年未修，預計115提案)</t>
         </is>
       </c>
     </row>
@@ -9192,12 +9556,12 @@
       </c>
       <c r="F54" s="97" t="inlineStr">
         <is>
-          <t>V</t>
+          <t>X</t>
         </is>
       </c>
       <c r="G54" s="97" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>V</t>
         </is>
       </c>
       <c r="H54" s="97" t="inlineStr">
@@ -9210,10 +9574,14 @@
           <t>教務處</t>
         </is>
       </c>
-      <c r="J54" s="38" t="n"/>
+      <c r="J54" s="38" t="inlineStr">
+        <is>
+          <t>110.9.27</t>
+        </is>
+      </c>
       <c r="K54" s="38" t="inlineStr">
         <is>
-          <t>無特別說明</t>
+          <t>格式瑕疵(含各式顏色標記)；逾2年未更新(5年未修，預計115提案)</t>
         </is>
       </c>
     </row>
@@ -9248,7 +9616,7 @@
       </c>
       <c r="G55" s="97" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>V</t>
         </is>
       </c>
       <c r="H55" s="97" t="inlineStr">
@@ -9261,10 +9629,14 @@
           <t>教務處</t>
         </is>
       </c>
-      <c r="J55" s="38" t="n"/>
+      <c r="J55" s="38" t="inlineStr">
+        <is>
+          <t>110.9.29</t>
+        </is>
+      </c>
       <c r="K55" s="38" t="inlineStr">
         <is>
-          <t>無特別說明</t>
+          <t>逾2年未更新(5年未修，預計115提案)</t>
         </is>
       </c>
     </row>
@@ -9312,7 +9684,11 @@
           <t>教務處</t>
         </is>
       </c>
-      <c r="J56" s="38" t="n"/>
+      <c r="J56" s="38" t="inlineStr">
+        <is>
+          <t>113.5.22</t>
+        </is>
+      </c>
       <c r="K56" s="38" t="inlineStr">
         <is>
           <t>無特別說明</t>
@@ -9345,7 +9721,7 @@
       </c>
       <c r="F57" s="97" t="inlineStr">
         <is>
-          <t>V</t>
+          <t>X</t>
         </is>
       </c>
       <c r="G57" s="97" t="inlineStr">
@@ -9363,10 +9739,14 @@
           <t>教務處</t>
         </is>
       </c>
-      <c r="J57" s="38" t="n"/>
+      <c r="J57" s="38" t="inlineStr">
+        <is>
+          <t>114.12.31</t>
+        </is>
+      </c>
       <c r="K57" s="38" t="inlineStr">
         <is>
-          <t>無特別說明</t>
+          <t>格式瑕疵(含各式顏色標記)</t>
         </is>
       </c>
     </row>
@@ -9401,7 +9781,7 @@
       </c>
       <c r="G58" s="97" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>V</t>
         </is>
       </c>
       <c r="H58" s="97" t="inlineStr">
@@ -9414,10 +9794,14 @@
           <t>教務處</t>
         </is>
       </c>
-      <c r="J58" s="38" t="n"/>
+      <c r="J58" s="38" t="inlineStr">
+        <is>
+          <t>110.9.14</t>
+        </is>
+      </c>
       <c r="K58" s="38" t="inlineStr">
         <is>
-          <t>無特別說明</t>
+          <t>逾2年未更新(5年未修，預計115提案)</t>
         </is>
       </c>
     </row>
@@ -9452,7 +9836,7 @@
       </c>
       <c r="G59" s="97" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>V</t>
         </is>
       </c>
       <c r="H59" s="97" t="inlineStr">
@@ -9465,10 +9849,14 @@
           <t>教務處</t>
         </is>
       </c>
-      <c r="J59" s="38" t="n"/>
+      <c r="J59" s="38" t="inlineStr">
+        <is>
+          <t>110.9.13</t>
+        </is>
+      </c>
       <c r="K59" s="38" t="inlineStr">
         <is>
-          <t>無特別說明</t>
+          <t>逾2年未更新(5年未修，預計115提案)</t>
         </is>
       </c>
     </row>
@@ -9503,7 +9891,7 @@
       </c>
       <c r="G60" s="97" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>V</t>
         </is>
       </c>
       <c r="H60" s="97" t="inlineStr">
@@ -9516,10 +9904,14 @@
           <t>教務處</t>
         </is>
       </c>
-      <c r="J60" s="38" t="n"/>
+      <c r="J60" s="38" t="inlineStr">
+        <is>
+          <t>110.10.5</t>
+        </is>
+      </c>
       <c r="K60" s="38" t="inlineStr">
         <is>
-          <t>無特別說明</t>
+          <t>逾2年未更新(5年未修，預計115提案)</t>
         </is>
       </c>
     </row>
@@ -9554,7 +9946,7 @@
       </c>
       <c r="G61" s="97" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>V</t>
         </is>
       </c>
       <c r="H61" s="97" t="inlineStr">
@@ -9567,10 +9959,14 @@
           <t>教務處</t>
         </is>
       </c>
-      <c r="J61" s="38" t="n"/>
+      <c r="J61" s="38" t="inlineStr">
+        <is>
+          <t>110.10.7</t>
+        </is>
+      </c>
       <c r="K61" s="38" t="inlineStr">
         <is>
-          <t>無特別說明</t>
+          <t>逾2年未更新(5年未修，預計115提案)</t>
         </is>
       </c>
     </row>
@@ -9605,7 +10001,7 @@
       </c>
       <c r="G62" s="97" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>V</t>
         </is>
       </c>
       <c r="H62" s="97" t="inlineStr">
@@ -9618,10 +10014,14 @@
           <t>教務處</t>
         </is>
       </c>
-      <c r="J62" s="38" t="n"/>
+      <c r="J62" s="38" t="inlineStr">
+        <is>
+          <t>110.9.28</t>
+        </is>
+      </c>
       <c r="K62" s="38" t="inlineStr">
         <is>
-          <t>無特別說明</t>
+          <t>逾2年未更新(5年未修，預計115提案)</t>
         </is>
       </c>
     </row>
@@ -9656,7 +10056,7 @@
       </c>
       <c r="G63" s="97" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>V</t>
         </is>
       </c>
       <c r="H63" s="97" t="inlineStr">
@@ -9669,10 +10069,14 @@
           <t>教務處</t>
         </is>
       </c>
-      <c r="J63" s="38" t="n"/>
+      <c r="J63" s="38" t="inlineStr">
+        <is>
+          <t>110.12.8</t>
+        </is>
+      </c>
       <c r="K63" s="38" t="inlineStr">
         <is>
-          <t>無特別說明</t>
+          <t>逾2年未更新(5年未修，預計115提案)</t>
         </is>
       </c>
     </row>
@@ -9720,7 +10124,11 @@
           <t>教務處</t>
         </is>
       </c>
-      <c r="J64" s="38" t="n"/>
+      <c r="J64" s="38" t="inlineStr">
+        <is>
+          <t>114.6.18</t>
+        </is>
+      </c>
       <c r="K64" s="38" t="inlineStr">
         <is>
           <t>無特別說明</t>
@@ -9758,7 +10166,7 @@
       </c>
       <c r="G65" s="97" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>V</t>
         </is>
       </c>
       <c r="H65" s="97" t="inlineStr">
@@ -9771,10 +10179,14 @@
           <t>教務處</t>
         </is>
       </c>
-      <c r="J65" s="38" t="n"/>
+      <c r="J65" s="38" t="inlineStr">
+        <is>
+          <t>104.5.18</t>
+        </is>
+      </c>
       <c r="K65" s="38" t="inlineStr">
         <is>
-          <t>無特別說明</t>
+          <t>逾2年未更新(11年未修，預計115提案)</t>
         </is>
       </c>
     </row>
@@ -9809,7 +10221,7 @@
       </c>
       <c r="G66" s="97" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>V</t>
         </is>
       </c>
       <c r="H66" s="97" t="inlineStr">
@@ -9822,10 +10234,14 @@
           <t>教務處</t>
         </is>
       </c>
-      <c r="J66" s="38" t="n"/>
+      <c r="J66" s="38" t="inlineStr">
+        <is>
+          <t>112.10.12</t>
+        </is>
+      </c>
       <c r="K66" s="38" t="inlineStr">
         <is>
-          <t>無特別說明</t>
+          <t>逾2年未更新(3年未修，預計115提案)</t>
         </is>
       </c>
     </row>
@@ -9873,7 +10289,11 @@
           <t>教務處</t>
         </is>
       </c>
-      <c r="J67" s="38" t="n"/>
+      <c r="J67" s="38" t="inlineStr">
+        <is>
+          <t>113.7.9</t>
+        </is>
+      </c>
       <c r="K67" s="38" t="inlineStr">
         <is>
           <t>無特別說明</t>
@@ -9924,7 +10344,11 @@
           <t>教務處</t>
         </is>
       </c>
-      <c r="J68" s="38" t="n"/>
+      <c r="J68" s="38" t="inlineStr">
+        <is>
+          <t>114.7.15</t>
+        </is>
+      </c>
       <c r="K68" s="38" t="inlineStr">
         <is>
           <t>無特別說明</t>
@@ -9975,7 +10399,11 @@
           <t>教務處</t>
         </is>
       </c>
-      <c r="J69" s="38" t="n"/>
+      <c r="J69" s="38" t="inlineStr">
+        <is>
+          <t>115.3.27</t>
+        </is>
+      </c>
       <c r="K69" s="38" t="inlineStr">
         <is>
           <t>無特別說明</t>
@@ -10013,7 +10441,7 @@
       </c>
       <c r="G70" s="97" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>V</t>
         </is>
       </c>
       <c r="H70" s="97" t="inlineStr">
@@ -10026,10 +10454,14 @@
           <t>教務處</t>
         </is>
       </c>
-      <c r="J70" s="38" t="n"/>
+      <c r="J70" s="38" t="inlineStr">
+        <is>
+          <t>112.10.25</t>
+        </is>
+      </c>
       <c r="K70" s="38" t="inlineStr">
         <is>
-          <t>無特別說明</t>
+          <t>逾2年未更新(3年未修，預計115提案)</t>
         </is>
       </c>
     </row>
@@ -10064,7 +10496,7 @@
       </c>
       <c r="G71" s="97" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>V</t>
         </is>
       </c>
       <c r="H71" s="97" t="inlineStr">
@@ -10077,10 +10509,14 @@
           <t>教務處</t>
         </is>
       </c>
-      <c r="J71" s="38" t="n"/>
+      <c r="J71" s="38" t="inlineStr">
+        <is>
+          <t>112.10.12</t>
+        </is>
+      </c>
       <c r="K71" s="38" t="inlineStr">
         <is>
-          <t>無特別說明</t>
+          <t>逾2年未更新(3年未修，預計115提案)</t>
         </is>
       </c>
     </row>
@@ -10115,7 +10551,7 @@
       </c>
       <c r="G72" s="97" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>V</t>
         </is>
       </c>
       <c r="H72" s="97" t="inlineStr">
@@ -10128,10 +10564,14 @@
           <t>教務處</t>
         </is>
       </c>
-      <c r="J72" s="38" t="n"/>
+      <c r="J72" s="38" t="inlineStr">
+        <is>
+          <t>111.11.24</t>
+        </is>
+      </c>
       <c r="K72" s="38" t="inlineStr">
         <is>
-          <t>無特別說明</t>
+          <t>逾2年未更新(4年未修，預計115提案)</t>
         </is>
       </c>
     </row>
@@ -10166,7 +10606,7 @@
       </c>
       <c r="G73" s="97" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>V</t>
         </is>
       </c>
       <c r="H73" s="97" t="inlineStr">
@@ -10179,10 +10619,14 @@
           <t>教務處</t>
         </is>
       </c>
-      <c r="J73" s="38" t="n"/>
+      <c r="J73" s="38" t="inlineStr">
+        <is>
+          <t>110.3.11</t>
+        </is>
+      </c>
       <c r="K73" s="38" t="inlineStr">
         <is>
-          <t>無特別說明</t>
+          <t>逾2年未更新(5年未修，預計115提案)</t>
         </is>
       </c>
     </row>
@@ -10217,7 +10661,7 @@
       </c>
       <c r="G74" s="97" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>V</t>
         </is>
       </c>
       <c r="H74" s="97" t="inlineStr">
@@ -10230,10 +10674,14 @@
           <t>教務處</t>
         </is>
       </c>
-      <c r="J74" s="38" t="n"/>
+      <c r="J74" s="38" t="inlineStr">
+        <is>
+          <t>112.10.25</t>
+        </is>
+      </c>
       <c r="K74" s="38" t="inlineStr">
         <is>
-          <t>無特別說明</t>
+          <t>逾2年未更新(3年未修，預計115提案)</t>
         </is>
       </c>
     </row>
@@ -10263,7 +10711,7 @@
       </c>
       <c r="F75" s="97" t="inlineStr">
         <is>
-          <t>V</t>
+          <t>X</t>
         </is>
       </c>
       <c r="G75" s="97" t="inlineStr">
@@ -10281,10 +10729,14 @@
           <t>教務處</t>
         </is>
       </c>
-      <c r="J75" s="38" t="n"/>
+      <c r="J75" s="38" t="inlineStr">
+        <is>
+          <t>115.1.7</t>
+        </is>
+      </c>
       <c r="K75" s="38" t="inlineStr">
         <is>
-          <t>無特別說明</t>
+          <t>格式瑕疵(含各式顏色標記)</t>
         </is>
       </c>
     </row>
@@ -10332,7 +10784,11 @@
           <t>教務處</t>
         </is>
       </c>
-      <c r="J76" s="38" t="n"/>
+      <c r="J76" s="38" t="inlineStr">
+        <is>
+          <t>113.4.3</t>
+        </is>
+      </c>
       <c r="K76" s="38" t="inlineStr">
         <is>
           <t>無特別說明</t>
@@ -10383,7 +10839,11 @@
           <t>教務處</t>
         </is>
       </c>
-      <c r="J77" s="38" t="n"/>
+      <c r="J77" s="38" t="inlineStr">
+        <is>
+          <t>115.6.11</t>
+        </is>
+      </c>
       <c r="K77" s="38" t="inlineStr">
         <is>
           <t>無特別說明</t>
@@ -10421,7 +10881,7 @@
       </c>
       <c r="G78" s="97" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>V</t>
         </is>
       </c>
       <c r="H78" s="97" t="inlineStr">
@@ -10434,10 +10894,14 @@
           <t>教務處</t>
         </is>
       </c>
-      <c r="J78" s="38" t="n"/>
+      <c r="J78" s="38" t="inlineStr">
+        <is>
+          <t>111.9.29</t>
+        </is>
+      </c>
       <c r="K78" s="38" t="inlineStr">
         <is>
-          <t>無特別說明</t>
+          <t>逾2年未更新(4年未修，預計115提案)</t>
         </is>
       </c>
     </row>
@@ -10485,7 +10949,11 @@
           <t>教務處</t>
         </is>
       </c>
-      <c r="J79" s="38" t="n"/>
+      <c r="J79" s="38" t="inlineStr">
+        <is>
+          <t>115.4.2</t>
+        </is>
+      </c>
       <c r="K79" s="38" t="inlineStr">
         <is>
           <t>無特別說明</t>
@@ -10536,7 +11004,11 @@
           <t>教務處</t>
         </is>
       </c>
-      <c r="J80" s="38" t="n"/>
+      <c r="J80" s="38" t="inlineStr">
+        <is>
+          <t>115.6.3</t>
+        </is>
+      </c>
       <c r="K80" s="38" t="inlineStr">
         <is>
           <t>無特別說明</t>
@@ -10569,7 +11041,7 @@
       </c>
       <c r="F81" s="97" t="inlineStr">
         <is>
-          <t>V</t>
+          <t>X</t>
         </is>
       </c>
       <c r="G81" s="97" t="inlineStr">
@@ -10587,10 +11059,14 @@
           <t>教務處</t>
         </is>
       </c>
-      <c r="J81" s="38" t="n"/>
+      <c r="J81" s="38" t="inlineStr">
+        <is>
+          <t>114.6.18</t>
+        </is>
+      </c>
       <c r="K81" s="38" t="inlineStr">
         <is>
-          <t>無特別說明</t>
+          <t>格式瑕疵(含各式顏色標記)</t>
         </is>
       </c>
     </row>
@@ -10638,7 +11114,11 @@
           <t>教務處</t>
         </is>
       </c>
-      <c r="J82" s="38" t="n"/>
+      <c r="J82" s="38" t="inlineStr">
+        <is>
+          <t>115.6.24</t>
+        </is>
+      </c>
       <c r="K82" s="38" t="inlineStr">
         <is>
           <t>無特別說明</t>
@@ -10689,7 +11169,11 @@
           <t>教務處</t>
         </is>
       </c>
-      <c r="J83" s="38" t="n"/>
+      <c r="J83" s="38" t="inlineStr">
+        <is>
+          <t>113.3.14</t>
+        </is>
+      </c>
       <c r="K83" s="38" t="inlineStr">
         <is>
           <t>無特別說明</t>
@@ -10740,7 +11224,11 @@
           <t>教務處</t>
         </is>
       </c>
-      <c r="J84" s="38" t="n"/>
+      <c r="J84" s="38" t="inlineStr">
+        <is>
+          <t>115.6.3</t>
+        </is>
+      </c>
       <c r="K84" s="38" t="inlineStr">
         <is>
           <t>無特別說明</t>
@@ -10791,7 +11279,11 @@
           <t>教務處</t>
         </is>
       </c>
-      <c r="J85" s="38" t="n"/>
+      <c r="J85" s="38" t="inlineStr">
+        <is>
+          <t>115.2.25</t>
+        </is>
+      </c>
       <c r="K85" s="38" t="inlineStr">
         <is>
           <t>無特別說明</t>
@@ -10842,7 +11334,11 @@
           <t>教務處</t>
         </is>
       </c>
-      <c r="J86" s="38" t="n"/>
+      <c r="J86" s="38" t="inlineStr">
+        <is>
+          <t>114.12.31</t>
+        </is>
+      </c>
       <c r="K86" s="38" t="inlineStr">
         <is>
           <t>無特別說明</t>
@@ -10880,7 +11376,7 @@
       </c>
       <c r="G87" s="97" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>V</t>
         </is>
       </c>
       <c r="H87" s="97" t="inlineStr">
@@ -10893,10 +11389,14 @@
           <t>教務處</t>
         </is>
       </c>
-      <c r="J87" s="38" t="n"/>
+      <c r="J87" s="38" t="inlineStr">
+        <is>
+          <t>112.2.8</t>
+        </is>
+      </c>
       <c r="K87" s="38" t="inlineStr">
         <is>
-          <t>無特別說明</t>
+          <t>逾2年未更新(3年未修，預計115提案)</t>
         </is>
       </c>
     </row>
@@ -10931,7 +11431,7 @@
       </c>
       <c r="G88" s="97" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>V</t>
         </is>
       </c>
       <c r="H88" s="97" t="inlineStr">
@@ -10944,10 +11444,14 @@
           <t>教務處</t>
         </is>
       </c>
-      <c r="J88" s="38" t="n"/>
+      <c r="J88" s="38" t="inlineStr">
+        <is>
+          <t>112.10.12</t>
+        </is>
+      </c>
       <c r="K88" s="38" t="inlineStr">
         <is>
-          <t>無特別說明</t>
+          <t>逾2年未更新(3年未修，預計115提案)</t>
         </is>
       </c>
     </row>
@@ -11140,7 +11644,7 @@
       </c>
       <c r="G4" s="97" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>V</t>
         </is>
       </c>
       <c r="H4" s="97" t="inlineStr">
@@ -11153,10 +11657,14 @@
           <t>幼兒保育暨產業系</t>
         </is>
       </c>
-      <c r="J4" s="38" t="n"/>
+      <c r="J4" s="38" t="inlineStr">
+        <is>
+          <t>106.9.28</t>
+        </is>
+      </c>
       <c r="K4" s="38" t="inlineStr">
         <is>
-          <t>無特別說明</t>
+          <t>逾2年未更新(9年未修，預計115提案)</t>
         </is>
       </c>
     </row>
@@ -11346,7 +11854,7 @@
       </c>
       <c r="G4" s="97" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>V</t>
         </is>
       </c>
       <c r="H4" s="97" t="inlineStr">
@@ -11359,10 +11867,14 @@
           <t>健康美容系</t>
         </is>
       </c>
-      <c r="J4" s="38" t="n"/>
+      <c r="J4" s="38" t="inlineStr">
+        <is>
+          <t>108.9.25</t>
+        </is>
+      </c>
       <c r="K4" s="38" t="inlineStr">
         <is>
-          <t>無特別說明</t>
+          <t>逾2年未更新(7年未修，預計115提案)</t>
         </is>
       </c>
     </row>
@@ -11572,7 +12084,7 @@
       </c>
       <c r="G4" s="12" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>V</t>
         </is>
       </c>
       <c r="H4" s="12" t="inlineStr">
@@ -11585,10 +12097,14 @@
           <t>學務處</t>
         </is>
       </c>
-      <c r="J4" s="38" t="n"/>
+      <c r="J4" s="38" t="inlineStr">
+        <is>
+          <t>111.11.30</t>
+        </is>
+      </c>
       <c r="K4" s="33" t="inlineStr">
         <is>
-          <t>無特別說明</t>
+          <t>逾2年未更新(4年未修，預計115提案)</t>
         </is>
       </c>
     </row>
@@ -11623,12 +12139,12 @@
       </c>
       <c r="G5" s="35" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>V</t>
         </is>
       </c>
       <c r="H5" s="35" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>V</t>
         </is>
       </c>
       <c r="I5" s="90" t="inlineStr">
@@ -11636,10 +12152,14 @@
           <t>學務處</t>
         </is>
       </c>
-      <c r="J5" s="38" t="n"/>
+      <c r="J5" s="38" t="inlineStr">
+        <is>
+          <t>112.6.7</t>
+        </is>
+      </c>
       <c r="K5" s="38" t="inlineStr">
         <is>
-          <t>無特別說明</t>
+          <t>逾2年未更新(3年未修，預計115提案)；配合組織規程修訂(軍訓室→學生事務處生活輔導組/校安中心)</t>
         </is>
       </c>
     </row>
@@ -11687,7 +12207,11 @@
           <t>學務處</t>
         </is>
       </c>
-      <c r="J6" s="38" t="n"/>
+      <c r="J6" s="38" t="inlineStr">
+        <is>
+          <t>113.6.19</t>
+        </is>
+      </c>
       <c r="K6" s="38" t="inlineStr">
         <is>
           <t>無特別說明</t>
@@ -11738,7 +12262,11 @@
           <t>學務處</t>
         </is>
       </c>
-      <c r="J7" s="38" t="n"/>
+      <c r="J7" s="38" t="inlineStr">
+        <is>
+          <t>113.6.19</t>
+        </is>
+      </c>
       <c r="K7" s="38" t="inlineStr">
         <is>
           <t>無特別說明</t>
@@ -11771,12 +12299,12 @@
       </c>
       <c r="F8" s="35" t="inlineStr">
         <is>
-          <t>V</t>
+          <t>X</t>
         </is>
       </c>
       <c r="G8" s="35" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>V</t>
         </is>
       </c>
       <c r="H8" s="35" t="inlineStr">
@@ -11789,10 +12317,14 @@
           <t>學務處</t>
         </is>
       </c>
-      <c r="J8" s="38" t="n"/>
+      <c r="J8" s="38" t="inlineStr">
+        <is>
+          <t>109.5.21</t>
+        </is>
+      </c>
       <c r="K8" s="38" t="inlineStr">
         <is>
-          <t>無特別說明</t>
+          <t>格式瑕疵(含各式顏色標記)；逾2年未更新(6年未修，預計115提案)</t>
         </is>
       </c>
     </row>
@@ -11822,12 +12354,12 @@
       </c>
       <c r="F9" s="35" t="inlineStr">
         <is>
-          <t>V</t>
+          <t>X</t>
         </is>
       </c>
       <c r="G9" s="35" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>V</t>
         </is>
       </c>
       <c r="H9" s="35" t="inlineStr">
@@ -11840,10 +12372,14 @@
           <t>學務處</t>
         </is>
       </c>
-      <c r="J9" s="38" t="n"/>
+      <c r="J9" s="38" t="inlineStr">
+        <is>
+          <t>112.10.18</t>
+        </is>
+      </c>
       <c r="K9" s="38" t="inlineStr">
         <is>
-          <t>無特別說明</t>
+          <t>格式瑕疵(含各式顏色標記)；逾2年未更新(3年未修，預計115提案)</t>
         </is>
       </c>
     </row>
@@ -11873,7 +12409,7 @@
       </c>
       <c r="F10" s="35" t="inlineStr">
         <is>
-          <t>V</t>
+          <t>X</t>
         </is>
       </c>
       <c r="G10" s="35" t="inlineStr">
@@ -11891,10 +12427,14 @@
           <t>學務處</t>
         </is>
       </c>
-      <c r="J10" s="38" t="n"/>
+      <c r="J10" s="38" t="inlineStr">
+        <is>
+          <t>114.5.21</t>
+        </is>
+      </c>
       <c r="K10" s="38" t="inlineStr">
         <is>
-          <t>無特別說明</t>
+          <t>格式瑕疵(含各式顏色標記)</t>
         </is>
       </c>
     </row>
@@ -11942,7 +12482,11 @@
           <t>學務處</t>
         </is>
       </c>
-      <c r="J11" s="38" t="n"/>
+      <c r="J11" s="38" t="inlineStr">
+        <is>
+          <t>114.1.2</t>
+        </is>
+      </c>
       <c r="K11" s="38" t="inlineStr">
         <is>
           <t>無特別說明</t>
@@ -11993,7 +12537,11 @@
           <t>學務處</t>
         </is>
       </c>
-      <c r="J12" s="38" t="n"/>
+      <c r="J12" s="38" t="inlineStr">
+        <is>
+          <t>115.7.1</t>
+        </is>
+      </c>
       <c r="K12" s="38" t="inlineStr">
         <is>
           <t>無特別說明</t>
@@ -12026,7 +12574,7 @@
       </c>
       <c r="F13" s="12" t="inlineStr">
         <is>
-          <t>V</t>
+          <t>X</t>
         </is>
       </c>
       <c r="G13" s="12" t="inlineStr">
@@ -12044,10 +12592,14 @@
           <t>學務處</t>
         </is>
       </c>
-      <c r="J13" s="38" t="n"/>
+      <c r="J13" s="38" t="inlineStr">
+        <is>
+          <t>115.3.26</t>
+        </is>
+      </c>
       <c r="K13" s="38" t="inlineStr">
         <is>
-          <t>無特別說明</t>
+          <t>格式瑕疵(含各式顏色標記)</t>
         </is>
       </c>
     </row>
@@ -12077,7 +12629,7 @@
       </c>
       <c r="F14" s="12" t="inlineStr">
         <is>
-          <t>V</t>
+          <t>X</t>
         </is>
       </c>
       <c r="G14" s="12" t="inlineStr">
@@ -12095,10 +12647,14 @@
           <t>學務處</t>
         </is>
       </c>
-      <c r="J14" s="38" t="n"/>
+      <c r="J14" s="38" t="inlineStr">
+        <is>
+          <t>115.3.26</t>
+        </is>
+      </c>
       <c r="K14" s="38" t="inlineStr">
         <is>
-          <t>無特別說明</t>
+          <t>格式瑕疵(含各式顏色標記)</t>
         </is>
       </c>
     </row>
@@ -12133,7 +12689,7 @@
       </c>
       <c r="G15" s="12" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>V</t>
         </is>
       </c>
       <c r="H15" s="12" t="inlineStr">
@@ -12146,10 +12702,14 @@
           <t>學務處</t>
         </is>
       </c>
-      <c r="J15" s="38" t="n"/>
+      <c r="J15" s="38" t="inlineStr">
+        <is>
+          <t>110.10.7</t>
+        </is>
+      </c>
       <c r="K15" s="38" t="inlineStr">
         <is>
-          <t>無特別說明</t>
+          <t>逾2年未更新(5年未修，預計115提案)</t>
         </is>
       </c>
     </row>
@@ -12184,7 +12744,7 @@
       </c>
       <c r="G16" s="12" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>V</t>
         </is>
       </c>
       <c r="H16" s="12" t="inlineStr">
@@ -12197,10 +12757,14 @@
           <t>學務處</t>
         </is>
       </c>
-      <c r="J16" s="38" t="n"/>
+      <c r="J16" s="38" t="inlineStr">
+        <is>
+          <t>111.1.20</t>
+        </is>
+      </c>
       <c r="K16" s="38" t="inlineStr">
         <is>
-          <t>無特別說明</t>
+          <t>逾2年未更新(4年未修，預計115提案)</t>
         </is>
       </c>
     </row>
@@ -12248,7 +12812,11 @@
           <t>學務處</t>
         </is>
       </c>
-      <c r="J17" s="38" t="n"/>
+      <c r="J17" s="38" t="inlineStr">
+        <is>
+          <t>113.5.22</t>
+        </is>
+      </c>
       <c r="K17" s="38" t="inlineStr">
         <is>
           <t>無特別說明</t>
@@ -12286,7 +12854,7 @@
       </c>
       <c r="G18" s="12" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>V</t>
         </is>
       </c>
       <c r="H18" s="12" t="inlineStr">
@@ -12299,10 +12867,14 @@
           <t>學務處</t>
         </is>
       </c>
-      <c r="J18" s="38" t="n"/>
+      <c r="J18" s="38" t="inlineStr">
+        <is>
+          <t>110.10.20</t>
+        </is>
+      </c>
       <c r="K18" s="38" t="inlineStr">
         <is>
-          <t>無特別說明</t>
+          <t>逾2年未更新(5年未修，預計115提案)</t>
         </is>
       </c>
     </row>
@@ -12332,7 +12904,7 @@
       </c>
       <c r="F19" s="12" t="inlineStr">
         <is>
-          <t>V</t>
+          <t>X</t>
         </is>
       </c>
       <c r="G19" s="12" t="inlineStr">
@@ -12350,10 +12922,14 @@
           <t>學務處</t>
         </is>
       </c>
-      <c r="J19" s="38" t="n"/>
+      <c r="J19" s="38" t="inlineStr">
+        <is>
+          <t>114.12.9</t>
+        </is>
+      </c>
       <c r="K19" s="38" t="inlineStr">
         <is>
-          <t>無特別說明</t>
+          <t>格式瑕疵(含各式顏色標記)</t>
         </is>
       </c>
     </row>
@@ -12401,7 +12977,11 @@
           <t>學務處</t>
         </is>
       </c>
-      <c r="J20" s="38" t="n"/>
+      <c r="J20" s="38" t="inlineStr">
+        <is>
+          <t>115.6.3</t>
+        </is>
+      </c>
       <c r="K20" s="38" t="inlineStr">
         <is>
           <t>無特別說明</t>
@@ -12439,12 +13019,12 @@
       </c>
       <c r="G21" s="12" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>V</t>
         </is>
       </c>
       <c r="H21" s="12" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>V</t>
         </is>
       </c>
       <c r="I21" s="90" t="inlineStr">
@@ -12452,10 +13032,14 @@
           <t>學務處</t>
         </is>
       </c>
-      <c r="J21" s="38" t="n"/>
+      <c r="J21" s="38" t="inlineStr">
+        <is>
+          <t>106.10.19</t>
+        </is>
+      </c>
       <c r="K21" s="38" t="inlineStr">
         <is>
-          <t>無特別說明</t>
+          <t>逾2年未更新(9年未修，預計115提案)；配合組織規程修訂(軍訓室→學生事務處生活輔導組/校安中心)</t>
         </is>
       </c>
     </row>
@@ -12490,7 +13074,7 @@
       </c>
       <c r="G22" s="12" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>V</t>
         </is>
       </c>
       <c r="H22" s="12" t="inlineStr">
@@ -12503,10 +13087,14 @@
           <t>學務處</t>
         </is>
       </c>
-      <c r="J22" s="38" t="n"/>
+      <c r="J22" s="38" t="inlineStr">
+        <is>
+          <t>105.11.2</t>
+        </is>
+      </c>
       <c r="K22" s="38" t="inlineStr">
         <is>
-          <t>無特別說明</t>
+          <t>逾2年未更新(10年未修，預計115提案)</t>
         </is>
       </c>
     </row>
@@ -12541,7 +13129,7 @@
       </c>
       <c r="G23" s="12" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>V</t>
         </is>
       </c>
       <c r="H23" s="12" t="inlineStr">
@@ -12554,10 +13142,14 @@
           <t>學務處</t>
         </is>
       </c>
-      <c r="J23" s="38" t="n"/>
+      <c r="J23" s="38" t="inlineStr">
+        <is>
+          <t>110.6.16</t>
+        </is>
+      </c>
       <c r="K23" s="38" t="inlineStr">
         <is>
-          <t>無特別說明</t>
+          <t>逾2年未更新(5年未修，預計115提案)</t>
         </is>
       </c>
     </row>
@@ -12587,7 +13179,7 @@
       </c>
       <c r="F24" s="12" t="inlineStr">
         <is>
-          <t>V</t>
+          <t>X</t>
         </is>
       </c>
       <c r="G24" s="12" t="inlineStr">
@@ -12605,10 +13197,14 @@
           <t>學務處</t>
         </is>
       </c>
-      <c r="J24" s="38" t="n"/>
+      <c r="J24" s="38" t="inlineStr">
+        <is>
+          <t>114.6.13</t>
+        </is>
+      </c>
       <c r="K24" s="38" t="inlineStr">
         <is>
-          <t>無特別說明</t>
+          <t>格式瑕疵(含各式顏色標記)</t>
         </is>
       </c>
     </row>
@@ -12643,12 +13239,12 @@
       </c>
       <c r="G25" s="12" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>V</t>
         </is>
       </c>
       <c r="H25" s="12" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>V</t>
         </is>
       </c>
       <c r="I25" s="90" t="inlineStr">
@@ -12656,10 +13252,14 @@
           <t>學務處</t>
         </is>
       </c>
-      <c r="J25" s="38" t="n"/>
+      <c r="J25" s="38" t="inlineStr">
+        <is>
+          <t>110.12.8</t>
+        </is>
+      </c>
       <c r="K25" s="38" t="inlineStr">
         <is>
-          <t>無特別說明</t>
+          <t>逾2年未更新(5年未修，預計115提案)；配合組織規程修訂(軍訓室→學生事務處生活輔導組/校安中心)</t>
         </is>
       </c>
     </row>
@@ -12699,7 +13299,7 @@
       </c>
       <c r="H26" s="12" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>V</t>
         </is>
       </c>
       <c r="I26" s="90" t="inlineStr">
@@ -12707,10 +13307,14 @@
           <t>學務處</t>
         </is>
       </c>
-      <c r="J26" s="38" t="n"/>
+      <c r="J26" s="38" t="inlineStr">
+        <is>
+          <t>114.1.15</t>
+        </is>
+      </c>
       <c r="K26" s="38" t="inlineStr">
         <is>
-          <t>無特別說明</t>
+          <t>配合組織規程修訂(軍訓室→學生事務處生活輔導組/校安中心)</t>
         </is>
       </c>
     </row>
@@ -12740,7 +13344,7 @@
       </c>
       <c r="F27" s="12" t="inlineStr">
         <is>
-          <t>V</t>
+          <t>X</t>
         </is>
       </c>
       <c r="G27" s="12" t="inlineStr">
@@ -12758,10 +13362,14 @@
           <t>學務處</t>
         </is>
       </c>
-      <c r="J27" s="38" t="n"/>
+      <c r="J27" s="38" t="inlineStr">
+        <is>
+          <t>115.2.25</t>
+        </is>
+      </c>
       <c r="K27" s="33" t="inlineStr">
         <is>
-          <t>無特別說明</t>
+          <t>格式瑕疵(含各式顏色標記)</t>
         </is>
       </c>
     </row>
@@ -12796,7 +13404,7 @@
       </c>
       <c r="G28" s="35" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>V</t>
         </is>
       </c>
       <c r="H28" s="35" t="inlineStr">
@@ -12809,10 +13417,14 @@
           <t>學務處</t>
         </is>
       </c>
-      <c r="J28" s="38" t="n"/>
+      <c r="J28" s="38" t="inlineStr">
+        <is>
+          <t>112.5.10</t>
+        </is>
+      </c>
       <c r="K28" s="38" t="inlineStr">
         <is>
-          <t>無特別說明</t>
+          <t>逾2年未更新(3年未修，預計115提案)</t>
         </is>
       </c>
     </row>
@@ -12860,7 +13472,11 @@
           <t>學務處</t>
         </is>
       </c>
-      <c r="J29" s="38" t="n"/>
+      <c r="J29" s="38" t="inlineStr">
+        <is>
+          <t>114.4.30</t>
+        </is>
+      </c>
       <c r="K29" s="38" t="inlineStr">
         <is>
           <t>無特別說明</t>
@@ -12893,12 +13509,12 @@
       </c>
       <c r="F30" s="12" t="inlineStr">
         <is>
-          <t>V</t>
+          <t>X</t>
         </is>
       </c>
       <c r="G30" s="12" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>V</t>
         </is>
       </c>
       <c r="H30" s="12" t="inlineStr">
@@ -12911,10 +13527,14 @@
           <t>學務處</t>
         </is>
       </c>
-      <c r="J30" s="38" t="n"/>
+      <c r="J30" s="38" t="inlineStr">
+        <is>
+          <t>110.3.10</t>
+        </is>
+      </c>
       <c r="K30" s="38" t="inlineStr">
         <is>
-          <t>無特別說明</t>
+          <t>格式瑕疵(含各式顏色標記)；逾2年未更新(5年未修，預計115提案)</t>
         </is>
       </c>
     </row>
@@ -12944,7 +13564,7 @@
       </c>
       <c r="F31" s="12" t="inlineStr">
         <is>
-          <t>V</t>
+          <t>X</t>
         </is>
       </c>
       <c r="G31" s="12" t="inlineStr">
@@ -12962,10 +13582,14 @@
           <t>學務處</t>
         </is>
       </c>
-      <c r="J31" s="38" t="n"/>
+      <c r="J31" s="38" t="inlineStr">
+        <is>
+          <t>115.4.2</t>
+        </is>
+      </c>
       <c r="K31" s="38" t="inlineStr">
         <is>
-          <t>無特別說明</t>
+          <t>格式瑕疵(含各式顏色標記)</t>
         </is>
       </c>
     </row>
@@ -12995,7 +13619,7 @@
       </c>
       <c r="F32" s="12" t="inlineStr">
         <is>
-          <t>V</t>
+          <t>X</t>
         </is>
       </c>
       <c r="G32" s="12" t="inlineStr">
@@ -13013,10 +13637,14 @@
           <t>學務處</t>
         </is>
       </c>
-      <c r="J32" s="38" t="n"/>
+      <c r="J32" s="38" t="inlineStr">
+        <is>
+          <t>113.12.24</t>
+        </is>
+      </c>
       <c r="K32" s="39" t="inlineStr">
         <is>
-          <t>無特別說明</t>
+          <t>格式瑕疵(含各式顏色標記)</t>
         </is>
       </c>
     </row>
@@ -13051,7 +13679,7 @@
       </c>
       <c r="G33" s="12" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>V</t>
         </is>
       </c>
       <c r="H33" s="12" t="inlineStr">
@@ -13064,10 +13692,14 @@
           <t>學務處</t>
         </is>
       </c>
-      <c r="J33" s="38" t="n"/>
+      <c r="J33" s="38" t="inlineStr">
+        <is>
+          <t>110.1.6</t>
+        </is>
+      </c>
       <c r="K33" s="39" t="inlineStr">
         <is>
-          <t>無特別說明</t>
+          <t>逾2年未更新(5年未修，預計115提案)</t>
         </is>
       </c>
     </row>
@@ -13097,7 +13729,7 @@
       </c>
       <c r="F34" s="12" t="inlineStr">
         <is>
-          <t>V</t>
+          <t>X</t>
         </is>
       </c>
       <c r="G34" s="12" t="inlineStr">
@@ -13115,10 +13747,14 @@
           <t>學務處</t>
         </is>
       </c>
-      <c r="J34" s="38" t="n"/>
+      <c r="J34" s="38" t="inlineStr">
+        <is>
+          <t>115.3.18</t>
+        </is>
+      </c>
       <c r="K34" s="39" t="inlineStr">
         <is>
-          <t>無特別說明</t>
+          <t>格式瑕疵(含各式顏色標記)</t>
         </is>
       </c>
     </row>
@@ -13166,7 +13802,11 @@
           <t>學務處</t>
         </is>
       </c>
-      <c r="J35" s="38" t="n"/>
+      <c r="J35" s="38" t="inlineStr">
+        <is>
+          <t>114.9.3</t>
+        </is>
+      </c>
       <c r="K35" s="40" t="inlineStr">
         <is>
           <t>無特別說明</t>
@@ -13217,7 +13857,11 @@
           <t>學務處</t>
         </is>
       </c>
-      <c r="J36" s="38" t="n"/>
+      <c r="J36" s="38" t="inlineStr">
+        <is>
+          <t>115.3.18</t>
+        </is>
+      </c>
       <c r="K36" s="41" t="inlineStr">
         <is>
           <t>無特別說明</t>
@@ -13268,7 +13912,11 @@
           <t>學務處</t>
         </is>
       </c>
-      <c r="J37" s="38" t="n"/>
+      <c r="J37" s="38" t="inlineStr">
+        <is>
+          <t>114.10.8</t>
+        </is>
+      </c>
       <c r="K37" s="38" t="inlineStr">
         <is>
           <t>無特別說明</t>
@@ -13319,7 +13967,11 @@
           <t>學務處</t>
         </is>
       </c>
-      <c r="J38" s="38" t="n"/>
+      <c r="J38" s="38" t="inlineStr">
+        <is>
+          <t>113.1.10</t>
+        </is>
+      </c>
       <c r="K38" s="38" t="inlineStr">
         <is>
           <t>無特別說明</t>
@@ -13352,12 +14004,12 @@
       </c>
       <c r="F39" s="12" t="inlineStr">
         <is>
-          <t>V</t>
+          <t>X</t>
         </is>
       </c>
       <c r="G39" s="35" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>V</t>
         </is>
       </c>
       <c r="H39" s="35" t="inlineStr">
@@ -13370,10 +14022,14 @@
           <t>學務處</t>
         </is>
       </c>
-      <c r="J39" s="38" t="n"/>
+      <c r="J39" s="38" t="inlineStr">
+        <is>
+          <t>108.12.18</t>
+        </is>
+      </c>
       <c r="K39" s="38" t="inlineStr">
         <is>
-          <t>無特別說明</t>
+          <t>格式瑕疵(含各式顏色標記)；逾2年未更新(7年未修，預計115提案)</t>
         </is>
       </c>
     </row>
@@ -13408,7 +14064,7 @@
       </c>
       <c r="G40" s="35" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>V</t>
         </is>
       </c>
       <c r="H40" s="35" t="inlineStr">
@@ -13421,10 +14077,14 @@
           <t>學務處</t>
         </is>
       </c>
-      <c r="J40" s="38" t="n"/>
+      <c r="J40" s="38" t="inlineStr">
+        <is>
+          <t>112.2.8</t>
+        </is>
+      </c>
       <c r="K40" s="38" t="inlineStr">
         <is>
-          <t>無特別說明</t>
+          <t>逾2年未更新(3年未修，預計115提案)</t>
         </is>
       </c>
     </row>
@@ -13459,7 +14119,7 @@
       </c>
       <c r="G41" s="35" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>V</t>
         </is>
       </c>
       <c r="H41" s="35" t="inlineStr">
@@ -13472,10 +14132,14 @@
           <t>學務處</t>
         </is>
       </c>
-      <c r="J41" s="38" t="n"/>
+      <c r="J41" s="38" t="inlineStr">
+        <is>
+          <t>110.1.14</t>
+        </is>
+      </c>
       <c r="K41" s="42" t="inlineStr">
         <is>
-          <t>無特別說明</t>
+          <t>逾2年未更新(5年未修，預計115提案)</t>
         </is>
       </c>
     </row>
@@ -13510,7 +14174,7 @@
       </c>
       <c r="G42" s="35" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>V</t>
         </is>
       </c>
       <c r="H42" s="35" t="inlineStr">
@@ -13523,10 +14187,14 @@
           <t>學務處</t>
         </is>
       </c>
-      <c r="J42" s="38" t="n"/>
+      <c r="J42" s="38" t="inlineStr">
+        <is>
+          <t>110.6.10</t>
+        </is>
+      </c>
       <c r="K42" s="38" t="inlineStr">
         <is>
-          <t>無特別說明</t>
+          <t>逾2年未更新(5年未修，預計115提案)</t>
         </is>
       </c>
     </row>
@@ -13561,7 +14229,7 @@
       </c>
       <c r="G43" s="35" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>V</t>
         </is>
       </c>
       <c r="H43" s="35" t="inlineStr">
@@ -13574,10 +14242,14 @@
           <t>學務處</t>
         </is>
       </c>
-      <c r="J43" s="38" t="n"/>
+      <c r="J43" s="38" t="inlineStr">
+        <is>
+          <t>111.11.30</t>
+        </is>
+      </c>
       <c r="K43" s="38" t="inlineStr">
         <is>
-          <t>無特別說明</t>
+          <t>逾2年未更新(4年未修，預計115提案)</t>
         </is>
       </c>
     </row>
@@ -13612,7 +14284,7 @@
       </c>
       <c r="G44" s="35" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>V</t>
         </is>
       </c>
       <c r="H44" s="35" t="inlineStr">
@@ -13625,10 +14297,14 @@
           <t>學務處</t>
         </is>
       </c>
-      <c r="J44" s="38" t="n"/>
+      <c r="J44" s="38" t="inlineStr">
+        <is>
+          <t>106.1.4</t>
+        </is>
+      </c>
       <c r="K44" s="38" t="inlineStr">
         <is>
-          <t>無特別說明</t>
+          <t>逾2年未更新(9年未修，預計115提案)</t>
         </is>
       </c>
     </row>
@@ -13663,7 +14339,7 @@
       </c>
       <c r="G45" s="35" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>V</t>
         </is>
       </c>
       <c r="H45" s="35" t="inlineStr">
@@ -13676,10 +14352,14 @@
           <t>學務處</t>
         </is>
       </c>
-      <c r="J45" s="38" t="n"/>
+      <c r="J45" s="38" t="inlineStr">
+        <is>
+          <t>106.1.4</t>
+        </is>
+      </c>
       <c r="K45" s="38" t="inlineStr">
         <is>
-          <t>無特別說明</t>
+          <t>逾2年未更新(9年未修，預計115提案)</t>
         </is>
       </c>
     </row>
@@ -13714,7 +14394,7 @@
       </c>
       <c r="G46" s="35" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>V</t>
         </is>
       </c>
       <c r="H46" s="35" t="inlineStr">
@@ -13727,10 +14407,14 @@
           <t>學務處</t>
         </is>
       </c>
-      <c r="J46" s="49" t="n"/>
+      <c r="J46" s="49" t="inlineStr">
+        <is>
+          <t>100.6.24</t>
+        </is>
+      </c>
       <c r="K46" s="38" t="inlineStr">
         <is>
-          <t>無特別說明</t>
+          <t>逾2年未更新(15年未修，預計115提案)</t>
         </is>
       </c>
     </row>
@@ -13765,7 +14449,7 @@
       </c>
       <c r="G47" s="35" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>V</t>
         </is>
       </c>
       <c r="H47" s="35" t="inlineStr">
@@ -13778,10 +14462,14 @@
           <t>學務處</t>
         </is>
       </c>
-      <c r="J47" s="38" t="n"/>
+      <c r="J47" s="38" t="inlineStr">
+        <is>
+          <t>110.1.14</t>
+        </is>
+      </c>
       <c r="K47" s="38" t="inlineStr">
         <is>
-          <t>無特別說明</t>
+          <t>逾2年未更新(5年未修，預計115提案)</t>
         </is>
       </c>
     </row>
@@ -13816,7 +14504,7 @@
       </c>
       <c r="G48" s="35" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>V</t>
         </is>
       </c>
       <c r="H48" s="35" t="inlineStr">
@@ -13829,10 +14517,14 @@
           <t>學務處</t>
         </is>
       </c>
-      <c r="J48" s="38" t="n"/>
+      <c r="J48" s="38" t="inlineStr">
+        <is>
+          <t>112.11.29</t>
+        </is>
+      </c>
       <c r="K48" s="38" t="inlineStr">
         <is>
-          <t>無特別說明</t>
+          <t>逾2年未更新(3年未修，預計115提案)</t>
         </is>
       </c>
     </row>
@@ -13867,7 +14559,7 @@
       </c>
       <c r="G49" s="35" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>V</t>
         </is>
       </c>
       <c r="H49" s="35" t="inlineStr">
@@ -13880,10 +14572,14 @@
           <t>學務處</t>
         </is>
       </c>
-      <c r="J49" s="38" t="n"/>
+      <c r="J49" s="38" t="inlineStr">
+        <is>
+          <t>106.10.19</t>
+        </is>
+      </c>
       <c r="K49" s="38" t="inlineStr">
         <is>
-          <t>無特別說明</t>
+          <t>逾2年未更新(9年未修，預計115提案)</t>
         </is>
       </c>
     </row>
@@ -13918,7 +14614,7 @@
       </c>
       <c r="G50" s="35" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>V</t>
         </is>
       </c>
       <c r="H50" s="35" t="inlineStr">
@@ -13931,10 +14627,14 @@
           <t>學務處</t>
         </is>
       </c>
-      <c r="J50" s="38" t="n"/>
+      <c r="J50" s="38" t="inlineStr">
+        <is>
+          <t>109.1.9</t>
+        </is>
+      </c>
       <c r="K50" s="38" t="inlineStr">
         <is>
-          <t>無特別說明</t>
+          <t>逾2年未更新(6年未修，預計115提案)</t>
         </is>
       </c>
     </row>
@@ -13969,7 +14669,7 @@
       </c>
       <c r="G51" s="35" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>V</t>
         </is>
       </c>
       <c r="H51" s="35" t="inlineStr">
@@ -13982,10 +14682,14 @@
           <t>學務處</t>
         </is>
       </c>
-      <c r="J51" s="38" t="n"/>
+      <c r="J51" s="38" t="inlineStr">
+        <is>
+          <t>110.9.2</t>
+        </is>
+      </c>
       <c r="K51" s="38" t="inlineStr">
         <is>
-          <t>無特別說明</t>
+          <t>逾2年未更新(5年未修，預計115提案)</t>
         </is>
       </c>
     </row>
@@ -14020,7 +14724,7 @@
       </c>
       <c r="G52" s="35" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>V</t>
         </is>
       </c>
       <c r="H52" s="35" t="inlineStr">
@@ -14033,10 +14737,14 @@
           <t>學務處</t>
         </is>
       </c>
-      <c r="J52" s="38" t="n"/>
+      <c r="J52" s="38" t="inlineStr">
+        <is>
+          <t>109.6.18</t>
+        </is>
+      </c>
       <c r="K52" s="38" t="inlineStr">
         <is>
-          <t>無特別說明</t>
+          <t>逾2年未更新(6年未修，預計115提案)</t>
         </is>
       </c>
     </row>
@@ -14066,12 +14774,12 @@
       </c>
       <c r="F53" s="12" t="inlineStr">
         <is>
-          <t>V</t>
+          <t>X</t>
         </is>
       </c>
       <c r="G53" s="35" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>V</t>
         </is>
       </c>
       <c r="H53" s="35" t="inlineStr">
@@ -14084,10 +14792,14 @@
           <t>學務處</t>
         </is>
       </c>
-      <c r="J53" s="38" t="n"/>
+      <c r="J53" s="38" t="inlineStr">
+        <is>
+          <t>109.10.14</t>
+        </is>
+      </c>
       <c r="K53" s="38" t="inlineStr">
         <is>
-          <t>無特別說明</t>
+          <t>格式瑕疵(含各式顏色標記)；逾2年未更新(6年未修，預計115提案)</t>
         </is>
       </c>
     </row>
@@ -14122,7 +14834,7 @@
       </c>
       <c r="G54" s="35" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>V</t>
         </is>
       </c>
       <c r="H54" s="35" t="inlineStr">
@@ -14135,10 +14847,14 @@
           <t>學務處</t>
         </is>
       </c>
-      <c r="J54" s="38" t="n"/>
+      <c r="J54" s="38" t="inlineStr">
+        <is>
+          <t>112.11.29</t>
+        </is>
+      </c>
       <c r="K54" s="38" t="inlineStr">
         <is>
-          <t>無特別說明</t>
+          <t>逾2年未更新(3年未修，預計115提案)</t>
         </is>
       </c>
     </row>
@@ -14186,7 +14902,11 @@
           <t>學務處</t>
         </is>
       </c>
-      <c r="J55" s="38" t="n"/>
+      <c r="J55" s="38" t="inlineStr">
+        <is>
+          <t>114.10.8</t>
+        </is>
+      </c>
       <c r="K55" s="38" t="inlineStr">
         <is>
           <t>無特別說明</t>
@@ -14237,7 +14957,11 @@
           <t>學務處</t>
         </is>
       </c>
-      <c r="J56" s="38" t="n"/>
+      <c r="J56" s="38" t="inlineStr">
+        <is>
+          <t>114.10.8</t>
+        </is>
+      </c>
       <c r="K56" s="49" t="inlineStr">
         <is>
           <t>無特別說明</t>
@@ -14288,7 +15012,11 @@
           <t>學務處</t>
         </is>
       </c>
-      <c r="J57" s="38" t="n"/>
+      <c r="J57" s="38" t="inlineStr">
+        <is>
+          <t>114.12.3</t>
+        </is>
+      </c>
       <c r="K57" s="38" t="inlineStr">
         <is>
           <t>無特別說明</t>
@@ -14339,7 +15067,11 @@
           <t>學務處</t>
         </is>
       </c>
-      <c r="J58" s="38" t="n"/>
+      <c r="J58" s="38" t="inlineStr">
+        <is>
+          <t>115.6.30</t>
+        </is>
+      </c>
       <c r="K58" s="38" t="inlineStr">
         <is>
           <t>無特別說明</t>
@@ -14390,7 +15122,11 @@
           <t>學務處</t>
         </is>
       </c>
-      <c r="J59" s="38" t="n"/>
+      <c r="J59" s="38" t="inlineStr">
+        <is>
+          <t>113.9.18</t>
+        </is>
+      </c>
       <c r="K59" s="38" t="inlineStr">
         <is>
           <t>無特別說明</t>
@@ -14423,12 +15159,12 @@
       </c>
       <c r="F60" s="97" t="inlineStr">
         <is>
-          <t>V</t>
+          <t>X</t>
         </is>
       </c>
       <c r="G60" s="97" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>V</t>
         </is>
       </c>
       <c r="H60" s="97" t="inlineStr">
@@ -14441,10 +15177,14 @@
           <t>學務處</t>
         </is>
       </c>
-      <c r="J60" s="38" t="n"/>
+      <c r="J60" s="38" t="inlineStr">
+        <is>
+          <t>112.6.8</t>
+        </is>
+      </c>
       <c r="K60" s="38" t="inlineStr">
         <is>
-          <t>無特別說明</t>
+          <t>格式瑕疵(含各式顏色標記)；逾2年未更新(3年未修，預計115提案)</t>
         </is>
       </c>
     </row>
@@ -14474,7 +15214,7 @@
       </c>
       <c r="F61" s="97" t="inlineStr">
         <is>
-          <t>V</t>
+          <t>X</t>
         </is>
       </c>
       <c r="G61" s="97" t="inlineStr">
@@ -14492,10 +15232,14 @@
           <t>學務處</t>
         </is>
       </c>
-      <c r="J61" s="38" t="n"/>
+      <c r="J61" s="38" t="inlineStr">
+        <is>
+          <t>114.9.3</t>
+        </is>
+      </c>
       <c r="K61" s="38" t="inlineStr">
         <is>
-          <t>無特別說明</t>
+          <t>格式瑕疵(含各式顏色標記)</t>
         </is>
       </c>
     </row>
@@ -14543,7 +15287,11 @@
           <t>學務處</t>
         </is>
       </c>
-      <c r="J62" s="38" t="n"/>
+      <c r="J62" s="38" t="inlineStr">
+        <is>
+          <t>113.4.18</t>
+        </is>
+      </c>
       <c r="K62" s="38" t="inlineStr">
         <is>
           <t>無特別說明</t>
@@ -14594,7 +15342,11 @@
           <t>學務處</t>
         </is>
       </c>
-      <c r="J63" s="38" t="n"/>
+      <c r="J63" s="38" t="inlineStr">
+        <is>
+          <t>114.10.28</t>
+        </is>
+      </c>
       <c r="K63" s="38" t="inlineStr">
         <is>
           <t>無特別說明</t>
@@ -14632,7 +15384,7 @@
       </c>
       <c r="G64" s="35" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>V</t>
         </is>
       </c>
       <c r="H64" s="35" t="inlineStr">
@@ -14645,10 +15397,14 @@
           <t>學務處</t>
         </is>
       </c>
-      <c r="J64" s="38" t="n"/>
+      <c r="J64" s="38" t="inlineStr">
+        <is>
+          <t>107.11.21</t>
+        </is>
+      </c>
       <c r="K64" s="49" t="inlineStr">
         <is>
-          <t>無特別說明</t>
+          <t>逾2年未更新(8年未修，預計115提案)</t>
         </is>
       </c>
     </row>
@@ -14683,7 +15439,7 @@
       </c>
       <c r="G65" s="35" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>V</t>
         </is>
       </c>
       <c r="H65" s="35" t="inlineStr">
@@ -14696,10 +15452,14 @@
           <t>學務處</t>
         </is>
       </c>
-      <c r="J65" s="38" t="n"/>
+      <c r="J65" s="38" t="inlineStr">
+        <is>
+          <t>108.4.30</t>
+        </is>
+      </c>
       <c r="K65" s="38" t="inlineStr">
         <is>
-          <t>無特別說明</t>
+          <t>逾2年未更新(7年未修，預計115提案)</t>
         </is>
       </c>
     </row>
@@ -14729,7 +15489,7 @@
       </c>
       <c r="F66" s="35" t="inlineStr">
         <is>
-          <t>V</t>
+          <t>X</t>
         </is>
       </c>
       <c r="G66" s="35" t="inlineStr">
@@ -14747,10 +15507,14 @@
           <t>學務處</t>
         </is>
       </c>
-      <c r="J66" s="38" t="n"/>
+      <c r="J66" s="38" t="inlineStr">
+        <is>
+          <t>113.9.12</t>
+        </is>
+      </c>
       <c r="K66" s="38" t="inlineStr">
         <is>
-          <t>無特別說明</t>
+          <t>格式瑕疵(含各式顏色標記)</t>
         </is>
       </c>
     </row>
@@ -14785,12 +15549,12 @@
       </c>
       <c r="G67" s="35" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>V</t>
         </is>
       </c>
       <c r="H67" s="35" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>V</t>
         </is>
       </c>
       <c r="I67" s="90" t="inlineStr">
@@ -14798,10 +15562,14 @@
           <t>學務處</t>
         </is>
       </c>
-      <c r="J67" s="38" t="n"/>
+      <c r="J67" s="38" t="inlineStr">
+        <is>
+          <t>109.1.9</t>
+        </is>
+      </c>
       <c r="K67" s="38" t="inlineStr">
         <is>
-          <t>無特別說明</t>
+          <t>逾2年未更新(6年未修，預計115提案)；配合組織規程修訂(衛生保健組→健康中心)</t>
         </is>
       </c>
     </row>
@@ -14836,12 +15604,12 @@
       </c>
       <c r="G68" s="35" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>V</t>
         </is>
       </c>
       <c r="H68" s="35" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>V</t>
         </is>
       </c>
       <c r="I68" s="90" t="inlineStr">
@@ -14849,10 +15617,14 @@
           <t>學務處</t>
         </is>
       </c>
-      <c r="J68" s="38" t="n"/>
+      <c r="J68" s="38" t="inlineStr">
+        <is>
+          <t>111.7.20</t>
+        </is>
+      </c>
       <c r="K68" s="38" t="inlineStr">
         <is>
-          <t>無特別說明</t>
+          <t>逾2年未更新(4年未修，預計115提案)；配合組織規程修訂(衛生保健組→健康中心;軍訓室→學生事務處生活輔導組/校安中心)</t>
         </is>
       </c>
     </row>
@@ -14887,12 +15659,12 @@
       </c>
       <c r="G69" s="35" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>V</t>
         </is>
       </c>
       <c r="H69" s="35" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>V</t>
         </is>
       </c>
       <c r="I69" s="90" t="inlineStr">
@@ -14900,10 +15672,14 @@
           <t>學務處</t>
         </is>
       </c>
-      <c r="J69" s="38" t="n"/>
+      <c r="J69" s="38" t="inlineStr">
+        <is>
+          <t>107.12.5</t>
+        </is>
+      </c>
       <c r="K69" s="38" t="inlineStr">
         <is>
-          <t>無特別說明</t>
+          <t>逾2年未更新(8年未修，預計115提案)；配合組織規程修訂(衛生保健組→健康中心)</t>
         </is>
       </c>
     </row>
@@ -14938,12 +15714,12 @@
       </c>
       <c r="G70" s="35" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>V</t>
         </is>
       </c>
       <c r="H70" s="35" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>V</t>
         </is>
       </c>
       <c r="I70" s="90" t="inlineStr">
@@ -14951,10 +15727,14 @@
           <t>學務處</t>
         </is>
       </c>
-      <c r="J70" s="38" t="n"/>
+      <c r="J70" s="38" t="inlineStr">
+        <is>
+          <t>107.6.28</t>
+        </is>
+      </c>
       <c r="K70" s="38" t="inlineStr">
         <is>
-          <t>無特別說明</t>
+          <t>逾2年未更新(8年未修，預計115提案)；配合組織規程修訂(衛生保健組→健康中心)</t>
         </is>
       </c>
     </row>
@@ -14989,7 +15769,7 @@
       </c>
       <c r="G71" s="35" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>V</t>
         </is>
       </c>
       <c r="H71" s="35" t="inlineStr">
@@ -15002,10 +15782,14 @@
           <t>學務處</t>
         </is>
       </c>
-      <c r="J71" s="38" t="n"/>
+      <c r="J71" s="38" t="inlineStr">
+        <is>
+          <t>106.6.21</t>
+        </is>
+      </c>
       <c r="K71" s="38" t="inlineStr">
         <is>
-          <t>無特別說明</t>
+          <t>逾2年未更新(9年未修，預計115提案)</t>
         </is>
       </c>
     </row>
@@ -15040,12 +15824,12 @@
       </c>
       <c r="G72" s="35" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>V</t>
         </is>
       </c>
       <c r="H72" s="35" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>V</t>
         </is>
       </c>
       <c r="I72" s="90" t="inlineStr">
@@ -15053,10 +15837,14 @@
           <t>學務處</t>
         </is>
       </c>
-      <c r="J72" s="38" t="n"/>
+      <c r="J72" s="38" t="inlineStr">
+        <is>
+          <t>109.6.11</t>
+        </is>
+      </c>
       <c r="K72" s="38" t="inlineStr">
         <is>
-          <t>無特別說明</t>
+          <t>逾2年未更新(6年未修，預計115提案)；配合組織規程修訂(衛生保健組→健康中心)</t>
         </is>
       </c>
     </row>
@@ -15302,7 +16090,11 @@
           <t>總務處</t>
         </is>
       </c>
-      <c r="J4" s="38" t="n"/>
+      <c r="J4" s="38" t="inlineStr">
+        <is>
+          <t>113.2.21</t>
+        </is>
+      </c>
       <c r="K4" s="38" t="inlineStr">
         <is>
           <t>無特別說明</t>
@@ -15345,7 +16137,7 @@
       </c>
       <c r="H5" s="97" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>V</t>
         </is>
       </c>
       <c r="I5" s="38" t="inlineStr">
@@ -15353,10 +16145,14 @@
           <t>總務處</t>
         </is>
       </c>
-      <c r="J5" s="38" t="n"/>
+      <c r="J5" s="38" t="inlineStr">
+        <is>
+          <t>114.5.21</t>
+        </is>
+      </c>
       <c r="K5" s="38" t="inlineStr">
         <is>
-          <t>無特別說明</t>
+          <t>配合組織規程修訂(衛生保健組→健康中心)</t>
         </is>
       </c>
     </row>
@@ -15404,7 +16200,11 @@
           <t>總務處</t>
         </is>
       </c>
-      <c r="J6" s="38" t="n"/>
+      <c r="J6" s="38" t="inlineStr">
+        <is>
+          <t>115.5.13</t>
+        </is>
+      </c>
       <c r="K6" s="38" t="inlineStr">
         <is>
           <t>無特別說明</t>
@@ -15442,7 +16242,7 @@
       </c>
       <c r="G7" s="97" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>V</t>
         </is>
       </c>
       <c r="H7" s="97" t="inlineStr">
@@ -15455,10 +16255,14 @@
           <t>總務處</t>
         </is>
       </c>
-      <c r="J7" s="38" t="n"/>
+      <c r="J7" s="38" t="inlineStr">
+        <is>
+          <t>105.9.30</t>
+        </is>
+      </c>
       <c r="K7" s="38" t="inlineStr">
         <is>
-          <t>無特別說明</t>
+          <t>逾2年未更新(10年未修，預計115提案)</t>
         </is>
       </c>
     </row>
@@ -15506,7 +16310,11 @@
           <t>總務處</t>
         </is>
       </c>
-      <c r="J8" s="38" t="n"/>
+      <c r="J8" s="38" t="inlineStr">
+        <is>
+          <t>115.7.8</t>
+        </is>
+      </c>
       <c r="K8" s="38" t="inlineStr">
         <is>
           <t>無特別說明</t>
@@ -15544,7 +16352,7 @@
       </c>
       <c r="G9" s="97" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>V</t>
         </is>
       </c>
       <c r="H9" s="97" t="inlineStr">
@@ -15557,10 +16365,14 @@
           <t>總務處</t>
         </is>
       </c>
-      <c r="J9" s="38" t="n"/>
+      <c r="J9" s="38" t="inlineStr">
+        <is>
+          <t>105.5.12</t>
+        </is>
+      </c>
       <c r="K9" s="38" t="inlineStr">
         <is>
-          <t>無特別說明</t>
+          <t>逾2年未更新(10年未修，預計115提案)</t>
         </is>
       </c>
     </row>
@@ -15608,7 +16420,11 @@
           <t>總務處</t>
         </is>
       </c>
-      <c r="J10" s="38" t="n"/>
+      <c r="J10" s="38" t="inlineStr">
+        <is>
+          <t>115.6.3</t>
+        </is>
+      </c>
       <c r="K10" s="38" t="inlineStr">
         <is>
           <t>無特別說明</t>
@@ -15659,7 +16475,11 @@
           <t>總務處</t>
         </is>
       </c>
-      <c r="J11" s="38" t="n"/>
+      <c r="J11" s="38" t="inlineStr">
+        <is>
+          <t>115.5.13</t>
+        </is>
+      </c>
       <c r="K11" s="38" t="inlineStr">
         <is>
           <t>無特別說明</t>
@@ -15692,7 +16512,7 @@
       </c>
       <c r="F12" s="97" t="inlineStr">
         <is>
-          <t>V</t>
+          <t>X</t>
         </is>
       </c>
       <c r="G12" s="97" t="inlineStr">
@@ -15702,7 +16522,7 @@
       </c>
       <c r="H12" s="97" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>V</t>
         </is>
       </c>
       <c r="I12" s="38" t="inlineStr">
@@ -15710,10 +16530,14 @@
           <t>總務處</t>
         </is>
       </c>
-      <c r="J12" s="38" t="n"/>
+      <c r="J12" s="38" t="inlineStr">
+        <is>
+          <t>115.2.25</t>
+        </is>
+      </c>
       <c r="K12" s="38" t="inlineStr">
         <is>
-          <t>無特別說明</t>
+          <t>格式瑕疵(含各式顏色標記)；配合組織規程修訂(軍訓室→學生事務處生活輔導組/校安中心)</t>
         </is>
       </c>
     </row>
@@ -15946,7 +16770,7 @@
       </c>
       <c r="K4" s="75" t="inlineStr">
         <is>
-          <t>格式瑕疵(含底線,含各式顏色標記)；逾2年未更新(預計115提案)</t>
+          <t>格式瑕疵(含底線,含各式顏色標記)；逾2年未更新(6年未修，預計115提案)</t>
         </is>
       </c>
     </row>
@@ -15996,12 +16820,12 @@
       </c>
       <c r="J5" s="103" t="inlineStr">
         <is>
-          <t>108.05.15</t>
+          <t>108.10.31</t>
         </is>
       </c>
       <c r="K5" s="75" t="inlineStr">
         <is>
-          <t>逾2年未更新(預計115提案)</t>
+          <t>逾2年未更新(7年未修，預計115提案)</t>
         </is>
       </c>
     </row>
@@ -16051,7 +16875,7 @@
       </c>
       <c r="J6" s="103" t="inlineStr">
         <is>
-          <t>113.07.09</t>
+          <t>113.7.9</t>
         </is>
       </c>
       <c r="K6" s="75" t="inlineStr">
@@ -16166,7 +16990,7 @@
       </c>
       <c r="K8" s="75" t="inlineStr">
         <is>
-          <t>格式瑕疵(含底線,含各式顏色標記)；逾2年未更新(預計115提案)</t>
+          <t>格式瑕疵(含底線,含各式顏色標記)；逾2年未更新(18年未修，預計115提案)</t>
         </is>
       </c>
     </row>
@@ -16216,7 +17040,7 @@
       </c>
       <c r="J9" s="103" t="inlineStr">
         <is>
-          <t>115.06.03</t>
+          <t>115.6.3</t>
         </is>
       </c>
       <c r="K9" s="75" t="inlineStr">
@@ -16271,7 +17095,7 @@
       </c>
       <c r="J10" s="103" t="inlineStr">
         <is>
-          <t>114.09.03</t>
+          <t>114.9.3</t>
         </is>
       </c>
       <c r="K10" s="75" t="inlineStr">
@@ -16326,12 +17150,12 @@
       </c>
       <c r="J11" s="103" t="inlineStr">
         <is>
-          <t>111.09.29</t>
+          <t>111.9.29</t>
         </is>
       </c>
       <c r="K11" s="78" t="inlineStr">
         <is>
-          <t>逾2年未更新(預計115提案)</t>
+          <t>逾2年未更新(4年未修，預計115提案)</t>
         </is>
       </c>
     </row>
@@ -16381,7 +17205,7 @@
       </c>
       <c r="J12" s="103" t="inlineStr">
         <is>
-          <t>113.04.03</t>
+          <t>113.4.3</t>
         </is>
       </c>
       <c r="K12" s="78" t="inlineStr">
@@ -16436,7 +17260,7 @@
       </c>
       <c r="J13" s="103" t="inlineStr">
         <is>
-          <t>115.01.07</t>
+          <t>115.1.7</t>
         </is>
       </c>
       <c r="K13" s="75" t="inlineStr">
@@ -16491,7 +17315,7 @@
       </c>
       <c r="J14" s="103" t="inlineStr">
         <is>
-          <t>113.06.19</t>
+          <t>113.6.19</t>
         </is>
       </c>
       <c r="K14" s="75" t="inlineStr">
@@ -16546,12 +17370,12 @@
       </c>
       <c r="J15" s="103" t="inlineStr">
         <is>
-          <t>106.04.06</t>
+          <t>106.4.6</t>
         </is>
       </c>
       <c r="K15" s="75" t="inlineStr">
         <is>
-          <t>格式瑕疵(含底線,含各式顏色標記)；逾2年未更新(預計115提案)；配合組織規程修訂</t>
+          <t>格式瑕疵(含底線,含各式顏色標記)；逾2年未更新(9年未修，預計115提案)；配合組織規程修訂(研究發展處→研究暨產學發展處)</t>
         </is>
       </c>
     </row>
@@ -16601,12 +17425,12 @@
       </c>
       <c r="J16" s="103" t="inlineStr">
         <is>
-          <t>105.09.30</t>
+          <t>105.9.30</t>
         </is>
       </c>
       <c r="K16" s="75" t="inlineStr">
         <is>
-          <t>格式瑕疵(含底線,含各式顏色標記)；逾2年未更新(預計115提案)</t>
+          <t>格式瑕疵(含底線,含各式顏色標記)；逾2年未更新(10年未修，預計115提案)</t>
         </is>
       </c>
     </row>
@@ -16661,7 +17485,7 @@
       </c>
       <c r="K17" s="75" t="inlineStr">
         <is>
-          <t>格式瑕疵(含底線,含各式顏色標記)；逾2年未更新(預計115提案)</t>
+          <t>格式瑕疵(含底線,含各式顏色標記)；逾2年未更新(7年未修，預計115提案)</t>
         </is>
       </c>
     </row>
@@ -16711,7 +17535,7 @@
       </c>
       <c r="J18" s="103" t="inlineStr">
         <is>
-          <t>114.11.05</t>
+          <t>114.11.10</t>
         </is>
       </c>
       <c r="K18" s="75" t="inlineStr">
@@ -16766,12 +17590,12 @@
       </c>
       <c r="J19" s="103" t="inlineStr">
         <is>
-          <t>105.09.30</t>
+          <t>105.9.30</t>
         </is>
       </c>
       <c r="K19" s="75" t="inlineStr">
         <is>
-          <t>格式瑕疵(含底線,含各式顏色標記)；逾2年未更新(預計115提案)</t>
+          <t>格式瑕疵(含底線,含各式顏色標記)；逾2年未更新(10年未修，預計115提案)</t>
         </is>
       </c>
     </row>
@@ -16801,12 +17625,12 @@
       </c>
       <c r="F20" s="103" t="inlineStr">
         <is>
-          <t>V</t>
+          <t>X</t>
         </is>
       </c>
       <c r="G20" s="83" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>V</t>
         </is>
       </c>
       <c r="H20" s="103" t="inlineStr">
@@ -16819,10 +17643,14 @@
           <t>研究暨產學發展處</t>
         </is>
       </c>
-      <c r="J20" s="103" t="n"/>
+      <c r="J20" s="103" t="inlineStr">
+        <is>
+          <t>108.6.13</t>
+        </is>
+      </c>
       <c r="K20" s="75" t="inlineStr">
         <is>
-          <t>無特別說明</t>
+          <t>格式瑕疵(含底線,含各式顏色標記,含修訂標籤)；逾2年未更新(7年未修，預計115提案)</t>
         </is>
       </c>
     </row>
@@ -16872,12 +17700,12 @@
       </c>
       <c r="J21" s="103" t="inlineStr">
         <is>
-          <t>112.04.26</t>
+          <t>112.4.26</t>
         </is>
       </c>
       <c r="K21" s="75" t="inlineStr">
         <is>
-          <t>逾2年未更新(預計115提案)</t>
+          <t>逾2年未更新(3年未修，預計115提案)</t>
         </is>
       </c>
     </row>
@@ -16927,12 +17755,12 @@
       </c>
       <c r="J22" s="103" t="inlineStr">
         <is>
-          <t>105.10.05</t>
+          <t>105.10.5</t>
         </is>
       </c>
       <c r="K22" s="75" t="inlineStr">
         <is>
-          <t>格式瑕疵(含底線,含各式顏色標記)；逾2年未更新(預計115提案)</t>
+          <t>格式瑕疵(含底線,含各式顏色標記)；逾2年未更新(10年未修，預計115提案)</t>
         </is>
       </c>
     </row>
@@ -16982,12 +17810,12 @@
       </c>
       <c r="J23" s="103" t="inlineStr">
         <is>
-          <t>106.02.22</t>
+          <t>106.2.22</t>
         </is>
       </c>
       <c r="K23" s="75" t="inlineStr">
         <is>
-          <t>格式瑕疵(含底線,含各式顏色標記)；逾2年未更新(預計115提案)</t>
+          <t>格式瑕疵(含底線,含各式顏色標記)；逾2年未更新(9年未修，預計115提案)</t>
         </is>
       </c>
     </row>
@@ -17042,7 +17870,7 @@
       </c>
       <c r="K24" s="75" t="inlineStr">
         <is>
-          <t>格式瑕疵(含底線,含各式顏色標記)；逾2年未更新(預計115提案)</t>
+          <t>格式瑕疵(含底線,含各式顏色標記)；逾2年未更新(4年未修，預計115提案)</t>
         </is>
       </c>
     </row>
@@ -17092,12 +17920,12 @@
       </c>
       <c r="J25" s="103" t="inlineStr">
         <is>
-          <t>111.10.05</t>
+          <t>111.10.5</t>
         </is>
       </c>
       <c r="K25" s="75" t="inlineStr">
         <is>
-          <t>格式瑕疵(含底線,含各式顏色標記)；逾2年未更新(預計115提案)</t>
+          <t>格式瑕疵(含底線,含各式顏色標記)；逾2年未更新(4年未修，預計115提案)</t>
         </is>
       </c>
     </row>
@@ -17147,12 +17975,12 @@
       </c>
       <c r="J26" s="103" t="inlineStr">
         <is>
-          <t>106.01.11</t>
+          <t>106.1.11</t>
         </is>
       </c>
       <c r="K26" s="75" t="inlineStr">
         <is>
-          <t>格式瑕疵(含底線,含各式顏色標記)；逾2年未更新(預計115提案)</t>
+          <t>格式瑕疵(含底線,含各式顏色標記)；逾2年未更新(9年未修，預計115提案)</t>
         </is>
       </c>
     </row>
@@ -17202,12 +18030,12 @@
       </c>
       <c r="J27" s="103" t="inlineStr">
         <is>
-          <t>110.07.05</t>
+          <t>110.7.5</t>
         </is>
       </c>
       <c r="K27" s="75" t="inlineStr">
         <is>
-          <t>格式瑕疵(含修訂標籤)；逾2年未更新(預計115提案)</t>
+          <t>格式瑕疵(含修訂標籤)；逾2年未更新(5年未修，預計115提案)</t>
         </is>
       </c>
     </row>
@@ -17257,12 +18085,12 @@
       </c>
       <c r="J28" s="103" t="inlineStr">
         <is>
-          <t>111.11.07</t>
+          <t>111.11.7</t>
         </is>
       </c>
       <c r="K28" s="75" t="inlineStr">
         <is>
-          <t>逾2年未更新(預計115提案)</t>
+          <t>逾2年未更新(4年未修，預計115提案)</t>
         </is>
       </c>
     </row>
@@ -17317,7 +18145,7 @@
       </c>
       <c r="K29" s="75" t="inlineStr">
         <is>
-          <t>格式瑕疵(含底線,含各式顏色標記)；逾2年未更新(預計115提案)</t>
+          <t>格式瑕疵(含底線,含各式顏色標記)；逾2年未更新(6年未修，預計115提案)</t>
         </is>
       </c>
     </row>
@@ -17347,7 +18175,7 @@
       </c>
       <c r="F30" s="103" t="inlineStr">
         <is>
-          <t>V</t>
+          <t>X</t>
         </is>
       </c>
       <c r="G30" s="83" t="inlineStr">
@@ -17367,12 +18195,12 @@
       </c>
       <c r="J30" s="103" t="inlineStr">
         <is>
-          <t>108.02.20</t>
+          <t>108.2.20</t>
         </is>
       </c>
       <c r="K30" s="75" t="inlineStr">
         <is>
-          <t>逾2年未更新(預計115提案)</t>
+          <t>格式瑕疵(含各式顏色標記)；逾2年未更新(7年未修，預計115提案)</t>
         </is>
       </c>
     </row>
@@ -17422,7 +18250,7 @@
       </c>
       <c r="J31" s="103" t="inlineStr">
         <is>
-          <t>114.06.18</t>
+          <t>114.6.18</t>
         </is>
       </c>
       <c r="K31" s="75" t="inlineStr">
@@ -17477,12 +18305,12 @@
       </c>
       <c r="J32" s="103" t="inlineStr">
         <is>
-          <t>111.03.11</t>
+          <t>111.3.11</t>
         </is>
       </c>
       <c r="K32" s="75" t="inlineStr">
         <is>
-          <t>格式瑕疵(含底線,含各式顏色標記)；逾2年未更新(預計115提案)</t>
+          <t>格式瑕疵(含底線,含各式顏色標記)；逾2年未更新(4年未修，預計115提案)</t>
         </is>
       </c>
     </row>
@@ -17532,7 +18360,7 @@
       </c>
       <c r="J33" s="103" t="inlineStr">
         <is>
-          <t>114.01.02</t>
+          <t>114.1.2</t>
         </is>
       </c>
       <c r="K33" s="75" t="inlineStr">
@@ -17587,7 +18415,7 @@
       </c>
       <c r="J34" s="103" t="inlineStr">
         <is>
-          <t>113.06.19</t>
+          <t>113.6.19</t>
         </is>
       </c>
       <c r="K34" s="75" t="inlineStr">
@@ -17642,7 +18470,7 @@
       </c>
       <c r="J35" s="103" t="inlineStr">
         <is>
-          <t>114.06.18</t>
+          <t>114.6.18</t>
         </is>
       </c>
       <c r="K35" s="75" t="inlineStr">
@@ -17697,7 +18525,7 @@
       </c>
       <c r="J36" s="103" t="inlineStr">
         <is>
-          <t>115.06.03</t>
+          <t>115.6.3</t>
         </is>
       </c>
       <c r="K36" s="75" t="inlineStr">
@@ -17752,12 +18580,12 @@
       </c>
       <c r="J37" s="103" t="inlineStr">
         <is>
-          <t>111.10.05</t>
+          <t>111.10.5</t>
         </is>
       </c>
       <c r="K37" s="75" t="inlineStr">
         <is>
-          <t>格式瑕疵(含底線,含各式顏色標記,含修訂標籤)；逾2年未更新(預計115提案)</t>
+          <t>格式瑕疵(含底線,含各式顏色標記,含修訂標籤)；逾2年未更新(4年未修，預計115提案)</t>
         </is>
       </c>
     </row>
@@ -17847,7 +18675,7 @@
       </c>
       <c r="G39" s="103" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>V</t>
         </is>
       </c>
       <c r="H39" s="103" t="inlineStr">
@@ -17860,10 +18688,14 @@
           <t>研究暨產學發展處</t>
         </is>
       </c>
-      <c r="J39" s="103" t="n"/>
+      <c r="J39" s="103" t="inlineStr">
+        <is>
+          <t>105.10.5</t>
+        </is>
+      </c>
       <c r="K39" s="75" t="inlineStr">
         <is>
-          <t>無特別說明</t>
+          <t>逾2年未更新(10年未修，預計115提案)</t>
         </is>
       </c>
     </row>
@@ -17893,7 +18725,7 @@
       </c>
       <c r="F40" s="103" t="inlineStr">
         <is>
-          <t>V</t>
+          <t>X</t>
         </is>
       </c>
       <c r="G40" s="103" t="inlineStr">
@@ -17911,10 +18743,14 @@
           <t>研究暨產學發展處</t>
         </is>
       </c>
-      <c r="J40" s="103" t="n"/>
+      <c r="J40" s="103" t="inlineStr">
+        <is>
+          <t>114.9.3</t>
+        </is>
+      </c>
       <c r="K40" s="75" t="inlineStr">
         <is>
-          <t>無特別說明</t>
+          <t>格式瑕疵(含各式顏色標記)</t>
         </is>
       </c>
     </row>
@@ -17949,7 +18785,7 @@
       </c>
       <c r="G41" s="103" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>V</t>
         </is>
       </c>
       <c r="H41" s="103" t="inlineStr">
@@ -17962,10 +18798,14 @@
           <t>研究暨產學發展處</t>
         </is>
       </c>
-      <c r="J41" s="103" t="n"/>
+      <c r="J41" s="103" t="inlineStr">
+        <is>
+          <t>112.3.8</t>
+        </is>
+      </c>
       <c r="K41" s="75" t="inlineStr">
         <is>
-          <t>無特別說明</t>
+          <t>逾2年未更新(3年未修，預計115提案)</t>
         </is>
       </c>
     </row>
@@ -18170,7 +19010,7 @@
       </c>
       <c r="G4" s="97" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>V</t>
         </is>
       </c>
       <c r="H4" s="97" t="inlineStr">
@@ -18183,10 +19023,14 @@
           <t>國際處</t>
         </is>
       </c>
-      <c r="J4" s="38" t="n"/>
+      <c r="J4" s="38" t="inlineStr">
+        <is>
+          <t>105.9.30</t>
+        </is>
+      </c>
       <c r="K4" s="38" t="inlineStr">
         <is>
-          <t>無特別說明</t>
+          <t>逾2年未更新(10年未修，預計115提案)</t>
         </is>
       </c>
     </row>
@@ -18221,12 +19065,12 @@
       </c>
       <c r="G5" s="97" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>V</t>
         </is>
       </c>
       <c r="H5" s="97" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>V</t>
         </is>
       </c>
       <c r="I5" s="38" t="inlineStr">
@@ -18234,10 +19078,14 @@
           <t>國際處</t>
         </is>
       </c>
-      <c r="J5" s="38" t="n"/>
+      <c r="J5" s="38" t="inlineStr">
+        <is>
+          <t>109.3.25</t>
+        </is>
+      </c>
       <c r="K5" s="38" t="inlineStr">
         <is>
-          <t>無特別說明</t>
+          <t>逾2年未更新(6年未修，預計115提案)；配合組織規程修訂(科技部→國家科學及技術委員會(國科會))</t>
         </is>
       </c>
     </row>
@@ -18272,7 +19120,7 @@
       </c>
       <c r="G6" s="35" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>V</t>
         </is>
       </c>
       <c r="H6" s="35" t="inlineStr">
@@ -18285,10 +19133,14 @@
           <t>國際處</t>
         </is>
       </c>
-      <c r="J6" s="38" t="n"/>
+      <c r="J6" s="38" t="inlineStr">
+        <is>
+          <t>105.9.30</t>
+        </is>
+      </c>
       <c r="K6" s="38" t="inlineStr">
         <is>
-          <t>無特別說明</t>
+          <t>逾2年未更新(10年未修，預計115提案)</t>
         </is>
       </c>
     </row>
@@ -18336,7 +19188,11 @@
           <t>國際處</t>
         </is>
       </c>
-      <c r="J7" s="38" t="n"/>
+      <c r="J7" s="38" t="inlineStr">
+        <is>
+          <t>114.6.26</t>
+        </is>
+      </c>
       <c r="K7" s="38" t="inlineStr">
         <is>
           <t>無特別說明</t>
@@ -18374,7 +19230,7 @@
       </c>
       <c r="G8" s="97" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>V</t>
         </is>
       </c>
       <c r="H8" s="97" t="inlineStr">
@@ -18387,10 +19243,14 @@
           <t>國際處</t>
         </is>
       </c>
-      <c r="J8" s="38" t="n"/>
+      <c r="J8" s="38" t="inlineStr">
+        <is>
+          <t>111.11.30</t>
+        </is>
+      </c>
       <c r="K8" s="38" t="inlineStr">
         <is>
-          <t>無特別說明</t>
+          <t>逾2年未更新(4年未修，預計115提案)</t>
         </is>
       </c>
     </row>
@@ -18425,7 +19285,7 @@
       </c>
       <c r="G9" s="97" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>V</t>
         </is>
       </c>
       <c r="H9" s="97" t="inlineStr">
@@ -18438,10 +19298,14 @@
           <t>國際處</t>
         </is>
       </c>
-      <c r="J9" s="38" t="n"/>
+      <c r="J9" s="38" t="inlineStr">
+        <is>
+          <t>110.3.10</t>
+        </is>
+      </c>
       <c r="K9" s="38" t="inlineStr">
         <is>
-          <t>無特別說明</t>
+          <t>逾2年未更新(5年未修，預計115提案)</t>
         </is>
       </c>
     </row>
@@ -18476,7 +19340,7 @@
       </c>
       <c r="G10" s="97" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>V</t>
         </is>
       </c>
       <c r="H10" s="97" t="inlineStr">
@@ -18489,10 +19353,14 @@
           <t>國際處</t>
         </is>
       </c>
-      <c r="J10" s="38" t="n"/>
+      <c r="J10" s="38" t="inlineStr">
+        <is>
+          <t>111.6.8</t>
+        </is>
+      </c>
       <c r="K10" s="38" t="inlineStr">
         <is>
-          <t>無特別說明</t>
+          <t>逾2年未更新(4年未修，預計115提案)</t>
         </is>
       </c>
     </row>
@@ -18522,7 +19390,7 @@
       </c>
       <c r="F11" s="35" t="inlineStr">
         <is>
-          <t>V</t>
+          <t>X</t>
         </is>
       </c>
       <c r="G11" s="97" t="inlineStr">
@@ -18540,10 +19408,14 @@
           <t>國際處</t>
         </is>
       </c>
-      <c r="J11" s="38" t="n"/>
+      <c r="J11" s="38" t="inlineStr">
+        <is>
+          <t>114.12.5</t>
+        </is>
+      </c>
       <c r="K11" s="38" t="inlineStr">
         <is>
-          <t>無特別說明</t>
+          <t>格式瑕疵(含各式顏色標記)</t>
         </is>
       </c>
     </row>
@@ -18578,7 +19450,7 @@
       </c>
       <c r="G12" s="97" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>V</t>
         </is>
       </c>
       <c r="H12" s="97" t="inlineStr">
@@ -18591,10 +19463,14 @@
           <t>國際處</t>
         </is>
       </c>
-      <c r="J12" s="38" t="n"/>
+      <c r="J12" s="38" t="inlineStr">
+        <is>
+          <t>111.7.20</t>
+        </is>
+      </c>
       <c r="K12" s="38" t="inlineStr">
         <is>
-          <t>無特別說明</t>
+          <t>逾2年未更新(4年未修，預計115提案)</t>
         </is>
       </c>
     </row>
@@ -18642,7 +19518,11 @@
           <t>國際處</t>
         </is>
       </c>
-      <c r="J13" s="38" t="n"/>
+      <c r="J13" s="38" t="inlineStr">
+        <is>
+          <t>113.4.29</t>
+        </is>
+      </c>
       <c r="K13" s="38" t="inlineStr">
         <is>
           <t>無特別說明</t>
@@ -18680,7 +19560,7 @@
       </c>
       <c r="G14" s="97" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>V</t>
         </is>
       </c>
       <c r="H14" s="97" t="inlineStr">
@@ -18693,10 +19573,14 @@
           <t>國際處</t>
         </is>
       </c>
-      <c r="J14" s="38" t="n"/>
+      <c r="J14" s="38" t="inlineStr">
+        <is>
+          <t>112.10.18</t>
+        </is>
+      </c>
       <c r="K14" s="38" t="inlineStr">
         <is>
-          <t>無特別說明</t>
+          <t>逾2年未更新(3年未修，預計115提案)</t>
         </is>
       </c>
     </row>
@@ -18744,7 +19628,11 @@
           <t>國際處</t>
         </is>
       </c>
-      <c r="J15" s="38" t="n"/>
+      <c r="J15" s="38" t="inlineStr">
+        <is>
+          <t>114.6.26</t>
+        </is>
+      </c>
       <c r="K15" s="38" t="inlineStr">
         <is>
           <t>無特別說明</t>
@@ -18795,7 +19683,11 @@
           <t>國際處</t>
         </is>
       </c>
-      <c r="J16" s="38" t="n"/>
+      <c r="J16" s="38" t="inlineStr">
+        <is>
+          <t>114.6.26</t>
+        </is>
+      </c>
       <c r="K16" s="38" t="inlineStr">
         <is>
           <t>無特別說明</t>
@@ -18846,7 +19738,11 @@
           <t>國際處</t>
         </is>
       </c>
-      <c r="J17" s="38" t="n"/>
+      <c r="J17" s="38" t="inlineStr">
+        <is>
+          <t>114.6.26</t>
+        </is>
+      </c>
       <c r="K17" s="38" t="inlineStr">
         <is>
           <t>無特別說明</t>
@@ -18897,7 +19793,11 @@
           <t>國際處</t>
         </is>
       </c>
-      <c r="J18" s="38" t="n"/>
+      <c r="J18" s="38" t="inlineStr">
+        <is>
+          <t>114.12.31</t>
+        </is>
+      </c>
       <c r="K18" s="38" t="inlineStr">
         <is>
           <t>無特別說明</t>
@@ -19116,7 +20016,11 @@
           <t>圖資處</t>
         </is>
       </c>
-      <c r="J4" s="38" t="n"/>
+      <c r="J4" s="38" t="inlineStr">
+        <is>
+          <t>115.6.30</t>
+        </is>
+      </c>
       <c r="K4" s="38" t="inlineStr">
         <is>
           <t>無特別說明</t>
@@ -19154,7 +20058,7 @@
       </c>
       <c r="G5" s="35" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>V</t>
         </is>
       </c>
       <c r="H5" s="35" t="inlineStr">
@@ -19167,10 +20071,14 @@
           <t>圖資處</t>
         </is>
       </c>
-      <c r="J5" s="38" t="n"/>
+      <c r="J5" s="38" t="inlineStr">
+        <is>
+          <t>105.11.2</t>
+        </is>
+      </c>
       <c r="K5" s="38" t="inlineStr">
         <is>
-          <t>無特別說明</t>
+          <t>逾2年未更新(10年未修，預計115提案)</t>
         </is>
       </c>
     </row>
@@ -19205,7 +20113,7 @@
       </c>
       <c r="G6" s="97" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>V</t>
         </is>
       </c>
       <c r="H6" s="97" t="inlineStr">
@@ -19218,10 +20126,14 @@
           <t>圖資處</t>
         </is>
       </c>
-      <c r="J6" s="38" t="n"/>
+      <c r="J6" s="38" t="inlineStr">
+        <is>
+          <t>106.1.18</t>
+        </is>
+      </c>
       <c r="K6" s="38" t="inlineStr">
         <is>
-          <t>無特別說明</t>
+          <t>逾2年未更新(9年未修，預計115提案)</t>
         </is>
       </c>
     </row>
@@ -19256,7 +20168,7 @@
       </c>
       <c r="G7" s="97" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>V</t>
         </is>
       </c>
       <c r="H7" s="97" t="inlineStr">
@@ -19269,10 +20181,14 @@
           <t>圖資處</t>
         </is>
       </c>
-      <c r="J7" s="38" t="n"/>
+      <c r="J7" s="38" t="inlineStr">
+        <is>
+          <t>106.1.18</t>
+        </is>
+      </c>
       <c r="K7" s="38" t="inlineStr">
         <is>
-          <t>無特別說明</t>
+          <t>逾2年未更新(9年未修，預計115提案)</t>
         </is>
       </c>
     </row>
@@ -19307,7 +20223,7 @@
       </c>
       <c r="G8" s="97" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>V</t>
         </is>
       </c>
       <c r="H8" s="97" t="inlineStr">
@@ -19320,10 +20236,14 @@
           <t>圖資處</t>
         </is>
       </c>
-      <c r="J8" s="38" t="n"/>
+      <c r="J8" s="38" t="inlineStr">
+        <is>
+          <t>111.12.23</t>
+        </is>
+      </c>
       <c r="K8" s="38" t="inlineStr">
         <is>
-          <t>無特別說明</t>
+          <t>逾2年未更新(4年未修，預計115提案)</t>
         </is>
       </c>
     </row>
@@ -19358,7 +20278,7 @@
       </c>
       <c r="G9" s="97" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>V</t>
         </is>
       </c>
       <c r="H9" s="97" t="inlineStr">
@@ -19371,10 +20291,14 @@
           <t>圖資處</t>
         </is>
       </c>
-      <c r="J9" s="38" t="n"/>
+      <c r="J9" s="38" t="inlineStr">
+        <is>
+          <t>105.9.30</t>
+        </is>
+      </c>
       <c r="K9" s="38" t="inlineStr">
         <is>
-          <t>無特別說明</t>
+          <t>逾2年未更新(10年未修，預計115提案)</t>
         </is>
       </c>
     </row>
@@ -19409,7 +20333,7 @@
       </c>
       <c r="G10" s="35" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>V</t>
         </is>
       </c>
       <c r="H10" s="35" t="inlineStr">
@@ -19422,10 +20346,14 @@
           <t>圖資處</t>
         </is>
       </c>
-      <c r="J10" s="50" t="n"/>
+      <c r="J10" s="50" t="inlineStr">
+        <is>
+          <t>112.11.30</t>
+        </is>
+      </c>
       <c r="K10" s="49" t="inlineStr">
         <is>
-          <t>無特別說明</t>
+          <t>逾2年未更新(3年未修，預計115提案)</t>
         </is>
       </c>
     </row>
@@ -19460,7 +20388,7 @@
       </c>
       <c r="G11" s="35" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>V</t>
         </is>
       </c>
       <c r="H11" s="35" t="inlineStr">
@@ -19476,7 +20404,7 @@
       <c r="J11" s="38" t="n"/>
       <c r="K11" s="38" t="inlineStr">
         <is>
-          <t>無特別說明</t>
+          <t>逾2年未更新(多年未修，預計115提案)</t>
         </is>
       </c>
     </row>
@@ -19511,7 +20439,7 @@
       </c>
       <c r="G12" s="35" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>V</t>
         </is>
       </c>
       <c r="H12" s="35" t="inlineStr">
@@ -19524,10 +20452,14 @@
           <t>圖資處</t>
         </is>
       </c>
-      <c r="J12" s="38" t="n"/>
+      <c r="J12" s="38" t="inlineStr">
+        <is>
+          <t>111.12.23</t>
+        </is>
+      </c>
       <c r="K12" s="38" t="inlineStr">
         <is>
-          <t>無特別說明</t>
+          <t>逾2年未更新(4年未修，預計115提案)</t>
         </is>
       </c>
     </row>
@@ -19575,7 +20507,11 @@
           <t>圖資處</t>
         </is>
       </c>
-      <c r="J13" s="38" t="n"/>
+      <c r="J13" s="38" t="inlineStr">
+        <is>
+          <t>115.6.30</t>
+        </is>
+      </c>
       <c r="K13" s="38" t="inlineStr">
         <is>
           <t>無特別說明</t>
@@ -19613,7 +20549,7 @@
       </c>
       <c r="G14" s="35" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>V</t>
         </is>
       </c>
       <c r="H14" s="35" t="inlineStr">
@@ -19626,10 +20562,14 @@
           <t>圖資處</t>
         </is>
       </c>
-      <c r="J14" s="38" t="n"/>
+      <c r="J14" s="38" t="inlineStr">
+        <is>
+          <t>111.12.23</t>
+        </is>
+      </c>
       <c r="K14" s="38" t="inlineStr">
         <is>
-          <t>無特別說明</t>
+          <t>逾2年未更新(4年未修，預計115提案)</t>
         </is>
       </c>
     </row>
@@ -19664,7 +20604,7 @@
       </c>
       <c r="G15" s="35" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>V</t>
         </is>
       </c>
       <c r="H15" s="35" t="inlineStr">
@@ -19677,10 +20617,14 @@
           <t>圖資處</t>
         </is>
       </c>
-      <c r="J15" s="38" t="n"/>
+      <c r="J15" s="38" t="inlineStr">
+        <is>
+          <t>112.10.18</t>
+        </is>
+      </c>
       <c r="K15" s="38" t="inlineStr">
         <is>
-          <t>無特別說明</t>
+          <t>逾2年未更新(3年未修，預計115提案)</t>
         </is>
       </c>
     </row>
@@ -19715,7 +20659,7 @@
       </c>
       <c r="G16" s="35" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>V</t>
         </is>
       </c>
       <c r="H16" s="35" t="inlineStr">
@@ -19728,10 +20672,14 @@
           <t>圖資處</t>
         </is>
       </c>
-      <c r="J16" s="38" t="n"/>
+      <c r="J16" s="38" t="inlineStr">
+        <is>
+          <t>104.12.30</t>
+        </is>
+      </c>
       <c r="K16" s="38" t="inlineStr">
         <is>
-          <t>無特別說明</t>
+          <t>逾2年未更新(11年未修，預計115提案)</t>
         </is>
       </c>
     </row>
@@ -19766,7 +20714,7 @@
       </c>
       <c r="G17" s="35" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>V</t>
         </is>
       </c>
       <c r="H17" s="35" t="inlineStr">
@@ -19779,10 +20727,14 @@
           <t>圖資處</t>
         </is>
       </c>
-      <c r="J17" s="38" t="n"/>
+      <c r="J17" s="38" t="inlineStr">
+        <is>
+          <t>110.12.14</t>
+        </is>
+      </c>
       <c r="K17" s="38" t="inlineStr">
         <is>
-          <t>無特別說明</t>
+          <t>逾2年未更新(5年未修，預計115提案)</t>
         </is>
       </c>
     </row>
@@ -19817,7 +20769,7 @@
       </c>
       <c r="G18" s="35" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>V</t>
         </is>
       </c>
       <c r="H18" s="35" t="inlineStr">
@@ -19830,10 +20782,14 @@
           <t>圖資處</t>
         </is>
       </c>
-      <c r="J18" s="38" t="n"/>
+      <c r="J18" s="38" t="inlineStr">
+        <is>
+          <t>105.9.30</t>
+        </is>
+      </c>
       <c r="K18" s="38" t="inlineStr">
         <is>
-          <t>無特別說明</t>
+          <t>逾2年未更新(10年未修，預計115提案)</t>
         </is>
       </c>
     </row>
@@ -19868,7 +20824,7 @@
       </c>
       <c r="G19" s="35" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>V</t>
         </is>
       </c>
       <c r="H19" s="35" t="inlineStr">
@@ -19881,10 +20837,14 @@
           <t>圖資處</t>
         </is>
       </c>
-      <c r="J19" s="38" t="n"/>
+      <c r="J19" s="38" t="inlineStr">
+        <is>
+          <t>106.2.13</t>
+        </is>
+      </c>
       <c r="K19" s="38" t="inlineStr">
         <is>
-          <t>無特別說明</t>
+          <t>逾2年未更新(9年未修，預計115提案)</t>
         </is>
       </c>
     </row>
@@ -19919,7 +20879,7 @@
       </c>
       <c r="G20" s="35" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>V</t>
         </is>
       </c>
       <c r="H20" s="35" t="inlineStr">
@@ -19932,10 +20892,14 @@
           <t>圖資處</t>
         </is>
       </c>
-      <c r="J20" s="38" t="n"/>
+      <c r="J20" s="38" t="inlineStr">
+        <is>
+          <t>105.9.13</t>
+        </is>
+      </c>
       <c r="K20" s="38" t="inlineStr">
         <is>
-          <t>無特別說明</t>
+          <t>逾2年未更新(10年未修，預計115提案)</t>
         </is>
       </c>
     </row>
@@ -19970,7 +20934,7 @@
       </c>
       <c r="G21" s="35" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>V</t>
         </is>
       </c>
       <c r="H21" s="35" t="inlineStr">
@@ -19983,10 +20947,14 @@
           <t>圖資處</t>
         </is>
       </c>
-      <c r="J21" s="38" t="n"/>
+      <c r="J21" s="38" t="inlineStr">
+        <is>
+          <t>106.1.12</t>
+        </is>
+      </c>
       <c r="K21" s="38" t="inlineStr">
         <is>
-          <t>無特別說明</t>
+          <t>逾2年未更新(9年未修，預計115提案)</t>
         </is>
       </c>
     </row>
@@ -20034,7 +21002,11 @@
           <t>圖資處</t>
         </is>
       </c>
-      <c r="J22" s="38" t="n"/>
+      <c r="J22" s="38" t="inlineStr">
+        <is>
+          <t>113.6.25</t>
+        </is>
+      </c>
       <c r="K22" s="38" t="inlineStr">
         <is>
           <t>無特別說明</t>
@@ -20072,7 +21044,7 @@
       </c>
       <c r="G23" s="35" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>V</t>
         </is>
       </c>
       <c r="H23" s="35" t="inlineStr">
@@ -20085,10 +21057,14 @@
           <t>圖資處</t>
         </is>
       </c>
-      <c r="J23" s="38" t="n"/>
+      <c r="J23" s="38" t="inlineStr">
+        <is>
+          <t>106.1.18</t>
+        </is>
+      </c>
       <c r="K23" s="38" t="inlineStr">
         <is>
-          <t>無特別說明</t>
+          <t>逾2年未更新(9年未修，預計115提案)</t>
         </is>
       </c>
     </row>
@@ -20123,7 +21099,7 @@
       </c>
       <c r="G24" s="35" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>V</t>
         </is>
       </c>
       <c r="H24" s="35" t="inlineStr">
@@ -20136,10 +21112,14 @@
           <t>圖資處</t>
         </is>
       </c>
-      <c r="J24" s="38" t="n"/>
+      <c r="J24" s="38" t="inlineStr">
+        <is>
+          <t>106.1.18</t>
+        </is>
+      </c>
       <c r="K24" s="38" t="inlineStr">
         <is>
-          <t>無特別說明</t>
+          <t>逾2年未更新(9年未修，預計115提案)</t>
         </is>
       </c>
     </row>
@@ -20187,7 +21167,11 @@
           <t>圖資處</t>
         </is>
       </c>
-      <c r="J25" s="38" t="n"/>
+      <c r="J25" s="38" t="inlineStr">
+        <is>
+          <t>115.6.30</t>
+        </is>
+      </c>
       <c r="K25" s="38" t="inlineStr">
         <is>
           <t>無特別說明</t>
@@ -20238,7 +21222,11 @@
           <t>圖資處</t>
         </is>
       </c>
-      <c r="J26" s="38" t="n"/>
+      <c r="J26" s="38" t="inlineStr">
+        <is>
+          <t>115.1.20</t>
+        </is>
+      </c>
       <c r="K26" s="38" t="inlineStr">
         <is>
           <t>無特別說明</t>
@@ -20423,7 +21411,7 @@
       </c>
       <c r="F4" s="97" t="inlineStr">
         <is>
-          <t>V</t>
+          <t>X</t>
         </is>
       </c>
       <c r="G4" s="97" t="inlineStr">
@@ -20441,10 +21429,14 @@
           <t>秘書室</t>
         </is>
       </c>
-      <c r="J4" s="38" t="n"/>
+      <c r="J4" s="38" t="inlineStr">
+        <is>
+          <t>114.6.18</t>
+        </is>
+      </c>
       <c r="K4" s="38" t="inlineStr">
         <is>
-          <t>無特別說明</t>
+          <t>格式瑕疵(含各式顏色標記)</t>
         </is>
       </c>
     </row>
@@ -20479,7 +21471,7 @@
       </c>
       <c r="G5" s="97" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>V</t>
         </is>
       </c>
       <c r="H5" s="97" t="inlineStr">
@@ -20492,10 +21484,14 @@
           <t>秘書室</t>
         </is>
       </c>
-      <c r="J5" s="38" t="n"/>
+      <c r="J5" s="38" t="inlineStr">
+        <is>
+          <t>112.6.7</t>
+        </is>
+      </c>
       <c r="K5" s="38" t="inlineStr">
         <is>
-          <t>無特別說明</t>
+          <t>逾2年未更新(3年未修，預計115提案)</t>
         </is>
       </c>
     </row>
@@ -20530,7 +21526,7 @@
       </c>
       <c r="G6" s="97" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>V</t>
         </is>
       </c>
       <c r="H6" s="97" t="inlineStr">
@@ -20543,10 +21539,14 @@
           <t>秘書室</t>
         </is>
       </c>
-      <c r="J6" s="38" t="n"/>
+      <c r="J6" s="38" t="inlineStr">
+        <is>
+          <t>99.7.23</t>
+        </is>
+      </c>
       <c r="K6" s="38" t="inlineStr">
         <is>
-          <t>無特別說明</t>
+          <t>逾2年未更新(16年未修，預計115提案)</t>
         </is>
       </c>
     </row>
@@ -20581,7 +21581,7 @@
       </c>
       <c r="G7" s="97" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>V</t>
         </is>
       </c>
       <c r="H7" s="97" t="inlineStr">
@@ -20594,10 +21594,14 @@
           <t>秘書室</t>
         </is>
       </c>
-      <c r="J7" s="38" t="n"/>
+      <c r="J7" s="38" t="inlineStr">
+        <is>
+          <t>104.10.25</t>
+        </is>
+      </c>
       <c r="K7" s="38" t="inlineStr">
         <is>
-          <t>無特別說明</t>
+          <t>逾2年未更新(11年未修，預計115提案)</t>
         </is>
       </c>
     </row>
@@ -20645,7 +21649,11 @@
           <t>秘書室</t>
         </is>
       </c>
-      <c r="J8" s="38" t="n"/>
+      <c r="J8" s="38" t="inlineStr">
+        <is>
+          <t>114.2.12</t>
+        </is>
+      </c>
       <c r="K8" s="38" t="inlineStr">
         <is>
           <t>無特別說明</t>
@@ -20678,7 +21686,7 @@
       </c>
       <c r="F9" s="97" t="inlineStr">
         <is>
-          <t>V</t>
+          <t>X</t>
         </is>
       </c>
       <c r="G9" s="97" t="inlineStr">
@@ -20688,7 +21696,7 @@
       </c>
       <c r="H9" s="97" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>V</t>
         </is>
       </c>
       <c r="I9" s="38" t="inlineStr">
@@ -20696,10 +21704,14 @@
           <t>秘書室</t>
         </is>
       </c>
-      <c r="J9" s="38" t="n"/>
+      <c r="J9" s="38" t="inlineStr">
+        <is>
+          <t>114.12.5</t>
+        </is>
+      </c>
       <c r="K9" s="38" t="inlineStr">
         <is>
-          <t>無特別說明</t>
+          <t>格式瑕疵(含各式顏色標記)；配合組織規程修訂(衛生保健組→健康中心;軍訓室→學生事務處生活輔導組/校安中心)</t>
         </is>
       </c>
     </row>
@@ -20734,7 +21746,7 @@
       </c>
       <c r="G10" s="97" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>V</t>
         </is>
       </c>
       <c r="H10" s="97" t="inlineStr">
@@ -20747,10 +21759,14 @@
           <t>秘書室</t>
         </is>
       </c>
-      <c r="J10" s="49" t="n"/>
+      <c r="J10" s="49" t="inlineStr">
+        <is>
+          <t>112.1.11</t>
+        </is>
+      </c>
       <c r="K10" s="38" t="inlineStr">
         <is>
-          <t>無特別說明</t>
+          <t>逾2年未更新(3年未修，預計115提案)</t>
         </is>
       </c>
     </row>
@@ -20798,7 +21814,11 @@
           <t>秘書室</t>
         </is>
       </c>
-      <c r="J11" s="38" t="n"/>
+      <c r="J11" s="38" t="inlineStr">
+        <is>
+          <t>114.6.18</t>
+        </is>
+      </c>
       <c r="K11" s="38" t="inlineStr">
         <is>
           <t>無特別說明</t>
@@ -20836,7 +21856,7 @@
       </c>
       <c r="G12" s="97" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>V</t>
         </is>
       </c>
       <c r="H12" s="97" t="inlineStr">
@@ -20849,10 +21869,14 @@
           <t>秘書室</t>
         </is>
       </c>
-      <c r="J12" s="38" t="n"/>
+      <c r="J12" s="38" t="inlineStr">
+        <is>
+          <t>102.9.11</t>
+        </is>
+      </c>
       <c r="K12" s="38" t="inlineStr">
         <is>
-          <t>無特別說明</t>
+          <t>逾2年未更新(13年未修，預計115提案)</t>
         </is>
       </c>
     </row>
@@ -20887,7 +21911,7 @@
       </c>
       <c r="G13" s="97" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>V</t>
         </is>
       </c>
       <c r="H13" s="97" t="inlineStr">
@@ -20900,10 +21924,14 @@
           <t>秘書室</t>
         </is>
       </c>
-      <c r="J13" s="38" t="n"/>
+      <c r="J13" s="38" t="inlineStr">
+        <is>
+          <t>102.10.9</t>
+        </is>
+      </c>
       <c r="K13" s="38" t="inlineStr">
         <is>
-          <t>無特別說明</t>
+          <t>逾2年未更新(13年未修，預計115提案)</t>
         </is>
       </c>
     </row>
@@ -21115,7 +22143,11 @@
           <t>人事室</t>
         </is>
       </c>
-      <c r="J4" s="38" t="n"/>
+      <c r="J4" s="38" t="inlineStr">
+        <is>
+          <t>115.7.1</t>
+        </is>
+      </c>
       <c r="K4" s="38" t="inlineStr">
         <is>
           <t>無特別說明</t>
@@ -21153,7 +22185,7 @@
       </c>
       <c r="G5" s="97" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>V</t>
         </is>
       </c>
       <c r="H5" s="97" t="inlineStr">
@@ -21166,10 +22198,14 @@
           <t>人事室</t>
         </is>
       </c>
-      <c r="J5" s="38" t="n"/>
+      <c r="J5" s="38" t="inlineStr">
+        <is>
+          <t>112.1.11</t>
+        </is>
+      </c>
       <c r="K5" s="38" t="inlineStr">
         <is>
-          <t>無特別說明</t>
+          <t>逾2年未更新(3年未修，預計115提案)</t>
         </is>
       </c>
     </row>
@@ -21204,7 +22240,7 @@
       </c>
       <c r="G6" s="97" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>V</t>
         </is>
       </c>
       <c r="H6" s="97" t="inlineStr">
@@ -21217,10 +22253,14 @@
           <t>人事室</t>
         </is>
       </c>
-      <c r="J6" s="38" t="n"/>
+      <c r="J6" s="38" t="inlineStr">
+        <is>
+          <t>109.9.16</t>
+        </is>
+      </c>
       <c r="K6" s="38" t="inlineStr">
         <is>
-          <t>無特別說明</t>
+          <t>逾2年未更新(6年未修，預計115提案)</t>
         </is>
       </c>
     </row>
@@ -21255,7 +22295,7 @@
       </c>
       <c r="G7" s="97" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>V</t>
         </is>
       </c>
       <c r="H7" s="97" t="inlineStr">
@@ -21268,10 +22308,14 @@
           <t>人事室</t>
         </is>
       </c>
-      <c r="J7" s="38" t="n"/>
+      <c r="J7" s="38" t="inlineStr">
+        <is>
+          <t>100.11.2</t>
+        </is>
+      </c>
       <c r="K7" s="38" t="inlineStr">
         <is>
-          <t>無特別說明</t>
+          <t>逾2年未更新(15年未修，預計115提案)</t>
         </is>
       </c>
     </row>
@@ -21306,7 +22350,7 @@
       </c>
       <c r="G8" s="97" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>V</t>
         </is>
       </c>
       <c r="H8" s="97" t="inlineStr">
@@ -21319,10 +22363,14 @@
           <t>人事室</t>
         </is>
       </c>
-      <c r="J8" s="38" t="n"/>
+      <c r="J8" s="38" t="inlineStr">
+        <is>
+          <t>112.1.11</t>
+        </is>
+      </c>
       <c r="K8" s="38" t="inlineStr">
         <is>
-          <t>無特別說明</t>
+          <t>逾2年未更新(3年未修，預計115提案)</t>
         </is>
       </c>
     </row>
@@ -21370,7 +22418,11 @@
           <t>人事室</t>
         </is>
       </c>
-      <c r="J9" s="38" t="n"/>
+      <c r="J9" s="38" t="inlineStr">
+        <is>
+          <t>114.6.18</t>
+        </is>
+      </c>
       <c r="K9" s="38" t="inlineStr">
         <is>
           <t>無特別說明</t>
@@ -21413,7 +22465,7 @@
       </c>
       <c r="H10" s="97" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>V</t>
         </is>
       </c>
       <c r="I10" s="38" t="inlineStr">
@@ -21421,10 +22473,14 @@
           <t>人事室</t>
         </is>
       </c>
-      <c r="J10" s="38" t="n"/>
+      <c r="J10" s="38" t="inlineStr">
+        <is>
+          <t>115.8.25</t>
+        </is>
+      </c>
       <c r="K10" s="38" t="inlineStr">
         <is>
-          <t>無特別說明</t>
+          <t>配合組織規程修訂(研究發展處→研究暨產學發展處)</t>
         </is>
       </c>
     </row>
@@ -21472,7 +22528,11 @@
           <t>人事室</t>
         </is>
       </c>
-      <c r="J11" s="38" t="n"/>
+      <c r="J11" s="38" t="inlineStr">
+        <is>
+          <t>115.6.11</t>
+        </is>
+      </c>
       <c r="K11" s="38" t="inlineStr">
         <is>
           <t>無特別說明</t>
@@ -21523,7 +22583,11 @@
           <t>人事室</t>
         </is>
       </c>
-      <c r="J12" s="38" t="n"/>
+      <c r="J12" s="38" t="inlineStr">
+        <is>
+          <t>114.7.15</t>
+        </is>
+      </c>
       <c r="K12" s="38" t="inlineStr">
         <is>
           <t>無特別說明</t>
@@ -21574,7 +22638,11 @@
           <t>人事室</t>
         </is>
       </c>
-      <c r="J13" s="38" t="n"/>
+      <c r="J13" s="38" t="inlineStr">
+        <is>
+          <t>113.1.10</t>
+        </is>
+      </c>
       <c r="K13" s="38" t="inlineStr">
         <is>
           <t>無特別說明</t>
@@ -21612,7 +22680,7 @@
       </c>
       <c r="G14" s="97" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>V</t>
         </is>
       </c>
       <c r="H14" s="97" t="inlineStr">
@@ -21625,10 +22693,14 @@
           <t>人事室</t>
         </is>
       </c>
-      <c r="J14" s="38" t="n"/>
+      <c r="J14" s="38" t="inlineStr">
+        <is>
+          <t>97.12.31</t>
+        </is>
+      </c>
       <c r="K14" s="38" t="inlineStr">
         <is>
-          <t>無特別說明</t>
+          <t>逾2年未更新(18年未修，預計115提案)</t>
         </is>
       </c>
     </row>
@@ -21658,12 +22730,12 @@
       </c>
       <c r="F15" s="97" t="inlineStr">
         <is>
-          <t>V</t>
+          <t>X</t>
         </is>
       </c>
       <c r="G15" s="97" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>V</t>
         </is>
       </c>
       <c r="H15" s="97" t="inlineStr">
@@ -21676,10 +22748,14 @@
           <t>人事室</t>
         </is>
       </c>
-      <c r="J15" s="38" t="n"/>
+      <c r="J15" s="38" t="inlineStr">
+        <is>
+          <t>108.8.20</t>
+        </is>
+      </c>
       <c r="K15" s="38" t="inlineStr">
         <is>
-          <t>無特別說明</t>
+          <t>格式瑕疵(含各式顏色標記)；逾2年未更新(7年未修，預計115提案)</t>
         </is>
       </c>
     </row>
@@ -21709,7 +22785,7 @@
       </c>
       <c r="F16" s="97" t="inlineStr">
         <is>
-          <t>V</t>
+          <t>X</t>
         </is>
       </c>
       <c r="G16" s="97" t="inlineStr">
@@ -21727,10 +22803,14 @@
           <t>人事室</t>
         </is>
       </c>
-      <c r="J16" s="38" t="n"/>
+      <c r="J16" s="38" t="inlineStr">
+        <is>
+          <t>115.1.14</t>
+        </is>
+      </c>
       <c r="K16" s="38" t="inlineStr">
         <is>
-          <t>無特別說明</t>
+          <t>格式瑕疵(含各式顏色標記)</t>
         </is>
       </c>
     </row>
@@ -21778,7 +22858,11 @@
           <t>人事室</t>
         </is>
       </c>
-      <c r="J17" s="38" t="n"/>
+      <c r="J17" s="38" t="inlineStr">
+        <is>
+          <t>114.12.31</t>
+        </is>
+      </c>
       <c r="K17" s="38" t="inlineStr">
         <is>
           <t>無特別說明</t>
@@ -21829,7 +22913,11 @@
           <t>人事室</t>
         </is>
       </c>
-      <c r="J18" s="38" t="n"/>
+      <c r="J18" s="38" t="inlineStr">
+        <is>
+          <t>114.1.15</t>
+        </is>
+      </c>
       <c r="K18" s="38" t="inlineStr">
         <is>
           <t>無特別說明</t>
@@ -21867,7 +22955,7 @@
       </c>
       <c r="G19" s="97" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>V</t>
         </is>
       </c>
       <c r="H19" s="97" t="inlineStr">
@@ -21880,10 +22968,14 @@
           <t>人事室</t>
         </is>
       </c>
-      <c r="J19" s="38" t="n"/>
+      <c r="J19" s="38" t="inlineStr">
+        <is>
+          <t>112.5.10</t>
+        </is>
+      </c>
       <c r="K19" s="38" t="inlineStr">
         <is>
-          <t>無特別說明</t>
+          <t>逾2年未更新(3年未修，預計115提案)</t>
         </is>
       </c>
     </row>
@@ -21913,12 +23005,12 @@
       </c>
       <c r="F20" s="97" t="inlineStr">
         <is>
-          <t>V</t>
+          <t>X</t>
         </is>
       </c>
       <c r="G20" s="97" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>V</t>
         </is>
       </c>
       <c r="H20" s="97" t="inlineStr">
@@ -21931,10 +23023,14 @@
           <t>人事室</t>
         </is>
       </c>
-      <c r="J20" s="38" t="n"/>
+      <c r="J20" s="38" t="inlineStr">
+        <is>
+          <t>98.1.16</t>
+        </is>
+      </c>
       <c r="K20" s="38" t="inlineStr">
         <is>
-          <t>無特別說明</t>
+          <t>格式瑕疵(含各式顏色標記)；逾2年未更新(17年未修，預計115提案)</t>
         </is>
       </c>
     </row>
@@ -21982,7 +23078,11 @@
           <t>人事室</t>
         </is>
       </c>
-      <c r="J21" s="38" t="n"/>
+      <c r="J21" s="38" t="inlineStr">
+        <is>
+          <t>115.6.3</t>
+        </is>
+      </c>
       <c r="K21" s="38" t="inlineStr">
         <is>
           <t>無特別說明</t>
@@ -22020,7 +23120,7 @@
       </c>
       <c r="G22" s="97" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>V</t>
         </is>
       </c>
       <c r="H22" s="97" t="inlineStr">
@@ -22033,10 +23133,14 @@
           <t>人事室</t>
         </is>
       </c>
-      <c r="J22" s="38" t="n"/>
+      <c r="J22" s="38" t="inlineStr">
+        <is>
+          <t>97.12.31</t>
+        </is>
+      </c>
       <c r="K22" s="38" t="inlineStr">
         <is>
-          <t>無特別說明</t>
+          <t>逾2年未更新(18年未修，預計115提案)</t>
         </is>
       </c>
     </row>
@@ -22071,7 +23175,7 @@
       </c>
       <c r="G23" s="97" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>V</t>
         </is>
       </c>
       <c r="H23" s="97" t="inlineStr">
@@ -22084,10 +23188,14 @@
           <t>人事室</t>
         </is>
       </c>
-      <c r="J23" s="38" t="n"/>
+      <c r="J23" s="38" t="inlineStr">
+        <is>
+          <t>112.10.2</t>
+        </is>
+      </c>
       <c r="K23" s="38" t="inlineStr">
         <is>
-          <t>無特別說明</t>
+          <t>逾2年未更新(3年未修，預計115提案)</t>
         </is>
       </c>
     </row>
@@ -22122,7 +23230,7 @@
       </c>
       <c r="G24" s="97" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>V</t>
         </is>
       </c>
       <c r="H24" s="97" t="inlineStr">
@@ -22135,10 +23243,14 @@
           <t>人事室</t>
         </is>
       </c>
-      <c r="J24" s="38" t="n"/>
+      <c r="J24" s="38" t="inlineStr">
+        <is>
+          <t>106.10.2</t>
+        </is>
+      </c>
       <c r="K24" s="38" t="inlineStr">
         <is>
-          <t>無特別說明</t>
+          <t>逾2年未更新(9年未修，預計115提案)</t>
         </is>
       </c>
     </row>
@@ -22186,7 +23298,11 @@
           <t>人事室</t>
         </is>
       </c>
-      <c r="J25" s="38" t="n"/>
+      <c r="J25" s="38" t="inlineStr">
+        <is>
+          <t>113.11.13</t>
+        </is>
+      </c>
       <c r="K25" s="38" t="inlineStr">
         <is>
           <t>無特別說明</t>
@@ -22237,7 +23353,11 @@
           <t>人事室</t>
         </is>
       </c>
-      <c r="J26" s="38" t="n"/>
+      <c r="J26" s="38" t="inlineStr">
+        <is>
+          <t>114.4.30</t>
+        </is>
+      </c>
       <c r="K26" s="38" t="inlineStr">
         <is>
           <t>無特別說明</t>
@@ -22288,7 +23408,11 @@
           <t>人事室</t>
         </is>
       </c>
-      <c r="J27" s="38" t="n"/>
+      <c r="J27" s="38" t="inlineStr">
+        <is>
+          <t>114.9.3</t>
+        </is>
+      </c>
       <c r="K27" s="38" t="inlineStr">
         <is>
           <t>無特別說明</t>
@@ -22326,7 +23450,7 @@
       </c>
       <c r="G28" s="97" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>V</t>
         </is>
       </c>
       <c r="H28" s="97" t="inlineStr">
@@ -22339,10 +23463,14 @@
           <t>人事室</t>
         </is>
       </c>
-      <c r="J28" s="38" t="n"/>
+      <c r="J28" s="38" t="inlineStr">
+        <is>
+          <t>106.4.12</t>
+        </is>
+      </c>
       <c r="K28" s="38" t="inlineStr">
         <is>
-          <t>無特別說明</t>
+          <t>逾2年未更新(9年未修，預計115提案)</t>
         </is>
       </c>
     </row>
@@ -22372,12 +23500,12 @@
       </c>
       <c r="F29" s="97" t="inlineStr">
         <is>
-          <t>V</t>
+          <t>X</t>
         </is>
       </c>
       <c r="G29" s="97" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>V</t>
         </is>
       </c>
       <c r="H29" s="97" t="inlineStr">
@@ -22390,10 +23518,14 @@
           <t>人事室</t>
         </is>
       </c>
-      <c r="J29" s="38" t="n"/>
+      <c r="J29" s="38" t="inlineStr">
+        <is>
+          <t>97.12.31</t>
+        </is>
+      </c>
       <c r="K29" s="38" t="inlineStr">
         <is>
-          <t>無特別說明</t>
+          <t>格式瑕疵(含各式顏色標記)；逾2年未更新(18年未修，預計115提案)</t>
         </is>
       </c>
     </row>
@@ -22428,7 +23560,7 @@
       </c>
       <c r="G30" s="97" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>V</t>
         </is>
       </c>
       <c r="H30" s="97" t="inlineStr">
@@ -22441,10 +23573,14 @@
           <t>人事室</t>
         </is>
       </c>
-      <c r="J30" s="38" t="n"/>
+      <c r="J30" s="38" t="inlineStr">
+        <is>
+          <t>102.12.5</t>
+        </is>
+      </c>
       <c r="K30" s="38" t="inlineStr">
         <is>
-          <t>無特別說明</t>
+          <t>逾2年未更新(13年未修，預計115提案)</t>
         </is>
       </c>
     </row>
@@ -22479,7 +23615,7 @@
       </c>
       <c r="G31" s="97" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>V</t>
         </is>
       </c>
       <c r="H31" s="97" t="inlineStr">
@@ -22492,10 +23628,14 @@
           <t>人事室</t>
         </is>
       </c>
-      <c r="J31" s="38" t="n"/>
+      <c r="J31" s="38" t="inlineStr">
+        <is>
+          <t>103.10.1</t>
+        </is>
+      </c>
       <c r="K31" s="38" t="inlineStr">
         <is>
-          <t>無特別說明</t>
+          <t>逾2年未更新(12年未修，預計115提案)</t>
         </is>
       </c>
     </row>
@@ -22525,7 +23665,7 @@
       </c>
       <c r="F32" s="97" t="inlineStr">
         <is>
-          <t>V</t>
+          <t>X</t>
         </is>
       </c>
       <c r="G32" s="97" t="inlineStr">
@@ -22543,10 +23683,14 @@
           <t>人事室</t>
         </is>
       </c>
-      <c r="J32" s="38" t="n"/>
+      <c r="J32" s="38" t="inlineStr">
+        <is>
+          <t>114.10.22</t>
+        </is>
+      </c>
       <c r="K32" s="38" t="inlineStr">
         <is>
-          <t>無特別說明</t>
+          <t>格式瑕疵(含各式顏色標記)</t>
         </is>
       </c>
     </row>
@@ -22581,7 +23725,7 @@
       </c>
       <c r="G33" s="97" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>V</t>
         </is>
       </c>
       <c r="H33" s="97" t="inlineStr">
@@ -22594,10 +23738,14 @@
           <t>人事室</t>
         </is>
       </c>
-      <c r="J33" s="38" t="n"/>
+      <c r="J33" s="38" t="inlineStr">
+        <is>
+          <t>105.6.22</t>
+        </is>
+      </c>
       <c r="K33" s="38" t="inlineStr">
         <is>
-          <t>無特別說明</t>
+          <t>逾2年未更新(10年未修，預計115提案)</t>
         </is>
       </c>
     </row>
@@ -22645,7 +23793,11 @@
           <t>人事室</t>
         </is>
       </c>
-      <c r="J34" s="38" t="n"/>
+      <c r="J34" s="38" t="inlineStr">
+        <is>
+          <t>115.6.11</t>
+        </is>
+      </c>
       <c r="K34" s="38" t="inlineStr">
         <is>
           <t>無特別說明</t>
@@ -22683,7 +23835,7 @@
       </c>
       <c r="G35" s="97" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>V</t>
         </is>
       </c>
       <c r="H35" s="97" t="inlineStr">
@@ -22696,10 +23848,14 @@
           <t>人事室</t>
         </is>
       </c>
-      <c r="J35" s="38" t="n"/>
+      <c r="J35" s="38" t="inlineStr">
+        <is>
+          <t>112.1.11</t>
+        </is>
+      </c>
       <c r="K35" s="38" t="inlineStr">
         <is>
-          <t>無特別說明</t>
+          <t>逾2年未更新(3年未修，預計115提案)</t>
         </is>
       </c>
     </row>
@@ -22734,7 +23890,7 @@
       </c>
       <c r="G36" s="97" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>V</t>
         </is>
       </c>
       <c r="H36" s="97" t="inlineStr">
@@ -22747,10 +23903,14 @@
           <t>人事室</t>
         </is>
       </c>
-      <c r="J36" s="38" t="n"/>
+      <c r="J36" s="38" t="inlineStr">
+        <is>
+          <t>111.11.3</t>
+        </is>
+      </c>
       <c r="K36" s="38" t="inlineStr">
         <is>
-          <t>無特別說明</t>
+          <t>逾2年未更新(4年未修，預計115提案)</t>
         </is>
       </c>
     </row>
@@ -22785,7 +23945,7 @@
       </c>
       <c r="G37" s="97" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>V</t>
         </is>
       </c>
       <c r="H37" s="97" t="inlineStr">
@@ -22798,10 +23958,14 @@
           <t>人事室</t>
         </is>
       </c>
-      <c r="J37" s="38" t="n"/>
+      <c r="J37" s="38" t="inlineStr">
+        <is>
+          <t>98.1.16</t>
+        </is>
+      </c>
       <c r="K37" s="38" t="inlineStr">
         <is>
-          <t>無特別說明</t>
+          <t>逾2年未更新(17年未修，預計115提案)</t>
         </is>
       </c>
     </row>
@@ -22831,7 +23995,7 @@
       </c>
       <c r="F38" s="97" t="inlineStr">
         <is>
-          <t>V</t>
+          <t>X</t>
         </is>
       </c>
       <c r="G38" s="97" t="inlineStr">
@@ -22849,10 +24013,14 @@
           <t>人事室</t>
         </is>
       </c>
-      <c r="J38" s="38" t="n"/>
+      <c r="J38" s="38" t="inlineStr">
+        <is>
+          <t>115.1.14</t>
+        </is>
+      </c>
       <c r="K38" s="38" t="inlineStr">
         <is>
-          <t>無特別說明</t>
+          <t>格式瑕疵(含各式顏色標記)</t>
         </is>
       </c>
     </row>
@@ -22887,7 +24055,7 @@
       </c>
       <c r="G39" s="97" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>V</t>
         </is>
       </c>
       <c r="H39" s="97" t="inlineStr">
@@ -22900,10 +24068,14 @@
           <t>人事室</t>
         </is>
       </c>
-      <c r="J39" s="38" t="n"/>
+      <c r="J39" s="38" t="inlineStr">
+        <is>
+          <t>106.2.22</t>
+        </is>
+      </c>
       <c r="K39" s="38" t="inlineStr">
         <is>
-          <t>無特別說明</t>
+          <t>逾2年未更新(9年未修，預計115提案)</t>
         </is>
       </c>
     </row>
@@ -22951,7 +24123,11 @@
           <t>人事室</t>
         </is>
       </c>
-      <c r="J40" s="38" t="n"/>
+      <c r="J40" s="38" t="inlineStr">
+        <is>
+          <t>114.1.15</t>
+        </is>
+      </c>
       <c r="K40" s="38" t="inlineStr">
         <is>
           <t>無特別說明</t>
@@ -23002,7 +24178,11 @@
           <t>人事室</t>
         </is>
       </c>
-      <c r="J41" s="38" t="n"/>
+      <c r="J41" s="38" t="inlineStr">
+        <is>
+          <t>113.11.13</t>
+        </is>
+      </c>
       <c r="K41" s="38" t="inlineStr">
         <is>
           <t>無特別說明</t>
@@ -23040,7 +24220,7 @@
       </c>
       <c r="G42" s="97" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>V</t>
         </is>
       </c>
       <c r="H42" s="97" t="inlineStr">
@@ -23053,10 +24233,14 @@
           <t>人事室</t>
         </is>
       </c>
-      <c r="J42" s="38" t="n"/>
+      <c r="J42" s="38" t="inlineStr">
+        <is>
+          <t>106.2.22</t>
+        </is>
+      </c>
       <c r="K42" s="38" t="inlineStr">
         <is>
-          <t>無特別說明</t>
+          <t>逾2年未更新(9年未修，預計115提案)</t>
         </is>
       </c>
     </row>
@@ -23091,7 +24275,7 @@
       </c>
       <c r="G43" s="97" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>V</t>
         </is>
       </c>
       <c r="H43" s="97" t="inlineStr">
@@ -23104,10 +24288,14 @@
           <t>人事室</t>
         </is>
       </c>
-      <c r="J43" s="38" t="n"/>
+      <c r="J43" s="38" t="inlineStr">
+        <is>
+          <t>104.1.21</t>
+        </is>
+      </c>
       <c r="K43" s="38" t="inlineStr">
         <is>
-          <t>無特別說明</t>
+          <t>逾2年未更新(11年未修，預計115提案)</t>
         </is>
       </c>
     </row>
@@ -23137,7 +24325,7 @@
       </c>
       <c r="F44" s="97" t="inlineStr">
         <is>
-          <t>V</t>
+          <t>X</t>
         </is>
       </c>
       <c r="G44" s="97" t="inlineStr">
@@ -23155,10 +24343,14 @@
           <t>人事室</t>
         </is>
       </c>
-      <c r="J44" s="38" t="n"/>
+      <c r="J44" s="38" t="inlineStr">
+        <is>
+          <t>114.6.18</t>
+        </is>
+      </c>
       <c r="K44" s="38" t="inlineStr">
         <is>
-          <t>無特別說明</t>
+          <t>格式瑕疵(含各式顏色標記)</t>
         </is>
       </c>
     </row>
@@ -23193,7 +24385,7 @@
       </c>
       <c r="G45" s="97" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>V</t>
         </is>
       </c>
       <c r="H45" s="97" t="inlineStr">
@@ -23206,10 +24398,14 @@
           <t>人事室</t>
         </is>
       </c>
-      <c r="J45" s="38" t="n"/>
+      <c r="J45" s="38" t="inlineStr">
+        <is>
+          <t>101.6.25</t>
+        </is>
+      </c>
       <c r="K45" s="38" t="inlineStr">
         <is>
-          <t>無特別說明</t>
+          <t>逾2年未更新(14年未修，預計115提案)</t>
         </is>
       </c>
     </row>
@@ -23244,7 +24440,7 @@
       </c>
       <c r="G46" s="97" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>V</t>
         </is>
       </c>
       <c r="H46" s="97" t="inlineStr">
@@ -23257,10 +24453,14 @@
           <t>人事室</t>
         </is>
       </c>
-      <c r="J46" s="38" t="n"/>
+      <c r="J46" s="38" t="inlineStr">
+        <is>
+          <t>104.12.11</t>
+        </is>
+      </c>
       <c r="K46" s="38" t="inlineStr">
         <is>
-          <t>無特別說明</t>
+          <t>逾2年未更新(11年未修，預計115提案)</t>
         </is>
       </c>
     </row>
@@ -23295,7 +24495,7 @@
       </c>
       <c r="G47" s="97" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>V</t>
         </is>
       </c>
       <c r="H47" s="97" t="inlineStr">
@@ -23308,10 +24508,14 @@
           <t>人事室</t>
         </is>
       </c>
-      <c r="J47" s="38" t="n"/>
+      <c r="J47" s="38" t="inlineStr">
+        <is>
+          <t>102.1.2</t>
+        </is>
+      </c>
       <c r="K47" s="38" t="inlineStr">
         <is>
-          <t>無特別說明</t>
+          <t>逾2年未更新(13年未修，預計115提案)</t>
         </is>
       </c>
     </row>
@@ -23359,7 +24563,11 @@
           <t>人事室</t>
         </is>
       </c>
-      <c r="J48" s="38" t="n"/>
+      <c r="J48" s="38" t="inlineStr">
+        <is>
+          <t>114.10.22</t>
+        </is>
+      </c>
       <c r="K48" s="38" t="inlineStr">
         <is>
           <t>無特別說明</t>
@@ -23397,7 +24605,7 @@
       </c>
       <c r="G49" s="97" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>V</t>
         </is>
       </c>
       <c r="H49" s="97" t="inlineStr">
@@ -23410,10 +24618,14 @@
           <t>人事室</t>
         </is>
       </c>
-      <c r="J49" s="38" t="n"/>
+      <c r="J49" s="38" t="inlineStr">
+        <is>
+          <t>105.10.5</t>
+        </is>
+      </c>
       <c r="K49" s="38" t="inlineStr">
         <is>
-          <t>無特別說明</t>
+          <t>逾2年未更新(10年未修，預計115提案)</t>
         </is>
       </c>
     </row>
@@ -23443,7 +24655,7 @@
       </c>
       <c r="F50" s="97" t="inlineStr">
         <is>
-          <t>V</t>
+          <t>X</t>
         </is>
       </c>
       <c r="G50" s="97" t="inlineStr">
@@ -23461,10 +24673,14 @@
           <t>人事室</t>
         </is>
       </c>
-      <c r="J50" s="38" t="n"/>
+      <c r="J50" s="38" t="inlineStr">
+        <is>
+          <t>115.3.18</t>
+        </is>
+      </c>
       <c r="K50" s="38" t="inlineStr">
         <is>
-          <t>無特別說明</t>
+          <t>格式瑕疵(含各式顏色標記)</t>
         </is>
       </c>
     </row>
@@ -23499,7 +24715,7 @@
       </c>
       <c r="G51" s="97" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>V</t>
         </is>
       </c>
       <c r="H51" s="97" t="inlineStr">
@@ -23512,10 +24728,14 @@
           <t>人事室</t>
         </is>
       </c>
-      <c r="J51" s="38" t="n"/>
+      <c r="J51" s="38" t="inlineStr">
+        <is>
+          <t>107.12.26</t>
+        </is>
+      </c>
       <c r="K51" s="38" t="inlineStr">
         <is>
-          <t>無特別說明</t>
+          <t>逾2年未更新(8年未修，預計115提案)</t>
         </is>
       </c>
     </row>
@@ -23550,7 +24770,7 @@
       </c>
       <c r="G52" s="97" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>V</t>
         </is>
       </c>
       <c r="H52" s="97" t="inlineStr">
@@ -23563,10 +24783,14 @@
           <t>人事室</t>
         </is>
       </c>
-      <c r="J52" s="38" t="n"/>
+      <c r="J52" s="38" t="inlineStr">
+        <is>
+          <t>105.9.30</t>
+        </is>
+      </c>
       <c r="K52" s="38" t="inlineStr">
         <is>
-          <t>無特別說明</t>
+          <t>逾2年未更新(10年未修，預計115提案)</t>
         </is>
       </c>
     </row>
@@ -23601,7 +24825,7 @@
       </c>
       <c r="G53" s="97" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>V</t>
         </is>
       </c>
       <c r="H53" s="97" t="inlineStr">
@@ -23614,10 +24838,14 @@
           <t>人事室</t>
         </is>
       </c>
-      <c r="J53" s="38" t="n"/>
+      <c r="J53" s="38" t="inlineStr">
+        <is>
+          <t>104.11.4</t>
+        </is>
+      </c>
       <c r="K53" s="38" t="inlineStr">
         <is>
-          <t>無特別說明</t>
+          <t>逾2年未更新(11年未修，預計115提案)</t>
         </is>
       </c>
     </row>
@@ -23652,7 +24880,7 @@
       </c>
       <c r="G54" s="97" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>V</t>
         </is>
       </c>
       <c r="H54" s="97" t="inlineStr">
@@ -23665,10 +24893,14 @@
           <t>人事室</t>
         </is>
       </c>
-      <c r="J54" s="38" t="n"/>
+      <c r="J54" s="38" t="inlineStr">
+        <is>
+          <t>104.10.14</t>
+        </is>
+      </c>
       <c r="K54" s="38" t="inlineStr">
         <is>
-          <t>無特別說明</t>
+          <t>逾2年未更新(11年未修，預計115提案)</t>
         </is>
       </c>
     </row>
@@ -23703,7 +24935,7 @@
       </c>
       <c r="G55" s="97" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>V</t>
         </is>
       </c>
       <c r="H55" s="97" t="inlineStr">
@@ -23716,10 +24948,14 @@
           <t>人事室</t>
         </is>
       </c>
-      <c r="J55" s="38" t="n"/>
+      <c r="J55" s="38" t="inlineStr">
+        <is>
+          <t>112.9.6</t>
+        </is>
+      </c>
       <c r="K55" s="38" t="inlineStr">
         <is>
-          <t>無特別說明</t>
+          <t>逾2年未更新(3年未修，預計115提案)</t>
         </is>
       </c>
     </row>
@@ -23749,12 +24985,12 @@
       </c>
       <c r="F56" s="97" t="inlineStr">
         <is>
-          <t>V</t>
+          <t>X</t>
         </is>
       </c>
       <c r="G56" s="97" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>V</t>
         </is>
       </c>
       <c r="H56" s="97" t="inlineStr">
@@ -23767,10 +25003,14 @@
           <t>人事室</t>
         </is>
       </c>
-      <c r="J56" s="38" t="n"/>
+      <c r="J56" s="38" t="inlineStr">
+        <is>
+          <t>108.6.19</t>
+        </is>
+      </c>
       <c r="K56" s="38" t="inlineStr">
         <is>
-          <t>無特別說明</t>
+          <t>格式瑕疵(含各式顏色標記)；逾2年未更新(7年未修，預計115提案)</t>
         </is>
       </c>
     </row>
@@ -23805,7 +25045,7 @@
       </c>
       <c r="G57" s="97" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>V</t>
         </is>
       </c>
       <c r="H57" s="97" t="inlineStr">
@@ -23818,10 +25058,14 @@
           <t>人事室</t>
         </is>
       </c>
-      <c r="J57" s="38" t="n"/>
+      <c r="J57" s="38" t="inlineStr">
+        <is>
+          <t>105.6.8</t>
+        </is>
+      </c>
       <c r="K57" s="38" t="inlineStr">
         <is>
-          <t>無特別說明</t>
+          <t>逾2年未更新(10年未修，預計115提案)</t>
         </is>
       </c>
     </row>
@@ -23856,12 +25100,12 @@
       </c>
       <c r="G58" s="97" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>V</t>
         </is>
       </c>
       <c r="H58" s="97" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>V</t>
         </is>
       </c>
       <c r="I58" s="38" t="inlineStr">
@@ -23869,10 +25113,14 @@
           <t>人事室</t>
         </is>
       </c>
-      <c r="J58" s="38" t="n"/>
+      <c r="J58" s="38" t="inlineStr">
+        <is>
+          <t>105.6.22</t>
+        </is>
+      </c>
       <c r="K58" s="38" t="inlineStr">
         <is>
-          <t>無特別說明</t>
+          <t>逾2年未更新(10年未修，預計115提案)；配合組織規程修訂(研究發展處→研究暨產學發展處)</t>
         </is>
       </c>
     </row>
@@ -23902,12 +25150,12 @@
       </c>
       <c r="F59" s="97" t="inlineStr">
         <is>
-          <t>V</t>
+          <t>X</t>
         </is>
       </c>
       <c r="G59" s="97" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>V</t>
         </is>
       </c>
       <c r="H59" s="97" t="inlineStr">
@@ -23920,10 +25168,14 @@
           <t>人事室</t>
         </is>
       </c>
-      <c r="J59" s="38" t="n"/>
+      <c r="J59" s="38" t="inlineStr">
+        <is>
+          <t>105.6.22</t>
+        </is>
+      </c>
       <c r="K59" s="38" t="inlineStr">
         <is>
-          <t>無特別說明</t>
+          <t>格式瑕疵(含各式顏色標記)；逾2年未更新(10年未修，預計115提案)</t>
         </is>
       </c>
     </row>
@@ -23953,12 +25205,12 @@
       </c>
       <c r="F60" s="97" t="inlineStr">
         <is>
-          <t>V</t>
+          <t>X</t>
         </is>
       </c>
       <c r="G60" s="97" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>V</t>
         </is>
       </c>
       <c r="H60" s="97" t="inlineStr">
@@ -23971,10 +25223,14 @@
           <t>人事室</t>
         </is>
       </c>
-      <c r="J60" s="38" t="n"/>
+      <c r="J60" s="38" t="inlineStr">
+        <is>
+          <t>106.1.11</t>
+        </is>
+      </c>
       <c r="K60" s="38" t="inlineStr">
         <is>
-          <t>無特別說明</t>
+          <t>格式瑕疵(含各式顏色標記)；逾2年未更新(9年未修，預計115提案)</t>
         </is>
       </c>
     </row>
@@ -24009,7 +25265,7 @@
       </c>
       <c r="G61" s="97" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>V</t>
         </is>
       </c>
       <c r="H61" s="97" t="inlineStr">
@@ -24022,10 +25278,14 @@
           <t>人事室</t>
         </is>
       </c>
-      <c r="J61" s="38" t="n"/>
+      <c r="J61" s="38" t="inlineStr">
+        <is>
+          <t>110.6.16</t>
+        </is>
+      </c>
       <c r="K61" s="38" t="inlineStr">
         <is>
-          <t>無特別說明</t>
+          <t>逾2年未更新(5年未修，預計115提案)</t>
         </is>
       </c>
     </row>
@@ -24055,7 +25315,7 @@
       </c>
       <c r="F62" s="97" t="inlineStr">
         <is>
-          <t>V</t>
+          <t>X</t>
         </is>
       </c>
       <c r="G62" s="97" t="inlineStr">
@@ -24073,10 +25333,14 @@
           <t>人事室</t>
         </is>
       </c>
-      <c r="J62" s="38" t="n"/>
+      <c r="J62" s="38" t="inlineStr">
+        <is>
+          <t>113.7.9</t>
+        </is>
+      </c>
       <c r="K62" s="38" t="inlineStr">
         <is>
-          <t>無特別說明</t>
+          <t>格式瑕疵(含各式顏色標記)</t>
         </is>
       </c>
     </row>
@@ -24106,12 +25370,12 @@
       </c>
       <c r="F63" s="97" t="inlineStr">
         <is>
-          <t>V</t>
+          <t>X</t>
         </is>
       </c>
       <c r="G63" s="97" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>V</t>
         </is>
       </c>
       <c r="H63" s="97" t="inlineStr">
@@ -24124,10 +25388,14 @@
           <t>人事室</t>
         </is>
       </c>
-      <c r="J63" s="38" t="n"/>
+      <c r="J63" s="38" t="inlineStr">
+        <is>
+          <t>108.4.15</t>
+        </is>
+      </c>
       <c r="K63" s="38" t="inlineStr">
         <is>
-          <t>無特別說明</t>
+          <t>格式瑕疵(含各式顏色標記)；逾2年未更新(7年未修，預計115提案)</t>
         </is>
       </c>
     </row>
@@ -24175,7 +25443,11 @@
           <t>人事室</t>
         </is>
       </c>
-      <c r="J64" s="38" t="n"/>
+      <c r="J64" s="38" t="inlineStr">
+        <is>
+          <t>114.1.15</t>
+        </is>
+      </c>
       <c r="K64" s="38" t="inlineStr">
         <is>
           <t>無特別說明</t>
@@ -24226,7 +25498,11 @@
           <t>人事室</t>
         </is>
       </c>
-      <c r="J65" s="38" t="n"/>
+      <c r="J65" s="38" t="inlineStr">
+        <is>
+          <t>113.10.30</t>
+        </is>
+      </c>
       <c r="K65" s="38" t="inlineStr">
         <is>
           <t>無特別說明</t>
@@ -24264,7 +25540,7 @@
       </c>
       <c r="G66" s="97" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>V</t>
         </is>
       </c>
       <c r="H66" s="97" t="inlineStr">
@@ -24277,10 +25553,14 @@
           <t>人事室</t>
         </is>
       </c>
-      <c r="J66" s="38" t="n"/>
+      <c r="J66" s="38" t="inlineStr">
+        <is>
+          <t>110.1.6</t>
+        </is>
+      </c>
       <c r="K66" s="38" t="inlineStr">
         <is>
-          <t>無特別說明</t>
+          <t>逾2年未更新(5年未修，預計115提案)</t>
         </is>
       </c>
     </row>
@@ -24310,12 +25590,12 @@
       </c>
       <c r="F67" s="97" t="inlineStr">
         <is>
-          <t>V</t>
+          <t>X</t>
         </is>
       </c>
       <c r="G67" s="97" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>V</t>
         </is>
       </c>
       <c r="H67" s="97" t="inlineStr">
@@ -24328,10 +25608,14 @@
           <t>人事室</t>
         </is>
       </c>
-      <c r="J67" s="38" t="n"/>
+      <c r="J67" s="38" t="inlineStr">
+        <is>
+          <t>111.6.15</t>
+        </is>
+      </c>
       <c r="K67" s="38" t="inlineStr">
         <is>
-          <t>無特別說明</t>
+          <t>格式瑕疵(含各式顏色標記)；逾2年未更新(4年未修，預計115提案)</t>
         </is>
       </c>
     </row>
@@ -24361,7 +25645,7 @@
       </c>
       <c r="F68" s="97" t="inlineStr">
         <is>
-          <t>V</t>
+          <t>X</t>
         </is>
       </c>
       <c r="G68" s="97" t="inlineStr">
@@ -24379,10 +25663,14 @@
           <t>人事室</t>
         </is>
       </c>
-      <c r="J68" s="38" t="n"/>
+      <c r="J68" s="38" t="inlineStr">
+        <is>
+          <t>113.11.13</t>
+        </is>
+      </c>
       <c r="K68" s="38" t="inlineStr">
         <is>
-          <t>無特別說明</t>
+          <t>格式瑕疵(含各式顏色標記)</t>
         </is>
       </c>
     </row>

--- a/115年法規清單檢核表_已完成檢核.xlsx
+++ b/115年法規清單檢核表_已完成檢核.xlsx
@@ -18,15 +18,14 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="會計室" sheetId="10" state="visible" r:id="rId10"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="稽核室" sheetId="11" state="visible" r:id="rId11"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="公共事務暨校友服務室" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="校務研究暨規劃室" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="體育暨健康促進中心" sheetId="14" state="visible" r:id="rId14"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="環境安全衛生中心" sheetId="15" state="visible" r:id="rId15"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="推廣教育中心" sheetId="16" state="visible" r:id="rId16"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="共同教育中心" sheetId="17" state="visible" r:id="rId17"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="老化及疾病預防研究中心" sheetId="18" state="visible" r:id="rId18"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="護理學院" sheetId="19" state="visible" r:id="rId19"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="幼兒保育暨產業系" sheetId="20" state="visible" r:id="rId20"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="健康美容系" sheetId="21" state="visible" r:id="rId21"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="體育暨健康促進中心" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="環境安全衛生中心" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="推廣教育中心" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="共同教育中心" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="老化及疾病預防研究中心" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="護理學院" sheetId="18" state="visible" r:id="rId18"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="幼兒保育暨產業系" sheetId="19" state="visible" r:id="rId19"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="健康美容系" sheetId="20" state="visible" r:id="rId20"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Titles" localSheetId="1">'教務處'!$1:$3</definedName>
@@ -39,14 +38,13 @@
     <definedName name="_xlnm.Print_Titles" localSheetId="8">'人事室'!$1:$3</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="9">'會計室'!$1:$3</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="11">'公共事務暨校友服務室'!$1:$3</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="12">'校務研究暨規劃室'!$1:$3</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="13">'體育暨健康促進中心'!$1:$3</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="14">'環境安全衛生中心'!$1:$3</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="15">'推廣教育中心'!$1:$3</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="16">'共同教育中心'!$1:$3</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="17">'老化及疾病預防研究中心'!$1:$3</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="19">'幼兒保育暨產業系'!$1:$3</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="20">'健康美容系'!$1:$3</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="12">'體育暨健康促進中心'!$1:$3</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="13">'環境安全衛生中心'!$1:$3</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="14">'推廣教育中心'!$1:$3</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="15">'共同教育中心'!$1:$3</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="16">'老化及疾病預防研究中心'!$1:$3</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="18">'幼兒保育暨產業系'!$1:$3</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="19">'健康美容系'!$1:$3</definedName>
   </definedNames>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
 </workbook>
@@ -361,7 +359,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="121">
+  <cellXfs count="122">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -715,6 +713,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -2806,7 +2807,7 @@
       </c>
       <c r="J4" s="38" t="inlineStr">
         <is>
-          <t>115.2.25</t>
+          <t>115.02.25</t>
         </is>
       </c>
       <c r="K4" s="38" t="inlineStr">
@@ -2861,7 +2862,7 @@
       </c>
       <c r="J5" s="38" t="inlineStr">
         <is>
-          <t>112.4.12</t>
+          <t>112.04.12</t>
         </is>
       </c>
       <c r="K5" s="38" t="inlineStr">
@@ -2916,7 +2917,7 @@
       </c>
       <c r="J6" s="38" t="inlineStr">
         <is>
-          <t>111.10.5</t>
+          <t>111.10.05</t>
         </is>
       </c>
       <c r="K6" s="38" t="inlineStr">
@@ -2961,7 +2962,7 @@
       </c>
       <c r="H7" s="97" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>V</t>
         </is>
       </c>
       <c r="I7" s="38" t="inlineStr">
@@ -2971,12 +2972,12 @@
       </c>
       <c r="J7" s="38" t="inlineStr">
         <is>
-          <t>111.10.5</t>
+          <t>111.10.05</t>
         </is>
       </c>
       <c r="K7" s="38" t="inlineStr">
         <is>
-          <t>逾2年未更新(4年未修，預計115提案)</t>
+          <t>逾2年未更新(4年未修，預計115提案)；配合組織規程修訂(研究暨產學發展處→研發與永續發展處)</t>
         </is>
       </c>
     </row>
@@ -3182,7 +3183,7 @@
       </c>
       <c r="J4" s="38" t="inlineStr">
         <is>
-          <t>105.9.7</t>
+          <t>105.09.07</t>
         </is>
       </c>
       <c r="K4" s="38" t="inlineStr">
@@ -3237,7 +3238,7 @@
       </c>
       <c r="J5" s="38" t="inlineStr">
         <is>
-          <t>114.3.26</t>
+          <t>114.03.26</t>
         </is>
       </c>
       <c r="K5" s="38" t="inlineStr">
@@ -3292,7 +3293,7 @@
       </c>
       <c r="J6" s="38" t="inlineStr">
         <is>
-          <t>114.11.5</t>
+          <t>114.11.05</t>
         </is>
       </c>
       <c r="K6" s="38" t="inlineStr">
@@ -3347,7 +3348,7 @@
       </c>
       <c r="J7" s="38" t="inlineStr">
         <is>
-          <t>114.11.5</t>
+          <t>114.11.05</t>
         </is>
       </c>
       <c r="K7" s="38" t="inlineStr">
@@ -3559,7 +3560,7 @@
       </c>
       <c r="J4" s="38" t="inlineStr">
         <is>
-          <t>114.9.3</t>
+          <t>114.09.03</t>
         </is>
       </c>
       <c r="K4" s="38" t="inlineStr">
@@ -3614,7 +3615,7 @@
       </c>
       <c r="J5" s="38" t="inlineStr">
         <is>
-          <t>113.5.22</t>
+          <t>113.05.22</t>
         </is>
       </c>
       <c r="K5" s="38" t="inlineStr">
@@ -3669,7 +3670,7 @@
       </c>
       <c r="J6" s="38" t="inlineStr">
         <is>
-          <t>108.3.13</t>
+          <t>108.03.13</t>
         </is>
       </c>
       <c r="K6" s="38" t="inlineStr">
@@ -3742,334 +3743,6 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K14"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15.6"/>
-  <cols>
-    <col width="6.77734375" customWidth="1" style="76" min="1" max="1"/>
-    <col width="12.88671875" bestFit="1" customWidth="1" style="76" min="2" max="2"/>
-    <col width="40.5546875" customWidth="1" style="67" min="3" max="3"/>
-    <col width="15.77734375" customWidth="1" style="76" min="4" max="8"/>
-    <col width="9.77734375" customWidth="1" style="76" min="9" max="9"/>
-    <col width="10.77734375" customWidth="1" style="76" min="10" max="10"/>
-    <col width="9.77734375" customWidth="1" style="76" min="11" max="11"/>
-    <col width="8.88671875" customWidth="1" style="76" min="12" max="16384"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="19.8" customHeight="1" s="113">
-      <c r="A1" s="66" t="inlineStr">
-        <is>
-          <t>校務研究暨規劃室法規清單檢核表</t>
-        </is>
-      </c>
-      <c r="B1" s="66" t="n"/>
-    </row>
-    <row r="2" ht="16.2" customHeight="1" s="113">
-      <c r="A2" s="102" t="inlineStr">
-        <is>
-          <t>序號</t>
-        </is>
-      </c>
-      <c r="B2" s="102" t="inlineStr">
-        <is>
-          <t>類別</t>
-        </is>
-      </c>
-      <c r="C2" s="104" t="inlineStr">
-        <is>
-          <t>法規名稱</t>
-        </is>
-      </c>
-      <c r="D2" s="119" t="inlineStr">
-        <is>
-          <t>現況(請勾選)</t>
-        </is>
-      </c>
-      <c r="E2" s="115" t="n"/>
-      <c r="F2" s="115" t="n"/>
-      <c r="G2" s="115" t="n"/>
-      <c r="H2" s="116" t="n"/>
-      <c r="I2" s="111" t="inlineStr">
-        <is>
-          <t>業管單位</t>
-        </is>
-      </c>
-      <c r="J2" s="101" t="inlineStr">
-        <is>
-          <t>最後一次修訂時間</t>
-        </is>
-      </c>
-      <c r="K2" s="103" t="inlineStr">
-        <is>
-          <t>備註</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="121.2" customHeight="1" s="113">
-      <c r="A3" s="117" t="n"/>
-      <c r="B3" s="117" t="n"/>
-      <c r="C3" s="117" t="n"/>
-      <c r="D3" s="70" t="inlineStr">
-        <is>
-          <t>1.是否已更新為現行最新法規版本。</t>
-        </is>
-      </c>
-      <c r="E3" s="70" t="inlineStr">
-        <is>
-          <t>2.法規名稱是否正確。</t>
-        </is>
-      </c>
-      <c r="F3" s="70" t="inlineStr">
-        <is>
-          <t>3.法規格式是否完整(須不含底線、刪除線及各式顏色標示等)。</t>
-        </is>
-      </c>
-      <c r="G3" s="70" t="inlineStr">
-        <is>
-          <t>4.若法規超過2年以上未更新，是否需要更新，並於115學年度行政會議提案。</t>
-        </is>
-      </c>
-      <c r="H3" s="70" t="inlineStr">
-        <is>
-          <t>5.因應校務會議、董事會通過之組職規程修訂案，是否需要更新，並於115學年度行政會議提案。</t>
-        </is>
-      </c>
-      <c r="I3" s="117" t="n"/>
-      <c r="J3" s="117" t="n"/>
-      <c r="K3" s="117" t="n"/>
-    </row>
-    <row r="4" ht="48.6" customFormat="1" customHeight="1" s="76">
-      <c r="A4" s="71" t="n">
-        <v>1</v>
-      </c>
-      <c r="B4" s="75" t="inlineStr">
-        <is>
-          <t>綜合性法規</t>
-        </is>
-      </c>
-      <c r="C4" s="80" t="inlineStr">
-        <is>
-          <t>輔英科技大學校務研究暨規劃室設置辦法(原：校務研究室設置辦法)</t>
-        </is>
-      </c>
-      <c r="D4" s="103" t="inlineStr">
-        <is>
-          <t>V</t>
-        </is>
-      </c>
-      <c r="E4" s="103" t="inlineStr">
-        <is>
-          <t>V</t>
-        </is>
-      </c>
-      <c r="F4" s="103" t="inlineStr">
-        <is>
-          <t>V</t>
-        </is>
-      </c>
-      <c r="G4" s="103" t="inlineStr">
-        <is>
-          <t>V</t>
-        </is>
-      </c>
-      <c r="H4" s="103" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="I4" s="80" t="inlineStr">
-        <is>
-          <t>校務研究與永續發展中心</t>
-        </is>
-      </c>
-      <c r="J4" s="75" t="inlineStr">
-        <is>
-          <t>105.10.5</t>
-        </is>
-      </c>
-      <c r="K4" s="75" t="inlineStr">
-        <is>
-          <t>預計廢止；逾2年未更新(10年未修，預計115提案)</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="48.6" customFormat="1" customHeight="1" s="76">
-      <c r="A5" s="71" t="n">
-        <v>2</v>
-      </c>
-      <c r="B5" s="75" t="inlineStr">
-        <is>
-          <t>綜合性法規</t>
-        </is>
-      </c>
-      <c r="C5" s="80" t="inlineStr">
-        <is>
-          <t>輔英科技大學永續發展委員會設置要點</t>
-        </is>
-      </c>
-      <c r="D5" s="103" t="inlineStr">
-        <is>
-          <t>V</t>
-        </is>
-      </c>
-      <c r="E5" s="103" t="inlineStr">
-        <is>
-          <t>V</t>
-        </is>
-      </c>
-      <c r="F5" s="103" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="G5" s="103" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="H5" s="103" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="I5" s="80" t="inlineStr">
-        <is>
-          <t>校務研究與永續發展中心</t>
-        </is>
-      </c>
-      <c r="J5" s="75" t="inlineStr">
-        <is>
-          <t>114.9.3</t>
-        </is>
-      </c>
-      <c r="K5" s="75" t="inlineStr">
-        <is>
-          <t>格式瑕疵(含各式顏色標記)</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="48.6" customFormat="1" customHeight="1" s="76">
-      <c r="A6" s="71" t="n">
-        <v>3</v>
-      </c>
-      <c r="B6" s="75" t="inlineStr">
-        <is>
-          <t>綜合性法規</t>
-        </is>
-      </c>
-      <c r="C6" s="80" t="inlineStr">
-        <is>
-          <t>輔英科技大學校務研究資料庫管理要點</t>
-        </is>
-      </c>
-      <c r="D6" s="103" t="inlineStr">
-        <is>
-          <t>V</t>
-        </is>
-      </c>
-      <c r="E6" s="103" t="inlineStr">
-        <is>
-          <t>V</t>
-        </is>
-      </c>
-      <c r="F6" s="103" t="inlineStr">
-        <is>
-          <t>V</t>
-        </is>
-      </c>
-      <c r="G6" s="103" t="inlineStr">
-        <is>
-          <t>V</t>
-        </is>
-      </c>
-      <c r="H6" s="103" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="I6" s="80" t="inlineStr">
-        <is>
-          <t>校務研究與永續發展中心</t>
-        </is>
-      </c>
-      <c r="J6" s="75" t="inlineStr">
-        <is>
-          <t>112.3.8</t>
-        </is>
-      </c>
-      <c r="K6" s="75" t="inlineStr">
-        <is>
-          <t>逾2年未更新(3年未修，預計115提案)</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" customFormat="1" s="76">
-      <c r="A7" s="76" t="n"/>
-      <c r="B7" s="76" t="n"/>
-      <c r="C7" s="67" t="n"/>
-      <c r="D7" s="76" t="n"/>
-      <c r="E7" s="76" t="n"/>
-      <c r="F7" s="76" t="n"/>
-      <c r="G7" s="76" t="n"/>
-      <c r="H7" s="76" t="n"/>
-    </row>
-    <row r="8" ht="16.2" customHeight="1" s="113">
-      <c r="A8" s="76" t="inlineStr">
-        <is>
-          <t>承辦人核章：</t>
-        </is>
-      </c>
-    </row>
-    <row r="9"/>
-    <row r="10"/>
-    <row r="11" ht="16.2" customHeight="1" s="113">
-      <c r="A11" s="76" t="inlineStr">
-        <is>
-          <t>二級主管核章：</t>
-        </is>
-      </c>
-    </row>
-    <row r="12"/>
-    <row r="13"/>
-    <row r="14" ht="16.2" customHeight="1" s="113">
-      <c r="A14" s="76" t="inlineStr">
-        <is>
-          <t>一級主管核章：</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="7">
-    <mergeCell ref="D2:H2"/>
-    <mergeCell ref="J2:J3"/>
-    <mergeCell ref="B2:B3"/>
-    <mergeCell ref="A2:A3"/>
-    <mergeCell ref="C2:C3"/>
-    <mergeCell ref="K2:K3"/>
-    <mergeCell ref="I2:I3"/>
-  </mergeCells>
-  <conditionalFormatting sqref="C2">
-    <cfRule type="duplicateValues" priority="2" dxfId="1" stopIfTrue="1"/>
-    <cfRule type="duplicateValues" priority="3" dxfId="1" stopIfTrue="1"/>
-    <cfRule type="duplicateValues" priority="4" dxfId="1" stopIfTrue="1"/>
-    <cfRule type="duplicateValues" priority="5" dxfId="1" stopIfTrue="1"/>
-    <cfRule type="duplicateValues" priority="6" dxfId="1" stopIfTrue="1"/>
-    <cfRule type="duplicateValues" priority="7" dxfId="1" stopIfTrue="1"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C4:C6">
-    <cfRule type="duplicateValues" priority="1" dxfId="0"/>
-  </conditionalFormatting>
-  <pageMargins left="0.7086614173228347" right="0.7086614173228347" top="0.7480314960629921" bottom="0.7480314960629921" header="0.3149606299212598" footer="0.3149606299212598"/>
-  <pageSetup orientation="landscape" paperSize="9" verticalDpi="0"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <tabColor theme="5" tint="0.5999938962981048"/>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
   <dimension ref="A1:K20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16.2"/>
   <cols>
@@ -4209,7 +3882,7 @@
       </c>
       <c r="J4" s="38" t="inlineStr">
         <is>
-          <t>114.6.18</t>
+          <t>114.06.18</t>
         </is>
       </c>
       <c r="K4" s="38" t="inlineStr">
@@ -4264,7 +3937,7 @@
       </c>
       <c r="J5" s="38" t="inlineStr">
         <is>
-          <t>111.9.6</t>
+          <t>111.09.06</t>
         </is>
       </c>
       <c r="K5" s="38" t="inlineStr">
@@ -4374,7 +4047,7 @@
       </c>
       <c r="J7" s="38" t="inlineStr">
         <is>
-          <t>111.9.6</t>
+          <t>111.09.06</t>
         </is>
       </c>
       <c r="K7" s="38" t="inlineStr">
@@ -4429,7 +4102,7 @@
       </c>
       <c r="J8" s="38" t="inlineStr">
         <is>
-          <t>111.9.6</t>
+          <t>111.09.06</t>
         </is>
       </c>
       <c r="K8" s="38" t="inlineStr">
@@ -4484,7 +4157,7 @@
       </c>
       <c r="J9" s="38" t="inlineStr">
         <is>
-          <t>110.2.3</t>
+          <t>110.02.03</t>
         </is>
       </c>
       <c r="K9" s="38" t="inlineStr">
@@ -4539,7 +4212,7 @@
       </c>
       <c r="J10" s="38" t="inlineStr">
         <is>
-          <t>111.9.6</t>
+          <t>111.09.06</t>
         </is>
       </c>
       <c r="K10" s="38" t="inlineStr">
@@ -4594,7 +4267,7 @@
       </c>
       <c r="J11" s="38" t="inlineStr">
         <is>
-          <t>108.9.25</t>
+          <t>108.09.25</t>
         </is>
       </c>
       <c r="K11" s="38" t="inlineStr">
@@ -4649,7 +4322,7 @@
       </c>
       <c r="J12" s="38" t="inlineStr">
         <is>
-          <t>113.2.2</t>
+          <t>113.02.02</t>
         </is>
       </c>
       <c r="K12" s="38" t="inlineStr">
@@ -4704,7 +4377,7 @@
       </c>
       <c r="J13" s="38" t="inlineStr">
         <is>
-          <t>113.4.26</t>
+          <t>113.04.26</t>
         </is>
       </c>
       <c r="K13" s="38" t="inlineStr">
@@ -4764,7 +4437,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor theme="5" tint="0.5999938962981048"/>
@@ -4910,7 +4583,7 @@
       </c>
       <c r="J4" s="38" t="inlineStr">
         <is>
-          <t>110.5.12</t>
+          <t>110.05.12</t>
         </is>
       </c>
       <c r="K4" s="38" t="inlineStr">
@@ -5030,7 +4703,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor theme="5" tint="0.5999938962981048"/>
@@ -5176,7 +4849,7 @@
       </c>
       <c r="J4" s="38" t="inlineStr">
         <is>
-          <t>106.5.10</t>
+          <t>106.05.10</t>
         </is>
       </c>
       <c r="K4" s="38" t="inlineStr">
@@ -5231,7 +4904,7 @@
       </c>
       <c r="J5" s="38" t="inlineStr">
         <is>
-          <t>104.12.2</t>
+          <t>104.12.02</t>
         </is>
       </c>
       <c r="K5" s="38" t="inlineStr">
@@ -5402,7 +5075,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor theme="5" tint="0.5999938962981048"/>
@@ -5548,7 +5221,7 @@
       </c>
       <c r="J4" s="38" t="inlineStr">
         <is>
-          <t>108.3.27</t>
+          <t>108.03.27</t>
         </is>
       </c>
       <c r="K4" s="53" t="inlineStr">
@@ -5603,7 +5276,7 @@
       </c>
       <c r="J5" s="38" t="inlineStr">
         <is>
-          <t>109.1.9</t>
+          <t>109.01.09</t>
         </is>
       </c>
       <c r="K5" s="53" t="inlineStr">
@@ -5658,7 +5331,7 @@
       </c>
       <c r="J6" s="38" t="inlineStr">
         <is>
-          <t>114.6.18</t>
+          <t>114.06.18</t>
         </is>
       </c>
       <c r="K6" s="53" t="inlineStr">
@@ -5713,7 +5386,7 @@
       </c>
       <c r="J7" s="38" t="inlineStr">
         <is>
-          <t>109.1.9</t>
+          <t>109.01.09</t>
         </is>
       </c>
       <c r="K7" s="53" t="inlineStr">
@@ -5823,7 +5496,7 @@
       </c>
       <c r="J9" s="38" t="inlineStr">
         <is>
-          <t>113.6.13</t>
+          <t>113.06.13</t>
         </is>
       </c>
       <c r="K9" s="53" t="inlineStr">
@@ -5878,7 +5551,7 @@
       </c>
       <c r="J10" s="38" t="inlineStr">
         <is>
-          <t>114.3.19</t>
+          <t>114.03.19</t>
         </is>
       </c>
       <c r="K10" s="53" t="inlineStr">
@@ -5933,7 +5606,7 @@
       </c>
       <c r="J11" s="38" t="inlineStr">
         <is>
-          <t>114.6.18</t>
+          <t>114.06.18</t>
         </is>
       </c>
       <c r="K11" s="53" t="inlineStr">
@@ -6013,7 +5686,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor theme="5" tint="0.5999938962981048"/>
@@ -6159,7 +5832,7 @@
       </c>
       <c r="J4" s="38" t="inlineStr">
         <is>
-          <t>105.9.30</t>
+          <t>105.09.30</t>
         </is>
       </c>
       <c r="K4" s="38" t="inlineStr">
@@ -6214,7 +5887,7 @@
       </c>
       <c r="J5" s="38" t="inlineStr">
         <is>
-          <t>114.1.2</t>
+          <t>114.01.02</t>
         </is>
       </c>
       <c r="K5" s="38" t="inlineStr">
@@ -6269,7 +5942,7 @@
       </c>
       <c r="J6" s="38" t="inlineStr">
         <is>
-          <t>105.9.30</t>
+          <t>105.09.30</t>
         </is>
       </c>
       <c r="K6" s="38" t="inlineStr">
@@ -6324,7 +5997,7 @@
       </c>
       <c r="J7" s="38" t="inlineStr">
         <is>
-          <t>114.3.19</t>
+          <t>114.03.19</t>
         </is>
       </c>
       <c r="K7" s="38" t="inlineStr">
@@ -6379,7 +6052,7 @@
       </c>
       <c r="J8" s="38" t="inlineStr">
         <is>
-          <t>103.10.1</t>
+          <t>103.10.01</t>
         </is>
       </c>
       <c r="K8" s="38" t="inlineStr">
@@ -6460,7 +6133,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor theme="5" tint="0.5999938962981048"/>
@@ -6606,7 +6279,7 @@
       </c>
       <c r="J4" s="38" t="inlineStr">
         <is>
-          <t>108.2.20</t>
+          <t>108.02.20</t>
         </is>
       </c>
       <c r="K4" s="38" t="inlineStr">
@@ -6679,6 +6352,217 @@
     <cfRule type="duplicateValues" priority="6" dxfId="1" stopIfTrue="1"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="landscape" paperSize="9" verticalDpi="0"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor theme="5" tint="0.5999938962981048"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K13"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="16.2"/>
+  <cols>
+    <col width="6.77734375" customWidth="1" style="65" min="1" max="1"/>
+    <col width="28.109375" bestFit="1" customWidth="1" style="65" min="2" max="2"/>
+    <col width="50.77734375" customWidth="1" style="47" min="3" max="3"/>
+    <col width="15.77734375" customWidth="1" style="65" min="4" max="8"/>
+    <col width="9.77734375" customWidth="1" style="65" min="9" max="11"/>
+    <col width="8.88671875" customWidth="1" style="65" min="12" max="16384"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="19.8" customHeight="1" s="113">
+      <c r="A1" s="9" t="inlineStr">
+        <is>
+          <t>幼兒保育暨產業系法規清單檢核表</t>
+        </is>
+      </c>
+      <c r="B1" s="9" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="96" t="inlineStr">
+        <is>
+          <t>序號</t>
+        </is>
+      </c>
+      <c r="B2" s="96" t="inlineStr">
+        <is>
+          <t>類別</t>
+        </is>
+      </c>
+      <c r="C2" s="94" t="inlineStr">
+        <is>
+          <t>法規名稱</t>
+        </is>
+      </c>
+      <c r="D2" s="114" t="inlineStr">
+        <is>
+          <t>現況(請勾選)</t>
+        </is>
+      </c>
+      <c r="E2" s="115" t="n"/>
+      <c r="F2" s="115" t="n"/>
+      <c r="G2" s="115" t="n"/>
+      <c r="H2" s="116" t="n"/>
+      <c r="I2" s="90" t="inlineStr">
+        <is>
+          <t>業管單位</t>
+        </is>
+      </c>
+      <c r="J2" s="112" t="inlineStr">
+        <is>
+          <t>最後一次修訂時間</t>
+        </is>
+      </c>
+      <c r="K2" s="97" t="inlineStr">
+        <is>
+          <t>備註</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="118.8" customHeight="1" s="113">
+      <c r="A3" s="117" t="n"/>
+      <c r="B3" s="117" t="n"/>
+      <c r="C3" s="117" t="n"/>
+      <c r="D3" s="11" t="inlineStr">
+        <is>
+          <t>1.是否已更新為現行最新法規版本。</t>
+        </is>
+      </c>
+      <c r="E3" s="11" t="inlineStr">
+        <is>
+          <t>2.法規名稱是否正確。</t>
+        </is>
+      </c>
+      <c r="F3" s="11" t="inlineStr">
+        <is>
+          <t>3.法規格式是否完整(須不含底線、刪除線及各式顏色標示等)。</t>
+        </is>
+      </c>
+      <c r="G3" s="11" t="inlineStr">
+        <is>
+          <t>4.若法規超過2年以上未更新，是否需要更新，並於115學年度行政會議提案。</t>
+        </is>
+      </c>
+      <c r="H3" s="11" t="inlineStr">
+        <is>
+          <t>5.因應校務會議、董事會通過之組職規程修訂案，是否需要更新，並於115學年度行政會議提案。</t>
+        </is>
+      </c>
+      <c r="I3" s="117" t="n"/>
+      <c r="J3" s="117" t="n"/>
+      <c r="K3" s="117" t="n"/>
+    </row>
+    <row r="4" ht="64.8" customFormat="1" customHeight="1" s="65">
+      <c r="A4" s="35" t="n">
+        <v>1</v>
+      </c>
+      <c r="B4" s="38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">共同教育中心及系科法規 </t>
+        </is>
+      </c>
+      <c r="C4" s="53" t="inlineStr">
+        <is>
+          <t>輔英科技大學幼兒保育暨產業系教保專業知能課程學分抵免採認辦法
+(原：幼兒保育系教保專業知能課程學分抵免採認辦法)</t>
+        </is>
+      </c>
+      <c r="D4" s="97" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+      <c r="E4" s="97" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+      <c r="F4" s="97" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+      <c r="G4" s="97" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+      <c r="H4" s="97" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I4" s="38" t="inlineStr">
+        <is>
+          <t>幼兒保育暨產業系</t>
+        </is>
+      </c>
+      <c r="J4" s="38" t="inlineStr">
+        <is>
+          <t>106.09.28</t>
+        </is>
+      </c>
+      <c r="K4" s="38" t="inlineStr">
+        <is>
+          <t>逾2年未更新(9年未修，預計115提案)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5"/>
+    <row r="6" customFormat="1" s="65">
+      <c r="A6" s="27" t="n"/>
+      <c r="B6" s="27" t="n"/>
+      <c r="C6" s="47" t="n"/>
+      <c r="D6" s="54" t="n"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="65" t="inlineStr">
+        <is>
+          <t>承辦人核章：</t>
+        </is>
+      </c>
+    </row>
+    <row r="8"/>
+    <row r="9"/>
+    <row r="10">
+      <c r="A10" s="65" t="inlineStr">
+        <is>
+          <t>二級主管核章：</t>
+        </is>
+      </c>
+    </row>
+    <row r="11"/>
+    <row r="12"/>
+    <row r="13">
+      <c r="A13" s="65" t="inlineStr">
+        <is>
+          <t>一級主管核章：</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="7">
+    <mergeCell ref="D2:H2"/>
+    <mergeCell ref="J2:J3"/>
+    <mergeCell ref="B2:B3"/>
+    <mergeCell ref="A2:A3"/>
+    <mergeCell ref="C2:C3"/>
+    <mergeCell ref="K2:K3"/>
+    <mergeCell ref="I2:I3"/>
+  </mergeCells>
+  <conditionalFormatting sqref="C2">
+    <cfRule type="duplicateValues" priority="1" dxfId="1" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" priority="2" dxfId="1" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" priority="3" dxfId="1" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" priority="4" dxfId="1" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" priority="5" dxfId="1" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" priority="6" dxfId="1" stopIfTrue="1"/>
+  </conditionalFormatting>
+  <pageMargins left="0.7086614173228347" right="0.7086614173228347" top="0.7480314960629921" bottom="0.7480314960629921" header="0.3149606299212598" footer="0.3149606299212598"/>
   <pageSetup orientation="landscape" paperSize="9" verticalDpi="0"/>
 </worksheet>
 </file>
@@ -6936,7 +6820,7 @@
       </c>
       <c r="J6" s="38" t="inlineStr">
         <is>
-          <t>113.2.15</t>
+          <t>113.02.15</t>
         </is>
       </c>
       <c r="K6" s="38" t="inlineStr">
@@ -7101,7 +6985,7 @@
       </c>
       <c r="J9" s="38" t="inlineStr">
         <is>
-          <t>109.3.5</t>
+          <t>109.03.05</t>
         </is>
       </c>
       <c r="K9" s="38" t="inlineStr">
@@ -7156,7 +7040,7 @@
       </c>
       <c r="J10" s="38" t="inlineStr">
         <is>
-          <t>114.3.20</t>
+          <t>114.03.20</t>
         </is>
       </c>
       <c r="K10" s="38" t="inlineStr">
@@ -7211,7 +7095,7 @@
       </c>
       <c r="J11" s="38" t="inlineStr">
         <is>
-          <t>104.9.30</t>
+          <t>104.09.30</t>
         </is>
       </c>
       <c r="K11" s="38" t="inlineStr">
@@ -7266,7 +7150,7 @@
       </c>
       <c r="J12" s="38" t="inlineStr">
         <is>
-          <t>115.1.15</t>
+          <t>115.01.15</t>
         </is>
       </c>
       <c r="K12" s="38" t="inlineStr">
@@ -7321,7 +7205,7 @@
       </c>
       <c r="J13" s="38" t="inlineStr">
         <is>
-          <t>115.4.2</t>
+          <t>115.04.02</t>
         </is>
       </c>
       <c r="K13" s="38" t="inlineStr">
@@ -7376,7 +7260,7 @@
       </c>
       <c r="J14" s="38" t="inlineStr">
         <is>
-          <t>109.3.5</t>
+          <t>109.03.05</t>
         </is>
       </c>
       <c r="K14" s="38" t="inlineStr">
@@ -7431,7 +7315,7 @@
       </c>
       <c r="J15" s="38" t="inlineStr">
         <is>
-          <t>115.6.3</t>
+          <t>115.06.03</t>
         </is>
       </c>
       <c r="K15" s="38" t="inlineStr">
@@ -7486,7 +7370,7 @@
       </c>
       <c r="J16" s="38" t="inlineStr">
         <is>
-          <t>100.7.8</t>
+          <t>100.07.08</t>
         </is>
       </c>
       <c r="K16" s="38" t="inlineStr">
@@ -7541,7 +7425,7 @@
       </c>
       <c r="J17" s="38" t="inlineStr">
         <is>
-          <t>113.3.14</t>
+          <t>113.03.14</t>
         </is>
       </c>
       <c r="K17" s="38" t="inlineStr">
@@ -7596,7 +7480,7 @@
       </c>
       <c r="J18" s="38" t="inlineStr">
         <is>
-          <t>114.4.30</t>
+          <t>114.04.30</t>
         </is>
       </c>
       <c r="K18" s="38" t="inlineStr">
@@ -7706,7 +7590,7 @@
       </c>
       <c r="J20" s="38" t="inlineStr">
         <is>
-          <t>114.6.12</t>
+          <t>114.06.12</t>
         </is>
       </c>
       <c r="K20" s="38" t="inlineStr">
@@ -7761,7 +7645,7 @@
       </c>
       <c r="J21" s="38" t="inlineStr">
         <is>
-          <t>110.10.7</t>
+          <t>110.10.07</t>
         </is>
       </c>
       <c r="K21" s="38" t="inlineStr">
@@ -7871,7 +7755,7 @@
       </c>
       <c r="J23" s="38" t="inlineStr">
         <is>
-          <t>115.1.15</t>
+          <t>115.01.15</t>
         </is>
       </c>
       <c r="K23" s="38" t="inlineStr">
@@ -7981,7 +7865,7 @@
       </c>
       <c r="J25" s="38" t="inlineStr">
         <is>
-          <t>104.9.30</t>
+          <t>104.09.30</t>
         </is>
       </c>
       <c r="K25" s="38" t="inlineStr">
@@ -8036,7 +7920,7 @@
       </c>
       <c r="J26" s="38" t="inlineStr">
         <is>
-          <t>114.1.9</t>
+          <t>114.01.09</t>
         </is>
       </c>
       <c r="K26" s="38" t="inlineStr">
@@ -8256,7 +8140,7 @@
       </c>
       <c r="J30" s="38" t="inlineStr">
         <is>
-          <t>113.6.13</t>
+          <t>113.06.13</t>
         </is>
       </c>
       <c r="K30" s="38" t="inlineStr">
@@ -8311,7 +8195,7 @@
       </c>
       <c r="J31" s="38" t="inlineStr">
         <is>
-          <t>114.1.9</t>
+          <t>114.01.09</t>
         </is>
       </c>
       <c r="K31" s="38" t="inlineStr">
@@ -8366,7 +8250,7 @@
       </c>
       <c r="J32" s="38" t="inlineStr">
         <is>
-          <t>114.12.3</t>
+          <t>114.12.03</t>
         </is>
       </c>
       <c r="K32" s="38" t="inlineStr">
@@ -8421,7 +8305,7 @@
       </c>
       <c r="J33" s="38" t="inlineStr">
         <is>
-          <t>112.5.10</t>
+          <t>112.05.10</t>
         </is>
       </c>
       <c r="K33" s="38" t="inlineStr">
@@ -8476,7 +8360,7 @@
       </c>
       <c r="J34" s="38" t="inlineStr">
         <is>
-          <t>115.3.5</t>
+          <t>115.03.05</t>
         </is>
       </c>
       <c r="K34" s="38" t="inlineStr">
@@ -8531,7 +8415,7 @@
       </c>
       <c r="J35" s="38" t="inlineStr">
         <is>
-          <t>105.7.26</t>
+          <t>105.07.26</t>
         </is>
       </c>
       <c r="K35" s="38" t="inlineStr">
@@ -8641,7 +8525,7 @@
       </c>
       <c r="J37" s="38" t="inlineStr">
         <is>
-          <t>103.1.22</t>
+          <t>103.01.22</t>
         </is>
       </c>
       <c r="K37" s="38" t="inlineStr">
@@ -8696,7 +8580,7 @@
       </c>
       <c r="J38" s="38" t="inlineStr">
         <is>
-          <t>115.1.15</t>
+          <t>115.01.15</t>
         </is>
       </c>
       <c r="K38" s="38" t="inlineStr">
@@ -8751,7 +8635,7 @@
       </c>
       <c r="J39" s="38" t="inlineStr">
         <is>
-          <t>105.4.29</t>
+          <t>105.04.29</t>
         </is>
       </c>
       <c r="K39" s="38" t="inlineStr">
@@ -8806,7 +8690,7 @@
       </c>
       <c r="J40" s="38" t="inlineStr">
         <is>
-          <t>114.9.3</t>
+          <t>114.09.03</t>
         </is>
       </c>
       <c r="K40" s="38" t="inlineStr">
@@ -8861,7 +8745,7 @@
       </c>
       <c r="J41" s="38" t="inlineStr">
         <is>
-          <t>111.6.16</t>
+          <t>111.06.16</t>
         </is>
       </c>
       <c r="K41" s="38" t="inlineStr">
@@ -8916,7 +8800,7 @@
       </c>
       <c r="J42" s="38" t="inlineStr">
         <is>
-          <t>110.6.16</t>
+          <t>110.06.16</t>
         </is>
       </c>
       <c r="K42" s="38" t="inlineStr">
@@ -8971,7 +8855,7 @@
       </c>
       <c r="J43" s="38" t="inlineStr">
         <is>
-          <t>108.6.12</t>
+          <t>108.06.12</t>
         </is>
       </c>
       <c r="K43" s="38" t="inlineStr">
@@ -9026,7 +8910,7 @@
       </c>
       <c r="J44" s="38" t="inlineStr">
         <is>
-          <t>115.4.2</t>
+          <t>115.04.02</t>
         </is>
       </c>
       <c r="K44" s="38" t="inlineStr">
@@ -9136,7 +9020,7 @@
       </c>
       <c r="J46" s="38" t="inlineStr">
         <is>
-          <t>110.6.24</t>
+          <t>110.06.24</t>
         </is>
       </c>
       <c r="K46" s="38" t="inlineStr">
@@ -9191,7 +9075,7 @@
       </c>
       <c r="J47" s="38" t="inlineStr">
         <is>
-          <t>114.6.12</t>
+          <t>114.06.12</t>
         </is>
       </c>
       <c r="K47" s="38" t="inlineStr">
@@ -9246,7 +9130,7 @@
       </c>
       <c r="J48" s="38" t="inlineStr">
         <is>
-          <t>111.10.6</t>
+          <t>111.10.06</t>
         </is>
       </c>
       <c r="K48" s="38" t="inlineStr">
@@ -9356,7 +9240,7 @@
       </c>
       <c r="J50" s="38" t="inlineStr">
         <is>
-          <t>112.5.10</t>
+          <t>112.05.10</t>
         </is>
       </c>
       <c r="K50" s="38" t="inlineStr">
@@ -9411,7 +9295,7 @@
       </c>
       <c r="J51" s="38" t="inlineStr">
         <is>
-          <t>113.2.15</t>
+          <t>113.02.15</t>
         </is>
       </c>
       <c r="K51" s="38" t="inlineStr">
@@ -9466,7 +9350,7 @@
       </c>
       <c r="J52" s="38" t="inlineStr">
         <is>
-          <t>114.9.3</t>
+          <t>114.09.03</t>
         </is>
       </c>
       <c r="K52" s="38" t="inlineStr">
@@ -9576,7 +9460,7 @@
       </c>
       <c r="J54" s="38" t="inlineStr">
         <is>
-          <t>110.9.27</t>
+          <t>110.09.27</t>
         </is>
       </c>
       <c r="K54" s="38" t="inlineStr">
@@ -9631,7 +9515,7 @@
       </c>
       <c r="J55" s="38" t="inlineStr">
         <is>
-          <t>110.9.29</t>
+          <t>110.09.29</t>
         </is>
       </c>
       <c r="K55" s="38" t="inlineStr">
@@ -9686,7 +9570,7 @@
       </c>
       <c r="J56" s="38" t="inlineStr">
         <is>
-          <t>113.5.22</t>
+          <t>113.05.22</t>
         </is>
       </c>
       <c r="K56" s="38" t="inlineStr">
@@ -9741,7 +9625,7 @@
       </c>
       <c r="J57" s="38" t="inlineStr">
         <is>
-          <t>114.12.31</t>
+          <t>115學年度</t>
         </is>
       </c>
       <c r="K57" s="38" t="inlineStr">
@@ -9796,7 +9680,7 @@
       </c>
       <c r="J58" s="38" t="inlineStr">
         <is>
-          <t>110.9.14</t>
+          <t>110.09.14</t>
         </is>
       </c>
       <c r="K58" s="38" t="inlineStr">
@@ -9851,7 +9735,7 @@
       </c>
       <c r="J59" s="38" t="inlineStr">
         <is>
-          <t>110.9.13</t>
+          <t>110.09.13</t>
         </is>
       </c>
       <c r="K59" s="38" t="inlineStr">
@@ -9906,7 +9790,7 @@
       </c>
       <c r="J60" s="38" t="inlineStr">
         <is>
-          <t>110.10.5</t>
+          <t>110.10.05</t>
         </is>
       </c>
       <c r="K60" s="38" t="inlineStr">
@@ -9961,7 +9845,7 @@
       </c>
       <c r="J61" s="38" t="inlineStr">
         <is>
-          <t>110.10.7</t>
+          <t>110.10.07</t>
         </is>
       </c>
       <c r="K61" s="38" t="inlineStr">
@@ -10016,7 +9900,7 @@
       </c>
       <c r="J62" s="38" t="inlineStr">
         <is>
-          <t>110.9.28</t>
+          <t>110.09.28</t>
         </is>
       </c>
       <c r="K62" s="38" t="inlineStr">
@@ -10071,7 +9955,7 @@
       </c>
       <c r="J63" s="38" t="inlineStr">
         <is>
-          <t>110.12.8</t>
+          <t>110.12.08</t>
         </is>
       </c>
       <c r="K63" s="38" t="inlineStr">
@@ -10126,7 +10010,7 @@
       </c>
       <c r="J64" s="38" t="inlineStr">
         <is>
-          <t>114.6.18</t>
+          <t>114.06.18</t>
         </is>
       </c>
       <c r="K64" s="38" t="inlineStr">
@@ -10181,7 +10065,7 @@
       </c>
       <c r="J65" s="38" t="inlineStr">
         <is>
-          <t>104.5.18</t>
+          <t>104.05.18</t>
         </is>
       </c>
       <c r="K65" s="38" t="inlineStr">
@@ -10291,7 +10175,7 @@
       </c>
       <c r="J67" s="38" t="inlineStr">
         <is>
-          <t>113.7.9</t>
+          <t>113.07.09</t>
         </is>
       </c>
       <c r="K67" s="38" t="inlineStr">
@@ -10346,7 +10230,7 @@
       </c>
       <c r="J68" s="38" t="inlineStr">
         <is>
-          <t>114.7.15</t>
+          <t>114.07.15</t>
         </is>
       </c>
       <c r="K68" s="38" t="inlineStr">
@@ -10401,7 +10285,7 @@
       </c>
       <c r="J69" s="38" t="inlineStr">
         <is>
-          <t>115.3.27</t>
+          <t>115.03.27</t>
         </is>
       </c>
       <c r="K69" s="38" t="inlineStr">
@@ -10621,7 +10505,7 @@
       </c>
       <c r="J73" s="38" t="inlineStr">
         <is>
-          <t>110.3.11</t>
+          <t>110.03.11</t>
         </is>
       </c>
       <c r="K73" s="38" t="inlineStr">
@@ -10731,7 +10615,7 @@
       </c>
       <c r="J75" s="38" t="inlineStr">
         <is>
-          <t>115.1.7</t>
+          <t>115.01.07</t>
         </is>
       </c>
       <c r="K75" s="38" t="inlineStr">
@@ -10786,7 +10670,7 @@
       </c>
       <c r="J76" s="38" t="inlineStr">
         <is>
-          <t>113.4.3</t>
+          <t>113.04.03</t>
         </is>
       </c>
       <c r="K76" s="38" t="inlineStr">
@@ -10841,7 +10725,7 @@
       </c>
       <c r="J77" s="38" t="inlineStr">
         <is>
-          <t>115.6.11</t>
+          <t>115.06.11</t>
         </is>
       </c>
       <c r="K77" s="38" t="inlineStr">
@@ -10896,7 +10780,7 @@
       </c>
       <c r="J78" s="38" t="inlineStr">
         <is>
-          <t>111.9.29</t>
+          <t>111.09.29</t>
         </is>
       </c>
       <c r="K78" s="38" t="inlineStr">
@@ -10951,7 +10835,7 @@
       </c>
       <c r="J79" s="38" t="inlineStr">
         <is>
-          <t>115.4.2</t>
+          <t>115.04.02</t>
         </is>
       </c>
       <c r="K79" s="38" t="inlineStr">
@@ -11006,7 +10890,7 @@
       </c>
       <c r="J80" s="38" t="inlineStr">
         <is>
-          <t>115.6.3</t>
+          <t>115.06.03</t>
         </is>
       </c>
       <c r="K80" s="38" t="inlineStr">
@@ -11061,7 +10945,7 @@
       </c>
       <c r="J81" s="38" t="inlineStr">
         <is>
-          <t>114.6.18</t>
+          <t>114.06.18</t>
         </is>
       </c>
       <c r="K81" s="38" t="inlineStr">
@@ -11116,7 +11000,7 @@
       </c>
       <c r="J82" s="38" t="inlineStr">
         <is>
-          <t>115.6.24</t>
+          <t>115.06.24</t>
         </is>
       </c>
       <c r="K82" s="38" t="inlineStr">
@@ -11171,7 +11055,7 @@
       </c>
       <c r="J83" s="38" t="inlineStr">
         <is>
-          <t>113.3.14</t>
+          <t>113.03.14</t>
         </is>
       </c>
       <c r="K83" s="38" t="inlineStr">
@@ -11226,7 +11110,7 @@
       </c>
       <c r="J84" s="38" t="inlineStr">
         <is>
-          <t>115.6.3</t>
+          <t>115.06.03</t>
         </is>
       </c>
       <c r="K84" s="38" t="inlineStr">
@@ -11281,7 +11165,7 @@
       </c>
       <c r="J85" s="38" t="inlineStr">
         <is>
-          <t>115.2.25</t>
+          <t>115.02.25</t>
         </is>
       </c>
       <c r="K85" s="38" t="inlineStr">
@@ -11391,7 +11275,7 @@
       </c>
       <c r="J87" s="38" t="inlineStr">
         <is>
-          <t>112.2.8</t>
+          <t>112.02.08</t>
         </is>
       </c>
       <c r="K87" s="38" t="inlineStr">
@@ -11523,217 +11407,6 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16.2"/>
   <cols>
     <col width="6.77734375" customWidth="1" style="65" min="1" max="1"/>
-    <col width="28.109375" bestFit="1" customWidth="1" style="65" min="2" max="2"/>
-    <col width="50.77734375" customWidth="1" style="47" min="3" max="3"/>
-    <col width="15.77734375" customWidth="1" style="65" min="4" max="8"/>
-    <col width="9.77734375" customWidth="1" style="65" min="9" max="11"/>
-    <col width="8.88671875" customWidth="1" style="65" min="12" max="16384"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="19.8" customHeight="1" s="113">
-      <c r="A1" s="9" t="inlineStr">
-        <is>
-          <t>幼兒保育暨產業系法規清單檢核表</t>
-        </is>
-      </c>
-      <c r="B1" s="9" t="n"/>
-    </row>
-    <row r="2">
-      <c r="A2" s="96" t="inlineStr">
-        <is>
-          <t>序號</t>
-        </is>
-      </c>
-      <c r="B2" s="96" t="inlineStr">
-        <is>
-          <t>類別</t>
-        </is>
-      </c>
-      <c r="C2" s="94" t="inlineStr">
-        <is>
-          <t>法規名稱</t>
-        </is>
-      </c>
-      <c r="D2" s="114" t="inlineStr">
-        <is>
-          <t>現況(請勾選)</t>
-        </is>
-      </c>
-      <c r="E2" s="115" t="n"/>
-      <c r="F2" s="115" t="n"/>
-      <c r="G2" s="115" t="n"/>
-      <c r="H2" s="116" t="n"/>
-      <c r="I2" s="90" t="inlineStr">
-        <is>
-          <t>業管單位</t>
-        </is>
-      </c>
-      <c r="J2" s="112" t="inlineStr">
-        <is>
-          <t>最後一次修訂時間</t>
-        </is>
-      </c>
-      <c r="K2" s="97" t="inlineStr">
-        <is>
-          <t>備註</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="118.8" customHeight="1" s="113">
-      <c r="A3" s="117" t="n"/>
-      <c r="B3" s="117" t="n"/>
-      <c r="C3" s="117" t="n"/>
-      <c r="D3" s="11" t="inlineStr">
-        <is>
-          <t>1.是否已更新為現行最新法規版本。</t>
-        </is>
-      </c>
-      <c r="E3" s="11" t="inlineStr">
-        <is>
-          <t>2.法規名稱是否正確。</t>
-        </is>
-      </c>
-      <c r="F3" s="11" t="inlineStr">
-        <is>
-          <t>3.法規格式是否完整(須不含底線、刪除線及各式顏色標示等)。</t>
-        </is>
-      </c>
-      <c r="G3" s="11" t="inlineStr">
-        <is>
-          <t>4.若法規超過2年以上未更新，是否需要更新，並於115學年度行政會議提案。</t>
-        </is>
-      </c>
-      <c r="H3" s="11" t="inlineStr">
-        <is>
-          <t>5.因應校務會議、董事會通過之組職規程修訂案，是否需要更新，並於115學年度行政會議提案。</t>
-        </is>
-      </c>
-      <c r="I3" s="117" t="n"/>
-      <c r="J3" s="117" t="n"/>
-      <c r="K3" s="117" t="n"/>
-    </row>
-    <row r="4" ht="64.8" customFormat="1" customHeight="1" s="65">
-      <c r="A4" s="35" t="n">
-        <v>1</v>
-      </c>
-      <c r="B4" s="38" t="inlineStr">
-        <is>
-          <t xml:space="preserve">共同教育中心及系科法規 </t>
-        </is>
-      </c>
-      <c r="C4" s="53" t="inlineStr">
-        <is>
-          <t>輔英科技大學幼兒保育暨產業系教保專業知能課程學分抵免採認辦法
-(原：幼兒保育系教保專業知能課程學分抵免採認辦法)</t>
-        </is>
-      </c>
-      <c r="D4" s="97" t="inlineStr">
-        <is>
-          <t>V</t>
-        </is>
-      </c>
-      <c r="E4" s="97" t="inlineStr">
-        <is>
-          <t>V</t>
-        </is>
-      </c>
-      <c r="F4" s="97" t="inlineStr">
-        <is>
-          <t>V</t>
-        </is>
-      </c>
-      <c r="G4" s="97" t="inlineStr">
-        <is>
-          <t>V</t>
-        </is>
-      </c>
-      <c r="H4" s="97" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="I4" s="38" t="inlineStr">
-        <is>
-          <t>幼兒保育暨產業系</t>
-        </is>
-      </c>
-      <c r="J4" s="38" t="inlineStr">
-        <is>
-          <t>106.9.28</t>
-        </is>
-      </c>
-      <c r="K4" s="38" t="inlineStr">
-        <is>
-          <t>逾2年未更新(9年未修，預計115提案)</t>
-        </is>
-      </c>
-    </row>
-    <row r="5"/>
-    <row r="6" customFormat="1" s="65">
-      <c r="A6" s="27" t="n"/>
-      <c r="B6" s="27" t="n"/>
-      <c r="C6" s="47" t="n"/>
-      <c r="D6" s="54" t="n"/>
-    </row>
-    <row r="7">
-      <c r="A7" s="65" t="inlineStr">
-        <is>
-          <t>承辦人核章：</t>
-        </is>
-      </c>
-    </row>
-    <row r="8"/>
-    <row r="9"/>
-    <row r="10">
-      <c r="A10" s="65" t="inlineStr">
-        <is>
-          <t>二級主管核章：</t>
-        </is>
-      </c>
-    </row>
-    <row r="11"/>
-    <row r="12"/>
-    <row r="13">
-      <c r="A13" s="65" t="inlineStr">
-        <is>
-          <t>一級主管核章：</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="7">
-    <mergeCell ref="D2:H2"/>
-    <mergeCell ref="J2:J3"/>
-    <mergeCell ref="B2:B3"/>
-    <mergeCell ref="A2:A3"/>
-    <mergeCell ref="C2:C3"/>
-    <mergeCell ref="K2:K3"/>
-    <mergeCell ref="I2:I3"/>
-  </mergeCells>
-  <conditionalFormatting sqref="C2">
-    <cfRule type="duplicateValues" priority="1" dxfId="1" stopIfTrue="1"/>
-    <cfRule type="duplicateValues" priority="2" dxfId="1" stopIfTrue="1"/>
-    <cfRule type="duplicateValues" priority="3" dxfId="1" stopIfTrue="1"/>
-    <cfRule type="duplicateValues" priority="4" dxfId="1" stopIfTrue="1"/>
-    <cfRule type="duplicateValues" priority="5" dxfId="1" stopIfTrue="1"/>
-    <cfRule type="duplicateValues" priority="6" dxfId="1" stopIfTrue="1"/>
-  </conditionalFormatting>
-  <pageMargins left="0.7086614173228347" right="0.7086614173228347" top="0.7480314960629921" bottom="0.7480314960629921" header="0.3149606299212598" footer="0.3149606299212598"/>
-  <pageSetup orientation="landscape" paperSize="9" verticalDpi="0"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <tabColor theme="5" tint="0.5999938962981048"/>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:K13"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="16.2"/>
-  <cols>
-    <col width="6.77734375" customWidth="1" style="65" min="1" max="1"/>
     <col width="29" bestFit="1" customWidth="1" style="65" min="2" max="2"/>
     <col width="50.77734375" customWidth="1" style="47" min="3" max="3"/>
     <col width="15.77734375" customWidth="1" style="65" min="4" max="8"/>
@@ -11869,7 +11542,7 @@
       </c>
       <c r="J4" s="38" t="inlineStr">
         <is>
-          <t>108.9.25</t>
+          <t>108.09.25</t>
         </is>
       </c>
       <c r="K4" s="38" t="inlineStr">
@@ -12154,7 +11827,7 @@
       </c>
       <c r="J5" s="38" t="inlineStr">
         <is>
-          <t>112.6.7</t>
+          <t>112.06.07</t>
         </is>
       </c>
       <c r="K5" s="38" t="inlineStr">
@@ -12209,7 +11882,7 @@
       </c>
       <c r="J6" s="38" t="inlineStr">
         <is>
-          <t>113.6.19</t>
+          <t>113.06.19</t>
         </is>
       </c>
       <c r="K6" s="38" t="inlineStr">
@@ -12264,7 +11937,7 @@
       </c>
       <c r="J7" s="38" t="inlineStr">
         <is>
-          <t>113.6.19</t>
+          <t>113.06.19</t>
         </is>
       </c>
       <c r="K7" s="38" t="inlineStr">
@@ -12319,7 +11992,7 @@
       </c>
       <c r="J8" s="38" t="inlineStr">
         <is>
-          <t>109.5.21</t>
+          <t>109.05.21</t>
         </is>
       </c>
       <c r="K8" s="38" t="inlineStr">
@@ -12429,7 +12102,7 @@
       </c>
       <c r="J10" s="38" t="inlineStr">
         <is>
-          <t>114.5.21</t>
+          <t>114.05.21</t>
         </is>
       </c>
       <c r="K10" s="38" t="inlineStr">
@@ -12484,7 +12157,7 @@
       </c>
       <c r="J11" s="38" t="inlineStr">
         <is>
-          <t>114.1.2</t>
+          <t>114.01.02</t>
         </is>
       </c>
       <c r="K11" s="38" t="inlineStr">
@@ -12539,7 +12212,7 @@
       </c>
       <c r="J12" s="38" t="inlineStr">
         <is>
-          <t>115.7.1</t>
+          <t>115.07.01</t>
         </is>
       </c>
       <c r="K12" s="38" t="inlineStr">
@@ -12594,7 +12267,7 @@
       </c>
       <c r="J13" s="38" t="inlineStr">
         <is>
-          <t>115.3.26</t>
+          <t>115.03.26</t>
         </is>
       </c>
       <c r="K13" s="38" t="inlineStr">
@@ -12649,7 +12322,7 @@
       </c>
       <c r="J14" s="38" t="inlineStr">
         <is>
-          <t>115.3.26</t>
+          <t>115.03.26</t>
         </is>
       </c>
       <c r="K14" s="38" t="inlineStr">
@@ -12704,7 +12377,7 @@
       </c>
       <c r="J15" s="38" t="inlineStr">
         <is>
-          <t>110.10.7</t>
+          <t>110.10.07</t>
         </is>
       </c>
       <c r="K15" s="38" t="inlineStr">
@@ -12759,7 +12432,7 @@
       </c>
       <c r="J16" s="38" t="inlineStr">
         <is>
-          <t>111.1.20</t>
+          <t>111.01.20</t>
         </is>
       </c>
       <c r="K16" s="38" t="inlineStr">
@@ -12814,7 +12487,7 @@
       </c>
       <c r="J17" s="38" t="inlineStr">
         <is>
-          <t>113.5.22</t>
+          <t>113.05.22</t>
         </is>
       </c>
       <c r="K17" s="38" t="inlineStr">
@@ -12924,7 +12597,7 @@
       </c>
       <c r="J19" s="38" t="inlineStr">
         <is>
-          <t>114.12.9</t>
+          <t>114.12.09</t>
         </is>
       </c>
       <c r="K19" s="38" t="inlineStr">
@@ -12979,7 +12652,7 @@
       </c>
       <c r="J20" s="38" t="inlineStr">
         <is>
-          <t>115.6.3</t>
+          <t>115.06.03</t>
         </is>
       </c>
       <c r="K20" s="38" t="inlineStr">
@@ -13089,7 +12762,7 @@
       </c>
       <c r="J22" s="38" t="inlineStr">
         <is>
-          <t>105.11.2</t>
+          <t>105.11.02</t>
         </is>
       </c>
       <c r="K22" s="38" t="inlineStr">
@@ -13144,7 +12817,7 @@
       </c>
       <c r="J23" s="38" t="inlineStr">
         <is>
-          <t>110.6.16</t>
+          <t>110.06.16</t>
         </is>
       </c>
       <c r="K23" s="38" t="inlineStr">
@@ -13199,7 +12872,7 @@
       </c>
       <c r="J24" s="38" t="inlineStr">
         <is>
-          <t>114.6.13</t>
+          <t>114.06.13</t>
         </is>
       </c>
       <c r="K24" s="38" t="inlineStr">
@@ -13254,7 +12927,7 @@
       </c>
       <c r="J25" s="38" t="inlineStr">
         <is>
-          <t>110.12.8</t>
+          <t>110.12.08</t>
         </is>
       </c>
       <c r="K25" s="38" t="inlineStr">
@@ -13309,7 +12982,7 @@
       </c>
       <c r="J26" s="38" t="inlineStr">
         <is>
-          <t>114.1.15</t>
+          <t>114.01.15</t>
         </is>
       </c>
       <c r="K26" s="38" t="inlineStr">
@@ -13364,7 +13037,7 @@
       </c>
       <c r="J27" s="38" t="inlineStr">
         <is>
-          <t>115.2.25</t>
+          <t>115.02.25</t>
         </is>
       </c>
       <c r="K27" s="33" t="inlineStr">
@@ -13419,7 +13092,7 @@
       </c>
       <c r="J28" s="38" t="inlineStr">
         <is>
-          <t>112.5.10</t>
+          <t>112.05.10</t>
         </is>
       </c>
       <c r="K28" s="38" t="inlineStr">
@@ -13474,7 +13147,7 @@
       </c>
       <c r="J29" s="38" t="inlineStr">
         <is>
-          <t>114.4.30</t>
+          <t>114.04.30</t>
         </is>
       </c>
       <c r="K29" s="38" t="inlineStr">
@@ -13529,7 +13202,7 @@
       </c>
       <c r="J30" s="38" t="inlineStr">
         <is>
-          <t>110.3.10</t>
+          <t>110.03.10</t>
         </is>
       </c>
       <c r="K30" s="38" t="inlineStr">
@@ -13584,7 +13257,7 @@
       </c>
       <c r="J31" s="38" t="inlineStr">
         <is>
-          <t>115.4.2</t>
+          <t>115.04.02</t>
         </is>
       </c>
       <c r="K31" s="38" t="inlineStr">
@@ -13694,7 +13367,7 @@
       </c>
       <c r="J33" s="38" t="inlineStr">
         <is>
-          <t>110.1.6</t>
+          <t>110.01.06</t>
         </is>
       </c>
       <c r="K33" s="39" t="inlineStr">
@@ -13749,7 +13422,7 @@
       </c>
       <c r="J34" s="38" t="inlineStr">
         <is>
-          <t>115.3.18</t>
+          <t>115.03.18</t>
         </is>
       </c>
       <c r="K34" s="39" t="inlineStr">
@@ -13804,7 +13477,7 @@
       </c>
       <c r="J35" s="38" t="inlineStr">
         <is>
-          <t>114.9.3</t>
+          <t>114.09.03</t>
         </is>
       </c>
       <c r="K35" s="40" t="inlineStr">
@@ -13859,7 +13532,7 @@
       </c>
       <c r="J36" s="38" t="inlineStr">
         <is>
-          <t>115.3.18</t>
+          <t>115.03.18</t>
         </is>
       </c>
       <c r="K36" s="41" t="inlineStr">
@@ -13914,7 +13587,7 @@
       </c>
       <c r="J37" s="38" t="inlineStr">
         <is>
-          <t>114.10.8</t>
+          <t>114.10.08</t>
         </is>
       </c>
       <c r="K37" s="38" t="inlineStr">
@@ -13969,7 +13642,7 @@
       </c>
       <c r="J38" s="38" t="inlineStr">
         <is>
-          <t>113.1.10</t>
+          <t>113.01.10</t>
         </is>
       </c>
       <c r="K38" s="38" t="inlineStr">
@@ -14079,7 +13752,7 @@
       </c>
       <c r="J40" s="38" t="inlineStr">
         <is>
-          <t>112.2.8</t>
+          <t>112.02.08</t>
         </is>
       </c>
       <c r="K40" s="38" t="inlineStr">
@@ -14134,7 +13807,7 @@
       </c>
       <c r="J41" s="38" t="inlineStr">
         <is>
-          <t>110.1.14</t>
+          <t>110.01.14</t>
         </is>
       </c>
       <c r="K41" s="42" t="inlineStr">
@@ -14189,7 +13862,7 @@
       </c>
       <c r="J42" s="38" t="inlineStr">
         <is>
-          <t>110.6.10</t>
+          <t>110.06.10</t>
         </is>
       </c>
       <c r="K42" s="38" t="inlineStr">
@@ -14299,7 +13972,7 @@
       </c>
       <c r="J44" s="38" t="inlineStr">
         <is>
-          <t>106.1.4</t>
+          <t>106.01.04</t>
         </is>
       </c>
       <c r="K44" s="38" t="inlineStr">
@@ -14354,7 +14027,7 @@
       </c>
       <c r="J45" s="38" t="inlineStr">
         <is>
-          <t>106.1.4</t>
+          <t>106.01.04</t>
         </is>
       </c>
       <c r="K45" s="38" t="inlineStr">
@@ -14409,7 +14082,7 @@
       </c>
       <c r="J46" s="49" t="inlineStr">
         <is>
-          <t>100.6.24</t>
+          <t>100.06.24</t>
         </is>
       </c>
       <c r="K46" s="38" t="inlineStr">
@@ -14464,7 +14137,7 @@
       </c>
       <c r="J47" s="38" t="inlineStr">
         <is>
-          <t>110.1.14</t>
+          <t>110.01.14</t>
         </is>
       </c>
       <c r="K47" s="38" t="inlineStr">
@@ -14629,7 +14302,7 @@
       </c>
       <c r="J50" s="38" t="inlineStr">
         <is>
-          <t>109.1.9</t>
+          <t>109.01.09</t>
         </is>
       </c>
       <c r="K50" s="38" t="inlineStr">
@@ -14684,7 +14357,7 @@
       </c>
       <c r="J51" s="38" t="inlineStr">
         <is>
-          <t>110.9.2</t>
+          <t>110.09.02</t>
         </is>
       </c>
       <c r="K51" s="38" t="inlineStr">
@@ -14739,7 +14412,7 @@
       </c>
       <c r="J52" s="38" t="inlineStr">
         <is>
-          <t>109.6.18</t>
+          <t>109.06.18</t>
         </is>
       </c>
       <c r="K52" s="38" t="inlineStr">
@@ -14904,7 +14577,7 @@
       </c>
       <c r="J55" s="38" t="inlineStr">
         <is>
-          <t>114.10.8</t>
+          <t>114.10.08</t>
         </is>
       </c>
       <c r="K55" s="38" t="inlineStr">
@@ -14959,7 +14632,7 @@
       </c>
       <c r="J56" s="38" t="inlineStr">
         <is>
-          <t>114.10.8</t>
+          <t>114.10.08</t>
         </is>
       </c>
       <c r="K56" s="49" t="inlineStr">
@@ -15014,7 +14687,7 @@
       </c>
       <c r="J57" s="38" t="inlineStr">
         <is>
-          <t>114.12.3</t>
+          <t>114.12.03</t>
         </is>
       </c>
       <c r="K57" s="38" t="inlineStr">
@@ -15069,7 +14742,7 @@
       </c>
       <c r="J58" s="38" t="inlineStr">
         <is>
-          <t>115.6.30</t>
+          <t>115.06.30</t>
         </is>
       </c>
       <c r="K58" s="38" t="inlineStr">
@@ -15124,7 +14797,7 @@
       </c>
       <c r="J59" s="38" t="inlineStr">
         <is>
-          <t>113.9.18</t>
+          <t>113.09.18</t>
         </is>
       </c>
       <c r="K59" s="38" t="inlineStr">
@@ -15179,7 +14852,7 @@
       </c>
       <c r="J60" s="38" t="inlineStr">
         <is>
-          <t>112.6.8</t>
+          <t>112.06.08</t>
         </is>
       </c>
       <c r="K60" s="38" t="inlineStr">
@@ -15234,7 +14907,7 @@
       </c>
       <c r="J61" s="38" t="inlineStr">
         <is>
-          <t>114.9.3</t>
+          <t>114.09.03</t>
         </is>
       </c>
       <c r="K61" s="38" t="inlineStr">
@@ -15289,7 +14962,7 @@
       </c>
       <c r="J62" s="38" t="inlineStr">
         <is>
-          <t>113.4.18</t>
+          <t>113.04.18</t>
         </is>
       </c>
       <c r="K62" s="38" t="inlineStr">
@@ -15454,7 +15127,7 @@
       </c>
       <c r="J65" s="38" t="inlineStr">
         <is>
-          <t>108.4.30</t>
+          <t>108.04.30</t>
         </is>
       </c>
       <c r="K65" s="38" t="inlineStr">
@@ -15509,7 +15182,7 @@
       </c>
       <c r="J66" s="38" t="inlineStr">
         <is>
-          <t>113.9.12</t>
+          <t>113.09.12</t>
         </is>
       </c>
       <c r="K66" s="38" t="inlineStr">
@@ -15564,7 +15237,7 @@
       </c>
       <c r="J67" s="38" t="inlineStr">
         <is>
-          <t>109.1.9</t>
+          <t>109.01.09</t>
         </is>
       </c>
       <c r="K67" s="38" t="inlineStr">
@@ -15619,7 +15292,7 @@
       </c>
       <c r="J68" s="38" t="inlineStr">
         <is>
-          <t>111.7.20</t>
+          <t>111.07.20</t>
         </is>
       </c>
       <c r="K68" s="38" t="inlineStr">
@@ -15674,7 +15347,7 @@
       </c>
       <c r="J69" s="38" t="inlineStr">
         <is>
-          <t>107.12.5</t>
+          <t>107.12.05</t>
         </is>
       </c>
       <c r="K69" s="38" t="inlineStr">
@@ -15729,7 +15402,7 @@
       </c>
       <c r="J70" s="38" t="inlineStr">
         <is>
-          <t>107.6.28</t>
+          <t>107.06.28</t>
         </is>
       </c>
       <c r="K70" s="38" t="inlineStr">
@@ -15784,7 +15457,7 @@
       </c>
       <c r="J71" s="38" t="inlineStr">
         <is>
-          <t>106.6.21</t>
+          <t>106.06.21</t>
         </is>
       </c>
       <c r="K71" s="38" t="inlineStr">
@@ -15839,7 +15512,7 @@
       </c>
       <c r="J72" s="38" t="inlineStr">
         <is>
-          <t>109.6.11</t>
+          <t>109.06.11</t>
         </is>
       </c>
       <c r="K72" s="38" t="inlineStr">
@@ -16092,7 +15765,7 @@
       </c>
       <c r="J4" s="38" t="inlineStr">
         <is>
-          <t>113.2.21</t>
+          <t>113.02.21</t>
         </is>
       </c>
       <c r="K4" s="38" t="inlineStr">
@@ -16147,7 +15820,7 @@
       </c>
       <c r="J5" s="38" t="inlineStr">
         <is>
-          <t>114.5.21</t>
+          <t>114.05.21</t>
         </is>
       </c>
       <c r="K5" s="38" t="inlineStr">
@@ -16202,7 +15875,7 @@
       </c>
       <c r="J6" s="38" t="inlineStr">
         <is>
-          <t>115.5.13</t>
+          <t>115.05.13</t>
         </is>
       </c>
       <c r="K6" s="38" t="inlineStr">
@@ -16257,7 +15930,7 @@
       </c>
       <c r="J7" s="38" t="inlineStr">
         <is>
-          <t>105.9.30</t>
+          <t>105.09.30</t>
         </is>
       </c>
       <c r="K7" s="38" t="inlineStr">
@@ -16312,7 +15985,7 @@
       </c>
       <c r="J8" s="38" t="inlineStr">
         <is>
-          <t>115.7.8</t>
+          <t>115.07.08</t>
         </is>
       </c>
       <c r="K8" s="38" t="inlineStr">
@@ -16367,7 +16040,7 @@
       </c>
       <c r="J9" s="38" t="inlineStr">
         <is>
-          <t>105.5.12</t>
+          <t>105.05.12</t>
         </is>
       </c>
       <c r="K9" s="38" t="inlineStr">
@@ -16422,7 +16095,7 @@
       </c>
       <c r="J10" s="38" t="inlineStr">
         <is>
-          <t>115.6.3</t>
+          <t>115.06.03</t>
         </is>
       </c>
       <c r="K10" s="38" t="inlineStr">
@@ -16477,7 +16150,7 @@
       </c>
       <c r="J11" s="38" t="inlineStr">
         <is>
-          <t>115.5.13</t>
+          <t>115.05.13</t>
         </is>
       </c>
       <c r="K11" s="38" t="inlineStr">
@@ -16532,7 +16205,7 @@
       </c>
       <c r="J12" s="38" t="inlineStr">
         <is>
-          <t>115.2.25</t>
+          <t>115.02.25</t>
         </is>
       </c>
       <c r="K12" s="38" t="inlineStr">
@@ -16755,7 +16428,7 @@
       </c>
       <c r="H4" s="103" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>V</t>
         </is>
       </c>
       <c r="I4" s="80" t="inlineStr">
@@ -16770,7 +16443,7 @@
       </c>
       <c r="K4" s="75" t="inlineStr">
         <is>
-          <t>格式瑕疵(含底線,含各式顏色標記)；逾2年未更新(6年未修，預計115提案)</t>
+          <t>格式瑕疵(含底線,含各式顏色標記)；逾2年未更新(6年未修，預計115提案)；配合組織規程修訂(研究暨產學發展處→研發與永續發展處)</t>
         </is>
       </c>
     </row>
@@ -16810,7 +16483,7 @@
       </c>
       <c r="H5" s="103" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>V</t>
         </is>
       </c>
       <c r="I5" s="101" t="inlineStr">
@@ -16825,7 +16498,7 @@
       </c>
       <c r="K5" s="75" t="inlineStr">
         <is>
-          <t>逾2年未更新(7年未修，預計115提案)</t>
+          <t>逾2年未更新(7年未修，預計115提案)；配合組織規程修訂(研究暨產學發展處→研發與永續發展處)</t>
         </is>
       </c>
     </row>
@@ -16865,7 +16538,7 @@
       </c>
       <c r="H6" s="103" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>V</t>
         </is>
       </c>
       <c r="I6" s="101" t="inlineStr">
@@ -16875,12 +16548,12 @@
       </c>
       <c r="J6" s="103" t="inlineStr">
         <is>
-          <t>113.7.9</t>
+          <t>113.07.09</t>
         </is>
       </c>
       <c r="K6" s="75" t="inlineStr">
         <is>
-          <t>格式瑕疵(含刪除線,含修訂標籤)</t>
+          <t>格式瑕疵(含刪除線,含修訂標籤)；配合組織規程修訂(研究暨產學發展處→研發與永續發展處)</t>
         </is>
       </c>
     </row>
@@ -16920,7 +16593,7 @@
       </c>
       <c r="H7" s="103" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>V</t>
         </is>
       </c>
       <c r="I7" s="80" t="inlineStr">
@@ -16935,7 +16608,7 @@
       </c>
       <c r="K7" s="75" t="inlineStr">
         <is>
-          <t>無特別說明</t>
+          <t>配合組織規程修訂(研究暨產學發展處→研發與永續發展處)</t>
         </is>
       </c>
     </row>
@@ -17030,7 +16703,7 @@
       </c>
       <c r="H9" s="103" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>V</t>
         </is>
       </c>
       <c r="I9" s="80" t="inlineStr">
@@ -17040,12 +16713,12 @@
       </c>
       <c r="J9" s="103" t="inlineStr">
         <is>
-          <t>115.6.3</t>
+          <t>115.06.03</t>
         </is>
       </c>
       <c r="K9" s="75" t="inlineStr">
         <is>
-          <t>無特別說明</t>
+          <t>配合組織規程修訂(研究暨產學發展處→研發與永續發展處)</t>
         </is>
       </c>
     </row>
@@ -17085,7 +16758,7 @@
       </c>
       <c r="H10" s="103" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>V</t>
         </is>
       </c>
       <c r="I10" s="101" t="inlineStr">
@@ -17095,12 +16768,12 @@
       </c>
       <c r="J10" s="103" t="inlineStr">
         <is>
-          <t>114.9.3</t>
+          <t>114.09.03</t>
         </is>
       </c>
       <c r="K10" s="75" t="inlineStr">
         <is>
-          <t>無特別說明</t>
+          <t>配合組織規程修訂(研發處→研發與永續發展處;研究暨產學發展處→研發與永續發展處)</t>
         </is>
       </c>
     </row>
@@ -17140,7 +16813,7 @@
       </c>
       <c r="H11" s="103" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>V</t>
         </is>
       </c>
       <c r="I11" s="80" t="inlineStr">
@@ -17150,12 +16823,12 @@
       </c>
       <c r="J11" s="103" t="inlineStr">
         <is>
-          <t>111.9.29</t>
+          <t>111.09.29</t>
         </is>
       </c>
       <c r="K11" s="78" t="inlineStr">
         <is>
-          <t>逾2年未更新(4年未修，預計115提案)</t>
+          <t>逾2年未更新(4年未修，預計115提案)；配合組織規程修訂(研究暨產學發展處→研發與永續發展處)</t>
         </is>
       </c>
     </row>
@@ -17205,7 +16878,7 @@
       </c>
       <c r="J12" s="103" t="inlineStr">
         <is>
-          <t>113.4.3</t>
+          <t>113.04.03</t>
         </is>
       </c>
       <c r="K12" s="78" t="inlineStr">
@@ -17250,7 +16923,7 @@
       </c>
       <c r="H13" s="103" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>V</t>
         </is>
       </c>
       <c r="I13" s="80" t="inlineStr">
@@ -17260,12 +16933,12 @@
       </c>
       <c r="J13" s="103" t="inlineStr">
         <is>
-          <t>115.1.7</t>
+          <t>115.01.07</t>
         </is>
       </c>
       <c r="K13" s="75" t="inlineStr">
         <is>
-          <t>格式瑕疵(含底線,含各式顏色標記,含修訂標籤)</t>
+          <t>格式瑕疵(含底線,含各式顏色標記,含修訂標籤)；配合組織規程修訂(研究暨產學發展處→研發與永續發展處)</t>
         </is>
       </c>
     </row>
@@ -17315,7 +16988,7 @@
       </c>
       <c r="J14" s="103" t="inlineStr">
         <is>
-          <t>113.6.19</t>
+          <t>113.06.19</t>
         </is>
       </c>
       <c r="K14" s="75" t="inlineStr">
@@ -17370,12 +17043,12 @@
       </c>
       <c r="J15" s="103" t="inlineStr">
         <is>
-          <t>106.4.6</t>
+          <t>106.04.06</t>
         </is>
       </c>
       <c r="K15" s="75" t="inlineStr">
         <is>
-          <t>格式瑕疵(含底線,含各式顏色標記)；逾2年未更新(9年未修，預計115提案)；配合組織規程修訂(研究發展處→研究暨產學發展處)</t>
+          <t>格式瑕疵(含底線,含各式顏色標記)；逾2年未更新(9年未修，預計115提案)；配合組織規程修訂(研究發展處→研發與永續發展處)</t>
         </is>
       </c>
     </row>
@@ -17415,7 +17088,7 @@
       </c>
       <c r="H16" s="103" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>V</t>
         </is>
       </c>
       <c r="I16" s="80" t="inlineStr">
@@ -17425,12 +17098,12 @@
       </c>
       <c r="J16" s="103" t="inlineStr">
         <is>
-          <t>105.9.30</t>
+          <t>105.09.30</t>
         </is>
       </c>
       <c r="K16" s="75" t="inlineStr">
         <is>
-          <t>格式瑕疵(含底線,含各式顏色標記)；逾2年未更新(10年未修，預計115提案)</t>
+          <t>格式瑕疵(含底線,含各式顏色標記)；逾2年未更新(10年未修，預計115提案)；配合組織規程修訂(研究暨產學發展處→研發與永續發展處)</t>
         </is>
       </c>
     </row>
@@ -17470,7 +17143,7 @@
       </c>
       <c r="H17" s="103" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>V</t>
         </is>
       </c>
       <c r="I17" s="80" t="inlineStr">
@@ -17485,7 +17158,7 @@
       </c>
       <c r="K17" s="75" t="inlineStr">
         <is>
-          <t>格式瑕疵(含底線,含各式顏色標記)；逾2年未更新(7年未修，預計115提案)</t>
+          <t>格式瑕疵(含底線,含各式顏色標記)；逾2年未更新(7年未修，預計115提案)；配合組織規程修訂(研究暨產學發展處→研發與永續發展處)</t>
         </is>
       </c>
     </row>
@@ -17535,7 +17208,7 @@
       </c>
       <c r="J18" s="103" t="inlineStr">
         <is>
-          <t>114.11.10</t>
+          <t>114.11.05</t>
         </is>
       </c>
       <c r="K18" s="75" t="inlineStr">
@@ -17580,7 +17253,7 @@
       </c>
       <c r="H19" s="103" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>V</t>
         </is>
       </c>
       <c r="I19" s="80" t="inlineStr">
@@ -17590,12 +17263,12 @@
       </c>
       <c r="J19" s="103" t="inlineStr">
         <is>
-          <t>105.9.30</t>
+          <t>105.09.30</t>
         </is>
       </c>
       <c r="K19" s="75" t="inlineStr">
         <is>
-          <t>格式瑕疵(含底線,含各式顏色標記)；逾2年未更新(10年未修，預計115提案)</t>
+          <t>格式瑕疵(含底線,含各式顏色標記)；逾2年未更新(10年未修，預計115提案)；配合組織規程修訂(研發處→研發與永續發展處;研究暨產學發展處→研發與永續發展處)</t>
         </is>
       </c>
     </row>
@@ -17635,7 +17308,7 @@
       </c>
       <c r="H20" s="103" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>V</t>
         </is>
       </c>
       <c r="I20" s="80" t="inlineStr">
@@ -17645,12 +17318,12 @@
       </c>
       <c r="J20" s="103" t="inlineStr">
         <is>
-          <t>108.6.13</t>
+          <t>108.06.13</t>
         </is>
       </c>
       <c r="K20" s="75" t="inlineStr">
         <is>
-          <t>格式瑕疵(含底線,含各式顏色標記,含修訂標籤)；逾2年未更新(7年未修，預計115提案)</t>
+          <t>格式瑕疵(含底線,含各式顏色標記,含修訂標籤)；逾2年未更新(7年未修，預計115提案)；配合組織規程修訂(研究暨產學發展處→研發與永續發展處)</t>
         </is>
       </c>
     </row>
@@ -17690,7 +17363,7 @@
       </c>
       <c r="H21" s="103" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>V</t>
         </is>
       </c>
       <c r="I21" s="101" t="inlineStr">
@@ -17700,12 +17373,12 @@
       </c>
       <c r="J21" s="103" t="inlineStr">
         <is>
-          <t>112.4.26</t>
+          <t>112.04.26</t>
         </is>
       </c>
       <c r="K21" s="75" t="inlineStr">
         <is>
-          <t>逾2年未更新(3年未修，預計115提案)</t>
+          <t>逾2年未更新(3年未修，預計115提案)；配合組織規程修訂(研究暨產學發展處→研發與永續發展處)</t>
         </is>
       </c>
     </row>
@@ -17745,7 +17418,7 @@
       </c>
       <c r="H22" s="103" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>V</t>
         </is>
       </c>
       <c r="I22" s="101" t="inlineStr">
@@ -17755,12 +17428,12 @@
       </c>
       <c r="J22" s="103" t="inlineStr">
         <is>
-          <t>105.10.5</t>
+          <t>105.10.05</t>
         </is>
       </c>
       <c r="K22" s="75" t="inlineStr">
         <is>
-          <t>格式瑕疵(含底線,含各式顏色標記)；逾2年未更新(10年未修，預計115提案)</t>
+          <t>格式瑕疵(含底線,含各式顏色標記)；逾2年未更新(10年未修，預計115提案)；配合組織規程修訂(研究暨產學發展處→研發與永續發展處)</t>
         </is>
       </c>
     </row>
@@ -17800,7 +17473,7 @@
       </c>
       <c r="H23" s="103" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>V</t>
         </is>
       </c>
       <c r="I23" s="80" t="inlineStr">
@@ -17810,12 +17483,12 @@
       </c>
       <c r="J23" s="103" t="inlineStr">
         <is>
-          <t>106.2.22</t>
+          <t>106.02.22</t>
         </is>
       </c>
       <c r="K23" s="75" t="inlineStr">
         <is>
-          <t>格式瑕疵(含底線,含各式顏色標記)；逾2年未更新(9年未修，預計115提案)</t>
+          <t>格式瑕疵(含底線,含各式顏色標記)；逾2年未更新(9年未修，預計115提案)；配合組織規程修訂(研究暨產學發展處→研發與永續發展處)</t>
         </is>
       </c>
     </row>
@@ -17910,7 +17583,7 @@
       </c>
       <c r="H25" s="103" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>V</t>
         </is>
       </c>
       <c r="I25" s="101" t="inlineStr">
@@ -17920,12 +17593,12 @@
       </c>
       <c r="J25" s="103" t="inlineStr">
         <is>
-          <t>111.10.5</t>
+          <t>111.10.05</t>
         </is>
       </c>
       <c r="K25" s="75" t="inlineStr">
         <is>
-          <t>格式瑕疵(含底線,含各式顏色標記)；逾2年未更新(4年未修，預計115提案)</t>
+          <t>格式瑕疵(含底線,含各式顏色標記)；逾2年未更新(4年未修，預計115提案)；配合組織規程修訂(研究暨產學發展處→研發與永續發展處)</t>
         </is>
       </c>
     </row>
@@ -17965,7 +17638,7 @@
       </c>
       <c r="H26" s="103" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>V</t>
         </is>
       </c>
       <c r="I26" s="101" t="inlineStr">
@@ -17975,12 +17648,12 @@
       </c>
       <c r="J26" s="103" t="inlineStr">
         <is>
-          <t>106.1.11</t>
+          <t>106.01.11</t>
         </is>
       </c>
       <c r="K26" s="75" t="inlineStr">
         <is>
-          <t>格式瑕疵(含底線,含各式顏色標記)；逾2年未更新(9年未修，預計115提案)</t>
+          <t>格式瑕疵(含底線,含各式顏色標記)；逾2年未更新(9年未修，預計115提案)；配合組織規程修訂(研究暨產學發展處→研發與永續發展處)</t>
         </is>
       </c>
     </row>
@@ -18020,7 +17693,7 @@
       </c>
       <c r="H27" s="103" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>V</t>
         </is>
       </c>
       <c r="I27" s="101" t="inlineStr">
@@ -18030,12 +17703,12 @@
       </c>
       <c r="J27" s="103" t="inlineStr">
         <is>
-          <t>110.7.5</t>
+          <t>110.07.05</t>
         </is>
       </c>
       <c r="K27" s="75" t="inlineStr">
         <is>
-          <t>格式瑕疵(含修訂標籤)；逾2年未更新(5年未修，預計115提案)</t>
+          <t>格式瑕疵(含修訂標籤)；逾2年未更新(5年未修，預計115提案)；配合組織規程修訂(研究暨產學發展處→研發與永續發展處)</t>
         </is>
       </c>
     </row>
@@ -18075,7 +17748,7 @@
       </c>
       <c r="H28" s="103" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>V</t>
         </is>
       </c>
       <c r="I28" s="101" t="inlineStr">
@@ -18085,12 +17758,12 @@
       </c>
       <c r="J28" s="103" t="inlineStr">
         <is>
-          <t>111.11.7</t>
+          <t>111.11.07</t>
         </is>
       </c>
       <c r="K28" s="75" t="inlineStr">
         <is>
-          <t>逾2年未更新(4年未修，預計115提案)</t>
+          <t>逾2年未更新(4年未修，預計115提案)；配合組織規程修訂(研究暨產學發展處→研發與永續發展處)</t>
         </is>
       </c>
     </row>
@@ -18130,7 +17803,7 @@
       </c>
       <c r="H29" s="103" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>V</t>
         </is>
       </c>
       <c r="I29" s="101" t="inlineStr">
@@ -18145,7 +17818,7 @@
       </c>
       <c r="K29" s="75" t="inlineStr">
         <is>
-          <t>格式瑕疵(含底線,含各式顏色標記)；逾2年未更新(6年未修，預計115提案)</t>
+          <t>格式瑕疵(含底線,含各式顏色標記)；逾2年未更新(6年未修，預計115提案)；配合組織規程修訂(研究暨產學發展處→研發與永續發展處)</t>
         </is>
       </c>
     </row>
@@ -18195,7 +17868,7 @@
       </c>
       <c r="J30" s="103" t="inlineStr">
         <is>
-          <t>108.2.20</t>
+          <t>108.02.20</t>
         </is>
       </c>
       <c r="K30" s="75" t="inlineStr">
@@ -18240,7 +17913,7 @@
       </c>
       <c r="H31" s="103" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>V</t>
         </is>
       </c>
       <c r="I31" s="101" t="inlineStr">
@@ -18250,12 +17923,12 @@
       </c>
       <c r="J31" s="103" t="inlineStr">
         <is>
-          <t>114.6.18</t>
+          <t>114.06.18</t>
         </is>
       </c>
       <c r="K31" s="75" t="inlineStr">
         <is>
-          <t>格式瑕疵(含底線,含各式顏色標記)</t>
+          <t>格式瑕疵(含底線,含各式顏色標記)；配合組織規程修訂(研究暨產學發展處→研發與永續發展處)</t>
         </is>
       </c>
     </row>
@@ -18295,7 +17968,7 @@
       </c>
       <c r="H32" s="103" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>V</t>
         </is>
       </c>
       <c r="I32" s="101" t="inlineStr">
@@ -18305,12 +17978,12 @@
       </c>
       <c r="J32" s="103" t="inlineStr">
         <is>
-          <t>111.3.11</t>
+          <t>111.03.11</t>
         </is>
       </c>
       <c r="K32" s="75" t="inlineStr">
         <is>
-          <t>格式瑕疵(含底線,含各式顏色標記)；逾2年未更新(4年未修，預計115提案)</t>
+          <t>格式瑕疵(含底線,含各式顏色標記)；逾2年未更新(4年未修，預計115提案)；配合組織規程修訂(研究暨產學發展處→研發與永續發展處)</t>
         </is>
       </c>
     </row>
@@ -18350,7 +18023,7 @@
       </c>
       <c r="H33" s="103" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>V</t>
         </is>
       </c>
       <c r="I33" s="101" t="inlineStr">
@@ -18360,12 +18033,12 @@
       </c>
       <c r="J33" s="103" t="inlineStr">
         <is>
-          <t>114.1.2</t>
+          <t>114.01.02</t>
         </is>
       </c>
       <c r="K33" s="75" t="inlineStr">
         <is>
-          <t>格式瑕疵(含底線,含各式顏色標記)</t>
+          <t>格式瑕疵(含底線,含各式顏色標記)；配合組織規程修訂(研究暨產學發展處→研發與永續發展處)</t>
         </is>
       </c>
     </row>
@@ -18405,7 +18078,7 @@
       </c>
       <c r="H34" s="103" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>V</t>
         </is>
       </c>
       <c r="I34" s="101" t="inlineStr">
@@ -18415,12 +18088,12 @@
       </c>
       <c r="J34" s="103" t="inlineStr">
         <is>
-          <t>113.6.19</t>
+          <t>113.06.19</t>
         </is>
       </c>
       <c r="K34" s="75" t="inlineStr">
         <is>
-          <t>格式瑕疵(含底線,含各式顏色標記)</t>
+          <t>格式瑕疵(含底線,含各式顏色標記)；配合組織規程修訂(研發處→研發與永續發展處;研究暨產學發展處→研發與永續發展處)</t>
         </is>
       </c>
     </row>
@@ -18470,7 +18143,7 @@
       </c>
       <c r="J35" s="103" t="inlineStr">
         <is>
-          <t>114.6.18</t>
+          <t>114.06.18</t>
         </is>
       </c>
       <c r="K35" s="75" t="inlineStr">
@@ -18515,7 +18188,7 @@
       </c>
       <c r="H36" s="103" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>V</t>
         </is>
       </c>
       <c r="I36" s="101" t="inlineStr">
@@ -18525,12 +18198,12 @@
       </c>
       <c r="J36" s="103" t="inlineStr">
         <is>
-          <t>115.6.3</t>
+          <t>115.06.03</t>
         </is>
       </c>
       <c r="K36" s="75" t="inlineStr">
         <is>
-          <t>格式瑕疵(含底線,含各式顏色標記,含修訂標籤)</t>
+          <t>格式瑕疵(含底線,含各式顏色標記,含修訂標籤)；配合組織規程修訂(研究暨產學發展處→研發與永續發展處)</t>
         </is>
       </c>
     </row>
@@ -18570,7 +18243,7 @@
       </c>
       <c r="H37" s="103" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>V</t>
         </is>
       </c>
       <c r="I37" s="101" t="inlineStr">
@@ -18580,12 +18253,12 @@
       </c>
       <c r="J37" s="103" t="inlineStr">
         <is>
-          <t>111.10.5</t>
+          <t>111.10.05</t>
         </is>
       </c>
       <c r="K37" s="75" t="inlineStr">
         <is>
-          <t>格式瑕疵(含底線,含各式顏色標記,含修訂標籤)；逾2年未更新(4年未修，預計115提案)</t>
+          <t>格式瑕疵(含底線,含各式顏色標記,含修訂標籤)；逾2年未更新(4年未修，預計115提案)；配合組織規程修訂(研發處→研發與永續發展處;研究暨產學發展處→研發與永續發展處)</t>
         </is>
       </c>
     </row>
@@ -18625,7 +18298,7 @@
       </c>
       <c r="H38" s="103" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>V</t>
         </is>
       </c>
       <c r="I38" s="101" t="inlineStr">
@@ -18640,7 +18313,7 @@
       </c>
       <c r="K38" s="75" t="inlineStr">
         <is>
-          <t>格式瑕疵(含底線)</t>
+          <t>格式瑕疵(含底線)；配合組織規程修訂(研究暨產學發展處→研發與永續發展處)</t>
         </is>
       </c>
     </row>
@@ -18725,7 +18398,7 @@
       </c>
       <c r="F40" s="103" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>V</t>
         </is>
       </c>
       <c r="G40" s="103" t="inlineStr">
@@ -18750,7 +18423,7 @@
       </c>
       <c r="K40" s="75" t="inlineStr">
         <is>
-          <t>格式瑕疵(含各式顏色標記)</t>
+          <t>無特別說明</t>
         </is>
       </c>
     </row>
@@ -18809,17 +18482,170 @@
         </is>
       </c>
     </row>
-    <row r="42"/>
+    <row r="42">
+      <c r="A42" s="0" t="n">
+        <v>39</v>
+      </c>
+      <c r="B42" s="0" t="inlineStr">
+        <is>
+          <t>綜合性法規</t>
+        </is>
+      </c>
+      <c r="C42" s="0" t="inlineStr">
+        <is>
+          <t>輔英科技大學校務研究暨規劃室設置辦法(原：校務研究室設置辦法)</t>
+        </is>
+      </c>
+      <c r="D42" s="121" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+      <c r="E42" s="121" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+      <c r="F42" s="121" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+      <c r="G42" s="121" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+      <c r="H42" s="121" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I42" s="0" t="inlineStr">
+        <is>
+          <t>校務研究與永續發展中心</t>
+        </is>
+      </c>
+      <c r="J42" s="0" t="inlineStr">
+        <is>
+          <t>105.10.5</t>
+        </is>
+      </c>
+      <c r="K42" s="0" t="inlineStr">
+        <is>
+          <t>預計廢止；逾2年未更新(10年未修，預計115提案)</t>
+        </is>
+      </c>
+    </row>
     <row r="43" ht="16.2" customHeight="1" s="113">
-      <c r="A43" s="76" t="inlineStr">
-        <is>
-          <t>承辦人核章：</t>
-        </is>
-      </c>
-      <c r="I43" s="76" t="n"/>
+      <c r="A43" s="76" t="n">
+        <v>40</v>
+      </c>
+      <c r="B43" s="0" t="inlineStr">
+        <is>
+          <t>綜合性法規</t>
+        </is>
+      </c>
+      <c r="C43" s="0" t="inlineStr">
+        <is>
+          <t>輔英科技大學永續發展委員會設置要點</t>
+        </is>
+      </c>
+      <c r="D43" s="121" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+      <c r="E43" s="121" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+      <c r="F43" s="121" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+      <c r="G43" s="121" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="H43" s="121" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I43" s="76" t="inlineStr">
+        <is>
+          <t>校務研究與永續發展中心</t>
+        </is>
+      </c>
+      <c r="J43" s="0" t="inlineStr">
+        <is>
+          <t>114.9.3</t>
+        </is>
+      </c>
+      <c r="K43" s="0" t="inlineStr">
+        <is>
+          <t>無特別說明</t>
+        </is>
+      </c>
     </row>
     <row r="44">
-      <c r="I44" s="76" t="n"/>
+      <c r="A44" s="0" t="n">
+        <v>41</v>
+      </c>
+      <c r="B44" s="0" t="inlineStr">
+        <is>
+          <t>綜合性法規</t>
+        </is>
+      </c>
+      <c r="C44" s="0" t="inlineStr">
+        <is>
+          <t>輔英科技大學校務研究資料庫管理要點</t>
+        </is>
+      </c>
+      <c r="D44" s="121" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+      <c r="E44" s="121" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+      <c r="F44" s="121" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+      <c r="G44" s="121" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+      <c r="H44" s="121" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I44" s="76" t="inlineStr">
+        <is>
+          <t>校務研究與永續發展中心</t>
+        </is>
+      </c>
+      <c r="J44" s="0" t="inlineStr">
+        <is>
+          <t>112.3.8</t>
+        </is>
+      </c>
+      <c r="K44" s="0" t="inlineStr">
+        <is>
+          <t>逾2年未更新(3年未修，預計115提案)</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="I45" s="76" t="n"/>
@@ -19025,7 +18851,7 @@
       </c>
       <c r="J4" s="38" t="inlineStr">
         <is>
-          <t>105.9.30</t>
+          <t>105.09.30</t>
         </is>
       </c>
       <c r="K4" s="38" t="inlineStr">
@@ -19080,7 +18906,7 @@
       </c>
       <c r="J5" s="38" t="inlineStr">
         <is>
-          <t>109.3.25</t>
+          <t>109.03.25</t>
         </is>
       </c>
       <c r="K5" s="38" t="inlineStr">
@@ -19135,7 +18961,7 @@
       </c>
       <c r="J6" s="38" t="inlineStr">
         <is>
-          <t>105.9.30</t>
+          <t>105.09.30</t>
         </is>
       </c>
       <c r="K6" s="38" t="inlineStr">
@@ -19190,7 +19016,7 @@
       </c>
       <c r="J7" s="38" t="inlineStr">
         <is>
-          <t>114.6.26</t>
+          <t>114.06.26</t>
         </is>
       </c>
       <c r="K7" s="38" t="inlineStr">
@@ -19300,7 +19126,7 @@
       </c>
       <c r="J9" s="38" t="inlineStr">
         <is>
-          <t>110.3.10</t>
+          <t>110.03.10</t>
         </is>
       </c>
       <c r="K9" s="38" t="inlineStr">
@@ -19355,7 +19181,7 @@
       </c>
       <c r="J10" s="38" t="inlineStr">
         <is>
-          <t>111.6.8</t>
+          <t>111.06.08</t>
         </is>
       </c>
       <c r="K10" s="38" t="inlineStr">
@@ -19410,7 +19236,7 @@
       </c>
       <c r="J11" s="38" t="inlineStr">
         <is>
-          <t>114.12.5</t>
+          <t>114.12.05</t>
         </is>
       </c>
       <c r="K11" s="38" t="inlineStr">
@@ -19465,7 +19291,7 @@
       </c>
       <c r="J12" s="38" t="inlineStr">
         <is>
-          <t>111.7.20</t>
+          <t>111.07.20</t>
         </is>
       </c>
       <c r="K12" s="38" t="inlineStr">
@@ -19520,7 +19346,7 @@
       </c>
       <c r="J13" s="38" t="inlineStr">
         <is>
-          <t>113.4.29</t>
+          <t>113.04.29</t>
         </is>
       </c>
       <c r="K13" s="38" t="inlineStr">
@@ -19630,7 +19456,7 @@
       </c>
       <c r="J15" s="38" t="inlineStr">
         <is>
-          <t>114.6.26</t>
+          <t>114.06.26</t>
         </is>
       </c>
       <c r="K15" s="38" t="inlineStr">
@@ -19685,7 +19511,7 @@
       </c>
       <c r="J16" s="38" t="inlineStr">
         <is>
-          <t>114.6.26</t>
+          <t>114.06.26</t>
         </is>
       </c>
       <c r="K16" s="38" t="inlineStr">
@@ -19730,7 +19556,7 @@
       </c>
       <c r="H17" s="97" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>V</t>
         </is>
       </c>
       <c r="I17" s="38" t="inlineStr">
@@ -19740,12 +19566,12 @@
       </c>
       <c r="J17" s="38" t="inlineStr">
         <is>
-          <t>114.6.26</t>
+          <t>114.06.26</t>
         </is>
       </c>
       <c r="K17" s="38" t="inlineStr">
         <is>
-          <t>無特別說明</t>
+          <t>配合組織規程修訂(研發處→研發與永續發展處)</t>
         </is>
       </c>
     </row>
@@ -20018,7 +19844,7 @@
       </c>
       <c r="J4" s="38" t="inlineStr">
         <is>
-          <t>115.6.30</t>
+          <t>115.06.30</t>
         </is>
       </c>
       <c r="K4" s="38" t="inlineStr">
@@ -20073,7 +19899,7 @@
       </c>
       <c r="J5" s="38" t="inlineStr">
         <is>
-          <t>105.11.2</t>
+          <t>105.11.02</t>
         </is>
       </c>
       <c r="K5" s="38" t="inlineStr">
@@ -20128,7 +19954,7 @@
       </c>
       <c r="J6" s="38" t="inlineStr">
         <is>
-          <t>106.1.18</t>
+          <t>106.01.18</t>
         </is>
       </c>
       <c r="K6" s="38" t="inlineStr">
@@ -20183,7 +20009,7 @@
       </c>
       <c r="J7" s="38" t="inlineStr">
         <is>
-          <t>106.1.18</t>
+          <t>106.01.18</t>
         </is>
       </c>
       <c r="K7" s="38" t="inlineStr">
@@ -20293,7 +20119,7 @@
       </c>
       <c r="J9" s="38" t="inlineStr">
         <is>
-          <t>105.9.30</t>
+          <t>105.09.30</t>
         </is>
       </c>
       <c r="K9" s="38" t="inlineStr">
@@ -20509,7 +20335,7 @@
       </c>
       <c r="J13" s="38" t="inlineStr">
         <is>
-          <t>115.6.30</t>
+          <t>115.06.30</t>
         </is>
       </c>
       <c r="K13" s="38" t="inlineStr">
@@ -20784,7 +20610,7 @@
       </c>
       <c r="J18" s="38" t="inlineStr">
         <is>
-          <t>105.9.30</t>
+          <t>105.09.30</t>
         </is>
       </c>
       <c r="K18" s="38" t="inlineStr">
@@ -20839,7 +20665,7 @@
       </c>
       <c r="J19" s="38" t="inlineStr">
         <is>
-          <t>106.2.13</t>
+          <t>106.02.13</t>
         </is>
       </c>
       <c r="K19" s="38" t="inlineStr">
@@ -20894,7 +20720,7 @@
       </c>
       <c r="J20" s="38" t="inlineStr">
         <is>
-          <t>105.9.13</t>
+          <t>105.09.13</t>
         </is>
       </c>
       <c r="K20" s="38" t="inlineStr">
@@ -20949,7 +20775,7 @@
       </c>
       <c r="J21" s="38" t="inlineStr">
         <is>
-          <t>106.1.12</t>
+          <t>106.01.12</t>
         </is>
       </c>
       <c r="K21" s="38" t="inlineStr">
@@ -21004,7 +20830,7 @@
       </c>
       <c r="J22" s="38" t="inlineStr">
         <is>
-          <t>113.6.25</t>
+          <t>113.06.25</t>
         </is>
       </c>
       <c r="K22" s="38" t="inlineStr">
@@ -21059,7 +20885,7 @@
       </c>
       <c r="J23" s="38" t="inlineStr">
         <is>
-          <t>106.1.18</t>
+          <t>106.01.18</t>
         </is>
       </c>
       <c r="K23" s="38" t="inlineStr">
@@ -21114,7 +20940,7 @@
       </c>
       <c r="J24" s="38" t="inlineStr">
         <is>
-          <t>106.1.18</t>
+          <t>106.01.18</t>
         </is>
       </c>
       <c r="K24" s="38" t="inlineStr">
@@ -21169,7 +20995,7 @@
       </c>
       <c r="J25" s="38" t="inlineStr">
         <is>
-          <t>115.6.30</t>
+          <t>115.06.30</t>
         </is>
       </c>
       <c r="K25" s="38" t="inlineStr">
@@ -21224,7 +21050,7 @@
       </c>
       <c r="J26" s="38" t="inlineStr">
         <is>
-          <t>115.1.20</t>
+          <t>115.01.20</t>
         </is>
       </c>
       <c r="K26" s="38" t="inlineStr">
@@ -21421,7 +21247,7 @@
       </c>
       <c r="H4" s="97" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>V</t>
         </is>
       </c>
       <c r="I4" s="38" t="inlineStr">
@@ -21431,12 +21257,12 @@
       </c>
       <c r="J4" s="38" t="inlineStr">
         <is>
-          <t>114.6.18</t>
+          <t>114.06.18</t>
         </is>
       </c>
       <c r="K4" s="38" t="inlineStr">
         <is>
-          <t>格式瑕疵(含各式顏色標記)</t>
+          <t>格式瑕疵(含各式顏色標記)；配合組織規程修訂(校務研究暨規劃室→研發與永續發展處)</t>
         </is>
       </c>
     </row>
@@ -21476,7 +21302,7 @@
       </c>
       <c r="H5" s="97" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>V</t>
         </is>
       </c>
       <c r="I5" s="38" t="inlineStr">
@@ -21486,12 +21312,12 @@
       </c>
       <c r="J5" s="38" t="inlineStr">
         <is>
-          <t>112.6.7</t>
+          <t>112.06.07</t>
         </is>
       </c>
       <c r="K5" s="38" t="inlineStr">
         <is>
-          <t>逾2年未更新(3年未修，預計115提案)</t>
+          <t>逾2年未更新(3年未修，預計115提案)；配合組織規程修訂(研究暨產學發展處→研發與永續發展處)</t>
         </is>
       </c>
     </row>
@@ -21541,7 +21367,7 @@
       </c>
       <c r="J6" s="38" t="inlineStr">
         <is>
-          <t>99.7.23</t>
+          <t>99.07.23</t>
         </is>
       </c>
       <c r="K6" s="38" t="inlineStr">
@@ -21641,7 +21467,7 @@
       </c>
       <c r="H8" s="97" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>V</t>
         </is>
       </c>
       <c r="I8" s="38" t="inlineStr">
@@ -21651,12 +21477,12 @@
       </c>
       <c r="J8" s="38" t="inlineStr">
         <is>
-          <t>114.2.12</t>
+          <t>114.02.12</t>
         </is>
       </c>
       <c r="K8" s="38" t="inlineStr">
         <is>
-          <t>無特別說明</t>
+          <t>配合組織規程修訂(校務研究暨規劃室→研發與永續發展處)</t>
         </is>
       </c>
     </row>
@@ -21706,12 +21532,12 @@
       </c>
       <c r="J9" s="38" t="inlineStr">
         <is>
-          <t>114.12.5</t>
+          <t>114.12.05</t>
         </is>
       </c>
       <c r="K9" s="38" t="inlineStr">
         <is>
-          <t>格式瑕疵(含各式顏色標記)；配合組織規程修訂(衛生保健組→健康中心;軍訓室→學生事務處生活輔導組/校安中心)</t>
+          <t>格式瑕疵(含各式顏色標記)；配合組織規程修訂(研究暨產學發展處→研發與永續發展處;校務研究暨規劃室→研發與永續發展處)</t>
         </is>
       </c>
     </row>
@@ -21761,7 +21587,7 @@
       </c>
       <c r="J10" s="49" t="inlineStr">
         <is>
-          <t>112.1.11</t>
+          <t>112.01.11</t>
         </is>
       </c>
       <c r="K10" s="38" t="inlineStr">
@@ -21806,7 +21632,7 @@
       </c>
       <c r="H11" s="97" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>V</t>
         </is>
       </c>
       <c r="I11" s="38" t="inlineStr">
@@ -21816,12 +21642,12 @@
       </c>
       <c r="J11" s="38" t="inlineStr">
         <is>
-          <t>114.6.18</t>
+          <t>114.06.18</t>
         </is>
       </c>
       <c r="K11" s="38" t="inlineStr">
         <is>
-          <t>無特別說明</t>
+          <t>配合組織規程修訂(校務研究暨規劃室→研發與永續發展處)</t>
         </is>
       </c>
     </row>
@@ -21871,7 +21697,7 @@
       </c>
       <c r="J12" s="38" t="inlineStr">
         <is>
-          <t>102.9.11</t>
+          <t>102.09.11</t>
         </is>
       </c>
       <c r="K12" s="38" t="inlineStr">
@@ -21926,7 +21752,7 @@
       </c>
       <c r="J13" s="38" t="inlineStr">
         <is>
-          <t>102.10.9</t>
+          <t>102.10.09</t>
         </is>
       </c>
       <c r="K13" s="38" t="inlineStr">
@@ -22145,7 +21971,7 @@
       </c>
       <c r="J4" s="38" t="inlineStr">
         <is>
-          <t>115.7.1</t>
+          <t>115.07.01</t>
         </is>
       </c>
       <c r="K4" s="38" t="inlineStr">
@@ -22200,7 +22026,7 @@
       </c>
       <c r="J5" s="38" t="inlineStr">
         <is>
-          <t>112.1.11</t>
+          <t>112.01.11</t>
         </is>
       </c>
       <c r="K5" s="38" t="inlineStr">
@@ -22255,7 +22081,7 @@
       </c>
       <c r="J6" s="38" t="inlineStr">
         <is>
-          <t>109.9.16</t>
+          <t>109.09.16</t>
         </is>
       </c>
       <c r="K6" s="38" t="inlineStr">
@@ -22310,7 +22136,7 @@
       </c>
       <c r="J7" s="38" t="inlineStr">
         <is>
-          <t>100.11.2</t>
+          <t>100.11.02</t>
         </is>
       </c>
       <c r="K7" s="38" t="inlineStr">
@@ -22365,7 +22191,7 @@
       </c>
       <c r="J8" s="38" t="inlineStr">
         <is>
-          <t>112.1.11</t>
+          <t>112.01.11</t>
         </is>
       </c>
       <c r="K8" s="38" t="inlineStr">
@@ -22420,7 +22246,7 @@
       </c>
       <c r="J9" s="38" t="inlineStr">
         <is>
-          <t>114.6.18</t>
+          <t>114.06.18</t>
         </is>
       </c>
       <c r="K9" s="38" t="inlineStr">
@@ -22475,12 +22301,12 @@
       </c>
       <c r="J10" s="38" t="inlineStr">
         <is>
-          <t>115.8.25</t>
+          <t>115.08.25</t>
         </is>
       </c>
       <c r="K10" s="38" t="inlineStr">
         <is>
-          <t>配合組織規程修訂(研究發展處→研究暨產學發展處)</t>
+          <t>配合組織規程修訂(研究發展處→研發與永續發展處)</t>
         </is>
       </c>
     </row>
@@ -22530,7 +22356,7 @@
       </c>
       <c r="J11" s="38" t="inlineStr">
         <is>
-          <t>115.6.11</t>
+          <t>115.06.11</t>
         </is>
       </c>
       <c r="K11" s="38" t="inlineStr">
@@ -22585,7 +22411,7 @@
       </c>
       <c r="J12" s="38" t="inlineStr">
         <is>
-          <t>114.7.15</t>
+          <t>114.07.15</t>
         </is>
       </c>
       <c r="K12" s="38" t="inlineStr">
@@ -22640,7 +22466,7 @@
       </c>
       <c r="J13" s="38" t="inlineStr">
         <is>
-          <t>113.1.10</t>
+          <t>113.01.10</t>
         </is>
       </c>
       <c r="K13" s="38" t="inlineStr">
@@ -22750,7 +22576,7 @@
       </c>
       <c r="J15" s="38" t="inlineStr">
         <is>
-          <t>108.8.20</t>
+          <t>108.08.20</t>
         </is>
       </c>
       <c r="K15" s="38" t="inlineStr">
@@ -22805,7 +22631,7 @@
       </c>
       <c r="J16" s="38" t="inlineStr">
         <is>
-          <t>115.1.14</t>
+          <t>115.01.14</t>
         </is>
       </c>
       <c r="K16" s="38" t="inlineStr">
@@ -22915,7 +22741,7 @@
       </c>
       <c r="J18" s="38" t="inlineStr">
         <is>
-          <t>114.1.15</t>
+          <t>114.01.15</t>
         </is>
       </c>
       <c r="K18" s="38" t="inlineStr">
@@ -22970,7 +22796,7 @@
       </c>
       <c r="J19" s="38" t="inlineStr">
         <is>
-          <t>112.5.10</t>
+          <t>112.05.10</t>
         </is>
       </c>
       <c r="K19" s="38" t="inlineStr">
@@ -23025,7 +22851,7 @@
       </c>
       <c r="J20" s="38" t="inlineStr">
         <is>
-          <t>98.1.16</t>
+          <t>98.01.16</t>
         </is>
       </c>
       <c r="K20" s="38" t="inlineStr">
@@ -23080,7 +22906,7 @@
       </c>
       <c r="J21" s="38" t="inlineStr">
         <is>
-          <t>115.6.3</t>
+          <t>115.06.03</t>
         </is>
       </c>
       <c r="K21" s="38" t="inlineStr">
@@ -23190,7 +23016,7 @@
       </c>
       <c r="J23" s="38" t="inlineStr">
         <is>
-          <t>112.10.2</t>
+          <t>112.10.02</t>
         </is>
       </c>
       <c r="K23" s="38" t="inlineStr">
@@ -23245,7 +23071,7 @@
       </c>
       <c r="J24" s="38" t="inlineStr">
         <is>
-          <t>106.10.2</t>
+          <t>106.10.02</t>
         </is>
       </c>
       <c r="K24" s="38" t="inlineStr">
@@ -23355,7 +23181,7 @@
       </c>
       <c r="J26" s="38" t="inlineStr">
         <is>
-          <t>114.4.30</t>
+          <t>114.04.30</t>
         </is>
       </c>
       <c r="K26" s="38" t="inlineStr">
@@ -23410,7 +23236,7 @@
       </c>
       <c r="J27" s="38" t="inlineStr">
         <is>
-          <t>114.9.3</t>
+          <t>114.09.03</t>
         </is>
       </c>
       <c r="K27" s="38" t="inlineStr">
@@ -23465,7 +23291,7 @@
       </c>
       <c r="J28" s="38" t="inlineStr">
         <is>
-          <t>106.4.12</t>
+          <t>106.04.12</t>
         </is>
       </c>
       <c r="K28" s="38" t="inlineStr">
@@ -23575,7 +23401,7 @@
       </c>
       <c r="J30" s="38" t="inlineStr">
         <is>
-          <t>102.12.5</t>
+          <t>102.12.05</t>
         </is>
       </c>
       <c r="K30" s="38" t="inlineStr">
@@ -23630,7 +23456,7 @@
       </c>
       <c r="J31" s="38" t="inlineStr">
         <is>
-          <t>103.10.1</t>
+          <t>103.10.01</t>
         </is>
       </c>
       <c r="K31" s="38" t="inlineStr">
@@ -23740,7 +23566,7 @@
       </c>
       <c r="J33" s="38" t="inlineStr">
         <is>
-          <t>105.6.22</t>
+          <t>105.06.22</t>
         </is>
       </c>
       <c r="K33" s="38" t="inlineStr">
@@ -23795,7 +23621,7 @@
       </c>
       <c r="J34" s="38" t="inlineStr">
         <is>
-          <t>115.6.11</t>
+          <t>115.06.11</t>
         </is>
       </c>
       <c r="K34" s="38" t="inlineStr">
@@ -23850,7 +23676,7 @@
       </c>
       <c r="J35" s="38" t="inlineStr">
         <is>
-          <t>112.1.11</t>
+          <t>112.01.11</t>
         </is>
       </c>
       <c r="K35" s="38" t="inlineStr">
@@ -23905,7 +23731,7 @@
       </c>
       <c r="J36" s="38" t="inlineStr">
         <is>
-          <t>111.11.3</t>
+          <t>111.11.03</t>
         </is>
       </c>
       <c r="K36" s="38" t="inlineStr">
@@ -23960,7 +23786,7 @@
       </c>
       <c r="J37" s="38" t="inlineStr">
         <is>
-          <t>98.1.16</t>
+          <t>98.01.16</t>
         </is>
       </c>
       <c r="K37" s="38" t="inlineStr">
@@ -24015,7 +23841,7 @@
       </c>
       <c r="J38" s="38" t="inlineStr">
         <is>
-          <t>115.1.14</t>
+          <t>115.01.14</t>
         </is>
       </c>
       <c r="K38" s="38" t="inlineStr">
@@ -24070,7 +23896,7 @@
       </c>
       <c r="J39" s="38" t="inlineStr">
         <is>
-          <t>106.2.22</t>
+          <t>106.02.22</t>
         </is>
       </c>
       <c r="K39" s="38" t="inlineStr">
@@ -24125,7 +23951,7 @@
       </c>
       <c r="J40" s="38" t="inlineStr">
         <is>
-          <t>114.1.15</t>
+          <t>114.01.15</t>
         </is>
       </c>
       <c r="K40" s="38" t="inlineStr">
@@ -24170,7 +23996,7 @@
       </c>
       <c r="H41" s="97" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>V</t>
         </is>
       </c>
       <c r="I41" s="38" t="inlineStr">
@@ -24185,7 +24011,7 @@
       </c>
       <c r="K41" s="38" t="inlineStr">
         <is>
-          <t>無特別說明</t>
+          <t>配合組織規程修訂(研究暨產學發展處→研發與永續發展處)</t>
         </is>
       </c>
     </row>
@@ -24235,7 +24061,7 @@
       </c>
       <c r="J42" s="38" t="inlineStr">
         <is>
-          <t>106.2.22</t>
+          <t>106.02.22</t>
         </is>
       </c>
       <c r="K42" s="38" t="inlineStr">
@@ -24290,7 +24116,7 @@
       </c>
       <c r="J43" s="38" t="inlineStr">
         <is>
-          <t>104.1.21</t>
+          <t>104.01.21</t>
         </is>
       </c>
       <c r="K43" s="38" t="inlineStr">
@@ -24345,7 +24171,7 @@
       </c>
       <c r="J44" s="38" t="inlineStr">
         <is>
-          <t>114.6.18</t>
+          <t>114.06.18</t>
         </is>
       </c>
       <c r="K44" s="38" t="inlineStr">
@@ -24400,7 +24226,7 @@
       </c>
       <c r="J45" s="38" t="inlineStr">
         <is>
-          <t>101.6.25</t>
+          <t>101.06.25</t>
         </is>
       </c>
       <c r="K45" s="38" t="inlineStr">
@@ -24510,7 +24336,7 @@
       </c>
       <c r="J47" s="38" t="inlineStr">
         <is>
-          <t>102.1.2</t>
+          <t>102.01.02</t>
         </is>
       </c>
       <c r="K47" s="38" t="inlineStr">
@@ -24620,7 +24446,7 @@
       </c>
       <c r="J49" s="38" t="inlineStr">
         <is>
-          <t>105.10.5</t>
+          <t>105.10.05</t>
         </is>
       </c>
       <c r="K49" s="38" t="inlineStr">
@@ -24675,7 +24501,7 @@
       </c>
       <c r="J50" s="38" t="inlineStr">
         <is>
-          <t>115.3.18</t>
+          <t>115.03.18</t>
         </is>
       </c>
       <c r="K50" s="38" t="inlineStr">
@@ -24720,7 +24546,7 @@
       </c>
       <c r="H51" s="97" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>V</t>
         </is>
       </c>
       <c r="I51" s="38" t="inlineStr">
@@ -24735,7 +24561,7 @@
       </c>
       <c r="K51" s="38" t="inlineStr">
         <is>
-          <t>逾2年未更新(8年未修，預計115提案)</t>
+          <t>逾2年未更新(8年未修，預計115提案)；配合組織規程修訂(研究暨產學發展處→研發與永續發展處)</t>
         </is>
       </c>
     </row>
@@ -24775,7 +24601,7 @@
       </c>
       <c r="H52" s="97" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>V</t>
         </is>
       </c>
       <c r="I52" s="38" t="inlineStr">
@@ -24785,12 +24611,12 @@
       </c>
       <c r="J52" s="38" t="inlineStr">
         <is>
-          <t>105.9.30</t>
+          <t>105.09.30</t>
         </is>
       </c>
       <c r="K52" s="38" t="inlineStr">
         <is>
-          <t>逾2年未更新(10年未修，預計115提案)</t>
+          <t>逾2年未更新(10年未修，預計115提案)；配合組織規程修訂(研究暨產學發展處→研發與永續發展處;校務研究暨規劃室→研發與永續發展處)</t>
         </is>
       </c>
     </row>
@@ -24840,7 +24666,7 @@
       </c>
       <c r="J53" s="38" t="inlineStr">
         <is>
-          <t>104.11.4</t>
+          <t>104.11.04</t>
         </is>
       </c>
       <c r="K53" s="38" t="inlineStr">
@@ -24950,7 +24776,7 @@
       </c>
       <c r="J55" s="38" t="inlineStr">
         <is>
-          <t>112.9.6</t>
+          <t>112.09.06</t>
         </is>
       </c>
       <c r="K55" s="38" t="inlineStr">
@@ -25005,7 +24831,7 @@
       </c>
       <c r="J56" s="38" t="inlineStr">
         <is>
-          <t>108.6.19</t>
+          <t>108.06.19</t>
         </is>
       </c>
       <c r="K56" s="38" t="inlineStr">
@@ -25060,7 +24886,7 @@
       </c>
       <c r="J57" s="38" t="inlineStr">
         <is>
-          <t>105.6.8</t>
+          <t>105.06.08</t>
         </is>
       </c>
       <c r="K57" s="38" t="inlineStr">
@@ -25115,12 +24941,12 @@
       </c>
       <c r="J58" s="38" t="inlineStr">
         <is>
-          <t>105.6.22</t>
+          <t>105.06.22</t>
         </is>
       </c>
       <c r="K58" s="38" t="inlineStr">
         <is>
-          <t>逾2年未更新(10年未修，預計115提案)；配合組織規程修訂(研究發展處→研究暨產學發展處)</t>
+          <t>逾2年未更新(10年未修，預計115提案)；配合組織規程修訂(研究發展處→研發與永續發展處)</t>
         </is>
       </c>
     </row>
@@ -25170,7 +24996,7 @@
       </c>
       <c r="J59" s="38" t="inlineStr">
         <is>
-          <t>105.6.22</t>
+          <t>105.06.22</t>
         </is>
       </c>
       <c r="K59" s="38" t="inlineStr">
@@ -25225,7 +25051,7 @@
       </c>
       <c r="J60" s="38" t="inlineStr">
         <is>
-          <t>106.1.11</t>
+          <t>106.01.11</t>
         </is>
       </c>
       <c r="K60" s="38" t="inlineStr">
@@ -25270,7 +25096,7 @@
       </c>
       <c r="H61" s="97" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>V</t>
         </is>
       </c>
       <c r="I61" s="38" t="inlineStr">
@@ -25280,12 +25106,12 @@
       </c>
       <c r="J61" s="38" t="inlineStr">
         <is>
-          <t>110.6.16</t>
+          <t>110.06.16</t>
         </is>
       </c>
       <c r="K61" s="38" t="inlineStr">
         <is>
-          <t>逾2年未更新(5年未修，預計115提案)</t>
+          <t>逾2年未更新(5年未修，預計115提案)；配合組織規程修訂(研究暨產學發展處→研發與永續發展處)</t>
         </is>
       </c>
     </row>
@@ -25325,7 +25151,7 @@
       </c>
       <c r="H62" s="97" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>V</t>
         </is>
       </c>
       <c r="I62" s="38" t="inlineStr">
@@ -25335,12 +25161,12 @@
       </c>
       <c r="J62" s="38" t="inlineStr">
         <is>
-          <t>113.7.9</t>
+          <t>113.07.09</t>
         </is>
       </c>
       <c r="K62" s="38" t="inlineStr">
         <is>
-          <t>格式瑕疵(含各式顏色標記)</t>
+          <t>格式瑕疵(含各式顏色標記)；配合組織規程修訂(研發處→研發與永續發展處)</t>
         </is>
       </c>
     </row>
@@ -25390,7 +25216,7 @@
       </c>
       <c r="J63" s="38" t="inlineStr">
         <is>
-          <t>108.4.15</t>
+          <t>108.04.15</t>
         </is>
       </c>
       <c r="K63" s="38" t="inlineStr">
@@ -25445,7 +25271,7 @@
       </c>
       <c r="J64" s="38" t="inlineStr">
         <is>
-          <t>114.1.15</t>
+          <t>114.01.15</t>
         </is>
       </c>
       <c r="K64" s="38" t="inlineStr">
@@ -25555,7 +25381,7 @@
       </c>
       <c r="J66" s="38" t="inlineStr">
         <is>
-          <t>110.1.6</t>
+          <t>110.01.06</t>
         </is>
       </c>
       <c r="K66" s="38" t="inlineStr">
@@ -25610,7 +25436,7 @@
       </c>
       <c r="J67" s="38" t="inlineStr">
         <is>
-          <t>111.6.15</t>
+          <t>111.06.15</t>
         </is>
       </c>
       <c r="K67" s="38" t="inlineStr">
